--- a/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
+++ b/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-10</t>
+          <t>ADOM-SL2-10-2024</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -575,16 +575,16 @@
         <v>19.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4208</v>
+        <v>0.01501</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5192</v>
+        <v>0.4039</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2381</v>
+        <v>0.03374</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4016</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="3">
@@ -592,47 +592,47 @@
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-3</t>
+          <t>ADOM-SL2-11-2024</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.416</v>
+        <v>3.519</v>
       </c>
       <c r="E3" t="n">
-        <v>25.23</v>
+        <v>22.91</v>
       </c>
       <c r="F3" t="n">
-        <v>3.908</v>
+        <v>4.383</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="I3" t="n">
-        <v>4.103</v>
+        <v>4.017</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7317</v>
+        <v>0.5249</v>
       </c>
       <c r="K3" t="n">
-        <v>1.241</v>
+        <v>1.261</v>
       </c>
       <c r="L3" t="n">
-        <v>19.05</v>
+        <v>24.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3811</v>
+        <v>0.01329</v>
       </c>
       <c r="N3" t="n">
-        <v>0.297</v>
+        <v>0.7015</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3024</v>
+        <v>0.04513</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2976</v>
+        <v>0.4082</v>
       </c>
     </row>
     <row r="4">
@@ -640,47 +640,47 @@
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-5</t>
+          <t>ADOM-SL2-3-2024</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.449</v>
+        <v>3.415</v>
       </c>
       <c r="E4" t="n">
-        <v>17.72</v>
+        <v>25.23</v>
       </c>
       <c r="F4" t="n">
-        <v>2.617</v>
+        <v>3.908</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H4" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="I4" t="n">
-        <v>4.007</v>
+        <v>4.103</v>
       </c>
       <c r="J4" t="n">
-        <v>0.494</v>
+        <v>0.7317</v>
       </c>
       <c r="K4" t="n">
-        <v>1.216</v>
+        <v>1.241</v>
       </c>
       <c r="L4" t="n">
-        <v>27.43</v>
+        <v>19.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3573</v>
+        <v>0.01254</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3084</v>
+        <v>0.3408</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2793</v>
+        <v>0.02904</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2963</v>
+        <v>0.2159</v>
       </c>
     </row>
     <row r="5">
@@ -688,47 +688,47 @@
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-6</t>
+          <t>ADOM-SL2-4-2024</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.819</v>
+        <v>3.421</v>
       </c>
       <c r="E5" t="n">
-        <v>13.71</v>
+        <v>16.21</v>
       </c>
       <c r="F5" t="n">
-        <v>2.646</v>
+        <v>2.677</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>4.407</v>
+        <v>4.461</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7856</v>
+        <v>0.9186</v>
       </c>
       <c r="K5" t="n">
-        <v>1.289</v>
+        <v>1.272</v>
       </c>
       <c r="L5" t="n">
-        <v>17.41</v>
+        <v>15.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5407</v>
+        <v>0.01245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5585</v>
+        <v>0.2744</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3507</v>
+        <v>0.03048</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5618</v>
+        <v>0.1607</v>
       </c>
     </row>
     <row r="6">
@@ -736,99 +736,95 @@
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-8</t>
+          <t>ADOM-SL2-5-2024</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.847</v>
+        <v>3.448</v>
       </c>
       <c r="E6" t="n">
-        <v>11.77</v>
+        <v>17.72</v>
       </c>
       <c r="F6" t="n">
-        <v>1.991</v>
+        <v>2.617</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="H6" t="n">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="I6" t="n">
-        <v>4.929</v>
+        <v>4.007</v>
       </c>
       <c r="J6" t="n">
-        <v>1.142</v>
+        <v>0.494</v>
       </c>
       <c r="K6" t="n">
-        <v>1.413</v>
+        <v>1.216</v>
       </c>
       <c r="L6" t="n">
-        <v>12.35</v>
+        <v>27.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4466</v>
+        <v>0.009778</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4218</v>
+        <v>0.4761</v>
       </c>
       <c r="O6" t="n">
-        <v>0.233</v>
+        <v>0.02557</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4289</v>
+        <v>0.2794</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Storage 3</t>
-        </is>
-      </c>
+      <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-5</t>
+          <t>ADOM-SL2-6-2024</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.559</v>
+        <v>3.818</v>
       </c>
       <c r="E7" t="n">
-        <v>3.152</v>
+        <v>13.71</v>
       </c>
       <c r="F7" t="n">
-        <v>17.47</v>
+        <v>2.647</v>
       </c>
       <c r="G7" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="I7" t="n">
-        <v>4.655</v>
+        <v>4.407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7415</v>
+        <v>0.7856</v>
       </c>
       <c r="K7" t="n">
-        <v>1.374</v>
+        <v>1.289</v>
       </c>
       <c r="L7" t="n">
-        <v>17.91</v>
+        <v>17.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3261</v>
+        <v>0.0155</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3254</v>
+        <v>0.3554</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2083</v>
+        <v>0.03228</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3494</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="8">
@@ -836,99 +832,99 @@
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-6</t>
+          <t>ADOM-SL2-8-2024</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.257</v>
+        <v>3.846</v>
       </c>
       <c r="E8" t="n">
-        <v>4.184</v>
+        <v>11.77</v>
       </c>
       <c r="F8" t="n">
-        <v>4.56</v>
+        <v>1.991</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="I8" t="n">
-        <v>4.515</v>
+        <v>4.929</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6903</v>
+        <v>1.142</v>
       </c>
       <c r="K8" t="n">
-        <v>1.367</v>
+        <v>1.413</v>
       </c>
       <c r="L8" t="n">
-        <v>22.21</v>
+        <v>12.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2611</v>
+        <v>0.0213</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2151</v>
+        <v>0.2952</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1838</v>
+        <v>0.04065</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2713</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Storage 4</t>
+          <t>Storage 3</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-3</t>
+          <t>ADOM-SL3-1-2024</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.319</v>
+        <v>4.531</v>
       </c>
       <c r="E9" t="n">
-        <v>1.963</v>
+        <v>1.633</v>
       </c>
       <c r="F9" t="n">
-        <v>5.198</v>
+        <v>6.665</v>
       </c>
       <c r="G9" t="n">
-        <v>8.6</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="I9" t="n">
-        <v>4.902</v>
+        <v>4.586</v>
       </c>
       <c r="J9" t="n">
-        <v>0.923</v>
+        <v>0.7396</v>
       </c>
       <c r="K9" t="n">
-        <v>1.368</v>
+        <v>1.344</v>
       </c>
       <c r="L9" t="n">
-        <v>12.77</v>
+        <v>14.53</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3772</v>
+        <v>0.03003</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2581</v>
+        <v>0.4922</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1627</v>
+        <v>0.04209</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3704</v>
+        <v>0.2892</v>
       </c>
     </row>
     <row r="10">
@@ -936,47 +932,47 @@
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-4</t>
+          <t>ADOM-SL3-10-2024</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.524</v>
+        <v>4.143</v>
       </c>
       <c r="E10" t="n">
-        <v>2.861</v>
+        <v>9.173999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>3.65</v>
+        <v>1.884</v>
       </c>
       <c r="G10" t="n">
-        <v>7.42</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="I10" t="n">
-        <v>4.883</v>
+        <v>4.182</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7313</v>
+        <v>0.611</v>
       </c>
       <c r="K10" t="n">
-        <v>1.387</v>
+        <v>1.262</v>
       </c>
       <c r="L10" t="n">
-        <v>17.2</v>
+        <v>22.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2272</v>
+        <v>0.01817</v>
       </c>
       <c r="N10" t="n">
-        <v>0.15</v>
+        <v>0.5998</v>
       </c>
       <c r="O10" t="n">
-        <v>0.15</v>
+        <v>0.03844</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2266</v>
+        <v>0.3041</v>
       </c>
     </row>
     <row r="11">
@@ -984,47 +980,47 @@
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-5</t>
+          <t>ADOM-SL3-11-2024</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.98</v>
+        <v>4.052</v>
       </c>
       <c r="E11" t="n">
-        <v>4.152</v>
+        <v>12.74</v>
       </c>
       <c r="F11" t="n">
-        <v>2.604</v>
+        <v>2.827</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="H11" t="n">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="I11" t="n">
-        <v>4.957</v>
+        <v>4.05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7618</v>
+        <v>0.5894</v>
       </c>
       <c r="K11" t="n">
-        <v>1.381</v>
+        <v>1.242</v>
       </c>
       <c r="L11" t="n">
-        <v>17.21</v>
+        <v>24.79</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3308</v>
+        <v>0.01296</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2163</v>
+        <v>0.3807</v>
       </c>
       <c r="O11" t="n">
-        <v>0.289</v>
+        <v>0.02466</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3075</v>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="12">
@@ -1032,47 +1028,47 @@
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-6</t>
+          <t>ADOM-SL3-3-2024</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.039</v>
+        <v>4.765</v>
       </c>
       <c r="E12" t="n">
-        <v>13.17</v>
+        <v>2.368</v>
       </c>
       <c r="F12" t="n">
-        <v>1.163</v>
+        <v>4.661</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="n">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I12" t="n">
-        <v>4.811</v>
+        <v>4.975</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9981</v>
+        <v>0.7894</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4</v>
+        <v>1.413</v>
       </c>
       <c r="L12" t="n">
-        <v>17.43</v>
+        <v>14.41</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2881</v>
+        <v>0.03233</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1876</v>
+        <v>0.5448</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1636</v>
+        <v>0.04971</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2652</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="13">
@@ -1080,47 +1076,47 @@
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-7</t>
+          <t>ADOM-SL3-4-2024</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.656</v>
+        <v>4.777</v>
       </c>
       <c r="E13" t="n">
-        <v>3.639</v>
+        <v>2.572</v>
       </c>
       <c r="F13" t="n">
-        <v>2.726</v>
+        <v>5.506</v>
       </c>
       <c r="G13" t="n">
-        <v>9.140000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="I13" t="n">
-        <v>4.185</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.6982</v>
       </c>
       <c r="K13" t="n">
-        <v>1.356</v>
+        <v>1.343</v>
       </c>
       <c r="L13" t="n">
-        <v>11.2</v>
+        <v>19.12</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2021</v>
+        <v>0.03363</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1141</v>
+        <v>0.7332</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1678</v>
+        <v>0.05639</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1855</v>
+        <v>0.3795</v>
       </c>
     </row>
     <row r="14">
@@ -1128,47 +1124,47 @@
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-8</t>
+          <t>ADOM-SL3-5-2024</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.047</v>
+        <v>3.558</v>
       </c>
       <c r="E14" t="n">
-        <v>3.263</v>
+        <v>3.152</v>
       </c>
       <c r="F14" t="n">
-        <v>3.466</v>
+        <v>17.47</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="I14" t="n">
-        <v>4.038</v>
+        <v>4.655</v>
       </c>
       <c r="J14" t="n">
-        <v>0.78</v>
+        <v>0.7415</v>
       </c>
       <c r="K14" t="n">
-        <v>1.325</v>
+        <v>1.374</v>
       </c>
       <c r="L14" t="n">
-        <v>12.08</v>
+        <v>17.91</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2985</v>
+        <v>0.02883</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1904</v>
+        <v>0.6204</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2268</v>
+        <v>0.05195</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2851</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="15">
@@ -1176,99 +1172,95 @@
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-9</t>
+          <t>ADOM-SL3-6-2024</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.71</v>
+        <v>4.257</v>
       </c>
       <c r="E15" t="n">
-        <v>3.979</v>
+        <v>4.184</v>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>4.56</v>
       </c>
       <c r="G15" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
-        <v>4.522</v>
+        <v>4.515</v>
       </c>
       <c r="J15" t="n">
-        <v>0.799</v>
+        <v>0.6903</v>
       </c>
       <c r="K15" t="n">
-        <v>1.354</v>
+        <v>1.367</v>
       </c>
       <c r="L15" t="n">
-        <v>13.05</v>
+        <v>22.21</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6498</v>
+        <v>0.0202</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5289</v>
+        <v>0.4521</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1565</v>
+        <v>0.03297</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6518</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>Storage 5</t>
-        </is>
-      </c>
+      <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-10</t>
+          <t>ADOM-SL3-7-2024</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.616</v>
+        <v>4.85</v>
       </c>
       <c r="E16" t="n">
-        <v>25.65</v>
+        <v>23.88</v>
       </c>
       <c r="F16" t="n">
-        <v>1.304</v>
+        <v>0.5437</v>
       </c>
       <c r="G16" t="n">
-        <v>7.65</v>
+        <v>6.1</v>
       </c>
       <c r="H16" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I16" t="n">
-        <v>4.542</v>
+        <v>3.638</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7412</v>
+        <v>0.5859</v>
       </c>
       <c r="K16" t="n">
-        <v>1.401</v>
+        <v>1.179</v>
       </c>
       <c r="L16" t="n">
-        <v>18.11</v>
+        <v>15.44</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.008781000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4616</v>
+        <v>0.2504</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3088</v>
+        <v>0.01678</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5481</v>
+        <v>0.1793</v>
       </c>
     </row>
     <row r="17">
@@ -1276,47 +1268,47 @@
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-2</t>
+          <t>ADOM-SL3-8-2024</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.868</v>
+        <v>3.411</v>
       </c>
       <c r="E17" t="n">
-        <v>9.198</v>
+        <v>14.26</v>
       </c>
       <c r="F17" t="n">
-        <v>1.234</v>
+        <v>6.031</v>
       </c>
       <c r="G17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="I17" t="n">
-        <v>5.367</v>
+        <v>3.88</v>
       </c>
       <c r="J17" t="n">
-        <v>1.22</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.461</v>
+        <v>1.237</v>
       </c>
       <c r="L17" t="n">
-        <v>10.07</v>
+        <v>24.09</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.01058</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4431</v>
+        <v>0.3674</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2938</v>
+        <v>0.0211</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4627</v>
+        <v>0.2217</v>
       </c>
     </row>
     <row r="18">
@@ -1324,95 +1316,99 @@
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-4</t>
+          <t>ADOM-SL3-9-2024</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5.406</v>
+        <v>3.748</v>
       </c>
       <c r="E18" t="n">
-        <v>12.02</v>
+        <v>14.13</v>
       </c>
       <c r="F18" t="n">
-        <v>1.544</v>
+        <v>3.548</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="H18" t="n">
-        <v>205</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>4.65</v>
+        <v>4.831</v>
       </c>
       <c r="J18" t="n">
-        <v>1.049</v>
+        <v>0.7236</v>
       </c>
       <c r="K18" t="n">
-        <v>1.378</v>
+        <v>1.398</v>
       </c>
       <c r="L18" t="n">
-        <v>14.47</v>
+        <v>16.62</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5941</v>
+        <v>0.01484</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4602</v>
+        <v>0.4561</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2403</v>
+        <v>0.03085</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4989</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Storage 4</t>
+        </is>
+      </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-5</t>
+          <t>ADOM-SL4-3-2024</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.546</v>
+        <v>5.319</v>
       </c>
       <c r="E19" t="n">
-        <v>13.1</v>
+        <v>1.963</v>
       </c>
       <c r="F19" t="n">
-        <v>1.377</v>
+        <v>5.198</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="H19" t="n">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="I19" t="n">
-        <v>4.73</v>
+        <v>4.902</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8583</v>
+        <v>0.923</v>
       </c>
       <c r="K19" t="n">
-        <v>1.425</v>
+        <v>1.368</v>
       </c>
       <c r="L19" t="n">
-        <v>16.5</v>
+        <v>12.77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4083</v>
+        <v>0.03168</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2204</v>
+        <v>0.3846</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2567</v>
+        <v>0.04503</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2905</v>
+        <v>0.2469</v>
       </c>
     </row>
     <row r="20">
@@ -1420,47 +1416,47 @@
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6</t>
+          <t>ADOM-SL4-4-2024</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4.912</v>
+        <v>4.524</v>
       </c>
       <c r="E20" t="n">
-        <v>13.3</v>
+        <v>2.861</v>
       </c>
       <c r="F20" t="n">
-        <v>1.827</v>
+        <v>3.65</v>
       </c>
       <c r="G20" t="n">
-        <v>7.3</v>
+        <v>7.42</v>
       </c>
       <c r="H20" t="n">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="I20" t="n">
-        <v>4.582</v>
+        <v>4.883</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7392</v>
+        <v>0.7313</v>
       </c>
       <c r="K20" t="n">
-        <v>1.373</v>
+        <v>1.387</v>
       </c>
       <c r="L20" t="n">
-        <v>17.77</v>
+        <v>17.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5845</v>
+        <v>0.03104</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4093</v>
+        <v>0.4965</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2945</v>
+        <v>0.04152</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="21">
@@ -1468,47 +1464,47 @@
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-7</t>
+          <t>ADOM-SL4-5-2024</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.154</v>
+        <v>4.98</v>
       </c>
       <c r="E21" t="n">
-        <v>18.97</v>
+        <v>4.152</v>
       </c>
       <c r="F21" t="n">
-        <v>1.438</v>
+        <v>2.604</v>
       </c>
       <c r="G21" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="H21" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="I21" t="n">
-        <v>4.345</v>
+        <v>4.957</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8197</v>
+        <v>0.7618</v>
       </c>
       <c r="K21" t="n">
-        <v>1.314</v>
+        <v>1.381</v>
       </c>
       <c r="L21" t="n">
-        <v>15.52</v>
+        <v>17.21</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3986</v>
+        <v>0.03206</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2339</v>
+        <v>0.5483</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2742</v>
+        <v>0.04622</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3054</v>
+        <v>0.2825</v>
       </c>
     </row>
     <row r="22">
@@ -1516,47 +1512,47 @@
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8</t>
+          <t>ADOM-SL4-6-2024</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.496</v>
+        <v>5.039</v>
       </c>
       <c r="E22" t="n">
-        <v>30.88</v>
+        <v>13.17</v>
       </c>
       <c r="F22" t="n">
-        <v>1.204</v>
+        <v>1.163</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="H22" t="n">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="I22" t="n">
-        <v>4.478</v>
+        <v>4.811</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.9981</v>
       </c>
       <c r="K22" t="n">
-        <v>1.315</v>
+        <v>1.4</v>
       </c>
       <c r="L22" t="n">
-        <v>19.45</v>
+        <v>17.43</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.02516</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4413</v>
+        <v>0.2948</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2674</v>
+        <v>0.03727</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5269</v>
+        <v>0.1751</v>
       </c>
     </row>
     <row r="23">
@@ -1564,99 +1560,95 @@
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-9</t>
+          <t>ADOM-SL4-7-2024</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5.219</v>
+        <v>6.656</v>
       </c>
       <c r="E23" t="n">
-        <v>13.81</v>
+        <v>3.639</v>
       </c>
       <c r="F23" t="n">
-        <v>1.252</v>
+        <v>2.726</v>
       </c>
       <c r="G23" t="n">
-        <v>9.01</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I23" t="n">
-        <v>4.248</v>
+        <v>4.185</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8599</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3</v>
+        <v>1.356</v>
       </c>
       <c r="L23" t="n">
-        <v>15.53</v>
+        <v>11.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.03249</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6401</v>
+        <v>0.3109</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2525</v>
+        <v>0.03612</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7209</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Storage 6</t>
-        </is>
-      </c>
+      <c r="B24" s="1" t="n"/>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-1</t>
+          <t>ADOM-SL4-8-2024</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4.749</v>
+        <v>6.047</v>
       </c>
       <c r="E24" t="n">
-        <v>8.269</v>
+        <v>3.263</v>
       </c>
       <c r="F24" t="n">
-        <v>0.153</v>
+        <v>3.467</v>
       </c>
       <c r="G24" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>5.017</v>
+        <v>4.038</v>
       </c>
       <c r="J24" t="n">
-        <v>1.024</v>
+        <v>0.78</v>
       </c>
       <c r="K24" t="n">
-        <v>1.471</v>
+        <v>1.325</v>
       </c>
       <c r="L24" t="n">
-        <v>13.43</v>
+        <v>12.08</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4695</v>
+        <v>0.03399</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4265</v>
+        <v>0.374</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1058</v>
+        <v>0.03697</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5131</v>
+        <v>0.3153</v>
       </c>
     </row>
     <row r="25">
@@ -1664,95 +1656,99 @@
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-10</t>
+          <t>ADOM-SL4-9-2024</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.888</v>
+        <v>5.71</v>
       </c>
       <c r="E25" t="n">
-        <v>16.81</v>
+        <v>3.979</v>
       </c>
       <c r="F25" t="n">
-        <v>2.038</v>
+        <v>2.42</v>
       </c>
       <c r="G25" t="n">
-        <v>7.87</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="I25" t="n">
-        <v>4.498</v>
+        <v>4.522</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5382</v>
+        <v>0.799</v>
       </c>
       <c r="K25" t="n">
-        <v>1.35</v>
+        <v>1.354</v>
       </c>
       <c r="L25" t="n">
-        <v>27.56</v>
+        <v>13.05</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5564</v>
+        <v>0.03198</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4087</v>
+        <v>0.4177</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1353</v>
+        <v>0.03769</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6397</v>
+        <v>0.2848</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="n"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Storage 5</t>
+        </is>
+      </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-2</t>
+          <t>ADOM-SL5-1-2024</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.011</v>
+        <v>5.706</v>
       </c>
       <c r="E26" t="n">
-        <v>8.269</v>
+        <v>9.333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1608</v>
+        <v>1.266</v>
       </c>
       <c r="G26" t="n">
-        <v>7.19</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="I26" t="n">
-        <v>5.015</v>
+        <v>4.871</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9167999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="K26" t="n">
-        <v>1.49</v>
+        <v>1.372</v>
       </c>
       <c r="L26" t="n">
-        <v>12.84</v>
+        <v>12.37</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4419</v>
+        <v>0.0131</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4445</v>
+        <v>0.1064</v>
       </c>
       <c r="O26" t="n">
-        <v>0.428</v>
+        <v>0.02172</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4944</v>
+        <v>0.08098</v>
       </c>
     </row>
     <row r="27">
@@ -1760,47 +1756,47 @@
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3</t>
+          <t>ADOM-SL5-10-2024</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5.397</v>
+        <v>4.616</v>
       </c>
       <c r="E27" t="n">
-        <v>9.866</v>
+        <v>25.65</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1336</v>
+        <v>1.304</v>
       </c>
       <c r="G27" t="n">
-        <v>7.19</v>
+        <v>7.65</v>
       </c>
       <c r="H27" t="n">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="I27" t="n">
-        <v>5.044</v>
+        <v>4.542</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8489</v>
+        <v>0.7412</v>
       </c>
       <c r="K27" t="n">
-        <v>1.428</v>
+        <v>1.401</v>
       </c>
       <c r="L27" t="n">
-        <v>15.27</v>
+        <v>18.11</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3722</v>
+        <v>0.01442</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3124</v>
+        <v>0.2623</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1685</v>
+        <v>0.02532</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4066</v>
+        <v>0.1481</v>
       </c>
     </row>
     <row r="28">
@@ -1808,47 +1804,47 @@
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-4</t>
+          <t>ADOM-SL5-11-2024</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3.946</v>
+        <v>4.597</v>
       </c>
       <c r="E28" t="n">
-        <v>14.82</v>
+        <v>22.14</v>
       </c>
       <c r="F28" t="n">
-        <v>1.795</v>
+        <v>1.72</v>
       </c>
       <c r="G28" t="n">
-        <v>7.21</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I28" t="n">
-        <v>4.533</v>
+        <v>4.781</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7331</v>
+        <v>0.7472</v>
       </c>
       <c r="K28" t="n">
-        <v>1.384</v>
+        <v>1.435</v>
       </c>
       <c r="L28" t="n">
-        <v>16.18</v>
+        <v>17.12</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3883</v>
+        <v>0.01497</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3511</v>
+        <v>0.2813</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4133</v>
+        <v>0.02632</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4013</v>
+        <v>0.1472</v>
       </c>
     </row>
     <row r="29">
@@ -1856,47 +1852,47 @@
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-7</t>
+          <t>ADOM-SL5-12-2024</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.551</v>
+        <v>5.3</v>
       </c>
       <c r="E29" t="n">
-        <v>14.98</v>
+        <v>22.78</v>
       </c>
       <c r="F29" t="n">
-        <v>1.247</v>
+        <v>1.604</v>
       </c>
       <c r="G29" t="n">
-        <v>7.42</v>
+        <v>7.4</v>
       </c>
       <c r="H29" t="n">
         <v>204</v>
       </c>
       <c r="I29" t="n">
-        <v>4.832</v>
+        <v>4.654</v>
       </c>
       <c r="J29" t="n">
-        <v>0.876</v>
+        <v>0.7778</v>
       </c>
       <c r="K29" t="n">
-        <v>1.46</v>
+        <v>1.411</v>
       </c>
       <c r="L29" t="n">
-        <v>11.82</v>
+        <v>16.82</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4093</v>
+        <v>0.02469</v>
       </c>
       <c r="N29" t="n">
-        <v>0.334</v>
+        <v>0.4219</v>
       </c>
       <c r="O29" t="n">
-        <v>0.3961</v>
+        <v>0.04129</v>
       </c>
       <c r="P29" t="n">
-        <v>0.4323</v>
+        <v>0.2191</v>
       </c>
     </row>
     <row r="30">
@@ -1904,47 +1900,47 @@
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-8</t>
+          <t>ADOM-SL5-13-2024</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.811</v>
+        <v>4.702</v>
       </c>
       <c r="E30" t="n">
-        <v>13.24</v>
+        <v>26.39</v>
       </c>
       <c r="F30" t="n">
-        <v>1.67</v>
+        <v>1.226</v>
       </c>
       <c r="G30" t="n">
-        <v>7.17</v>
+        <v>7.85</v>
       </c>
       <c r="H30" t="n">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I30" t="n">
-        <v>4.677</v>
+        <v>4.726</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6365</v>
+        <v>1.045</v>
       </c>
       <c r="K30" t="n">
-        <v>1.413</v>
+        <v>1.363</v>
       </c>
       <c r="L30" t="n">
-        <v>20.41</v>
+        <v>12.94</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4496</v>
+        <v>0.01272</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4482</v>
+        <v>0.1461</v>
       </c>
       <c r="O30" t="n">
-        <v>0.4485</v>
+        <v>0.02117</v>
       </c>
       <c r="P30" t="n">
-        <v>0.4434</v>
+        <v>0.09963</v>
       </c>
     </row>
     <row r="31">
@@ -1952,99 +1948,95 @@
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-9</t>
+          <t>ADOM-SL5-14-2024</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.372</v>
+        <v>5.676</v>
       </c>
       <c r="E31" t="n">
-        <v>14.38</v>
+        <v>11.99</v>
       </c>
       <c r="F31" t="n">
-        <v>1.783</v>
+        <v>1.275</v>
       </c>
       <c r="G31" t="n">
-        <v>7.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I31" t="n">
-        <v>4.726</v>
+        <v>4.782</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6029</v>
+        <v>0.9799</v>
       </c>
       <c r="K31" t="n">
-        <v>1.416</v>
+        <v>1.433</v>
       </c>
       <c r="L31" t="n">
-        <v>24.27</v>
+        <v>12.56</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5286</v>
+        <v>0.02255</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4232</v>
+        <v>0.2943</v>
       </c>
       <c r="O31" t="n">
-        <v>0.2401</v>
+        <v>0.03781</v>
       </c>
       <c r="P31" t="n">
-        <v>0.4983</v>
+        <v>0.1677</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Storage 7</t>
-        </is>
-      </c>
+      <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-1</t>
+          <t>ADOM-SL5-15-2024</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.138</v>
+        <v>5.506</v>
       </c>
       <c r="E32" t="n">
-        <v>11.87</v>
+        <v>12.19</v>
       </c>
       <c r="F32" t="n">
-        <v>1.03</v>
+        <v>1.405</v>
       </c>
       <c r="G32" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="I32" t="n">
-        <v>4.907</v>
+        <v>4.796</v>
       </c>
       <c r="J32" t="n">
-        <v>1.499</v>
+        <v>0.8965</v>
       </c>
       <c r="K32" t="n">
-        <v>1.464</v>
+        <v>1.418</v>
       </c>
       <c r="L32" t="n">
-        <v>7.805</v>
+        <v>16.65</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3879</v>
+        <v>0.01976</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4</v>
+        <v>0.2949</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1431</v>
+        <v>0.03546</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4223</v>
+        <v>0.1708</v>
       </c>
     </row>
     <row r="33">
@@ -2052,47 +2044,47 @@
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-10</t>
+          <t>ADOM-SL5-2-2024</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.74</v>
+        <v>5.865</v>
       </c>
       <c r="E33" t="n">
-        <v>10.67</v>
+        <v>9.198</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2223</v>
+        <v>1.234</v>
       </c>
       <c r="G33" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I33" t="n">
-        <v>4.488</v>
+        <v>5.367</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9808</v>
+        <v>1.22</v>
       </c>
       <c r="K33" t="n">
-        <v>1.358</v>
+        <v>1.461</v>
       </c>
       <c r="L33" t="n">
-        <v>11.07</v>
+        <v>10.07</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3541</v>
+        <v>0.01306</v>
       </c>
       <c r="N33" t="n">
-        <v>0.281</v>
+        <v>0.1156</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1675</v>
+        <v>0.02109</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3918</v>
+        <v>0.08235000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2100,47 +2092,47 @@
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-2</t>
+          <t>ADOM-SL5-3-2024</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6.062</v>
+        <v>5.707</v>
       </c>
       <c r="E34" t="n">
-        <v>11.14</v>
+        <v>9.935</v>
       </c>
       <c r="F34" t="n">
-        <v>1.085</v>
+        <v>1.28</v>
       </c>
       <c r="G34" t="n">
-        <v>8.869999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H34" t="n">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="I34" t="n">
-        <v>4.991</v>
+        <v>4.745</v>
       </c>
       <c r="J34" t="n">
-        <v>1.504</v>
+        <v>1.199</v>
       </c>
       <c r="K34" t="n">
-        <v>1.388</v>
+        <v>1.308</v>
       </c>
       <c r="L34" t="n">
-        <v>7.636</v>
+        <v>12.26</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1953</v>
+        <v>0.01505</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1278</v>
+        <v>0.1372</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7457</v>
+        <v>0.02366</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2148</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="35">
@@ -2148,47 +2140,47 @@
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-3</t>
+          <t>ADOM-SL5-4-2024</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.29</v>
+        <v>5.405</v>
       </c>
       <c r="E35" t="n">
-        <v>9.343999999999999</v>
+        <v>12.02</v>
       </c>
       <c r="F35" t="n">
-        <v>1.057</v>
+        <v>1.544</v>
       </c>
       <c r="G35" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="H35" t="n">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="I35" t="n">
-        <v>4.996</v>
+        <v>4.65</v>
       </c>
       <c r="J35" t="n">
-        <v>1.596</v>
+        <v>1.049</v>
       </c>
       <c r="K35" t="n">
-        <v>1.44</v>
+        <v>1.378</v>
       </c>
       <c r="L35" t="n">
-        <v>6.413</v>
+        <v>14.47</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2914</v>
+        <v>0.01422</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1633</v>
+        <v>0.1637</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2579</v>
+        <v>0.02361</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2006</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="36">
@@ -2196,47 +2188,47 @@
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-5</t>
+          <t>ADOM-SL5-5-2024</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5.4</v>
+        <v>5.543</v>
       </c>
       <c r="E36" t="n">
-        <v>16.6</v>
+        <v>13.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1.007</v>
+        <v>1.377</v>
       </c>
       <c r="G36" t="n">
-        <v>7.16</v>
+        <v>7.7</v>
       </c>
       <c r="H36" t="n">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="I36" t="n">
-        <v>4.614</v>
+        <v>4.73</v>
       </c>
       <c r="J36" t="n">
-        <v>1.246</v>
+        <v>0.8583</v>
       </c>
       <c r="K36" t="n">
-        <v>1.42</v>
+        <v>1.425</v>
       </c>
       <c r="L36" t="n">
-        <v>8.355</v>
+        <v>16.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1991</v>
+        <v>0.01625</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1286</v>
+        <v>0.2341</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2419</v>
+        <v>0.02594</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2376</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="37">
@@ -2244,47 +2236,47 @@
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-6</t>
+          <t>ADOM-SL5-6-2024</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4.512</v>
+        <v>4.912</v>
       </c>
       <c r="E37" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9935</v>
+        <v>1.827</v>
       </c>
       <c r="G37" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H37" t="n">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="I37" t="n">
-        <v>4.498</v>
+        <v>4.582</v>
       </c>
       <c r="J37" t="n">
-        <v>1.071</v>
+        <v>0.7392</v>
       </c>
       <c r="K37" t="n">
-        <v>1.391</v>
+        <v>1.373</v>
       </c>
       <c r="L37" t="n">
-        <v>10.94</v>
+        <v>17.77</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1566</v>
+        <v>0.01715</v>
       </c>
       <c r="N37" t="n">
-        <v>0.09177</v>
+        <v>0.2918</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1836</v>
+        <v>0.02782</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1834</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="38">
@@ -2292,47 +2284,47 @@
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-7</t>
+          <t>ADOM-SL5-7-2024</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4.642</v>
+        <v>5.153</v>
       </c>
       <c r="E38" t="n">
-        <v>17.99</v>
+        <v>18.97</v>
       </c>
       <c r="F38" t="n">
-        <v>1.46</v>
+        <v>1.438</v>
       </c>
       <c r="G38" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="H38" t="n">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="I38" t="n">
-        <v>4.018</v>
+        <v>4.345</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.8197</v>
       </c>
       <c r="K38" t="n">
-        <v>1.236</v>
+        <v>1.314</v>
       </c>
       <c r="L38" t="n">
-        <v>20.63</v>
+        <v>15.52</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1848</v>
+        <v>0.01612</v>
       </c>
       <c r="N38" t="n">
-        <v>0.109</v>
+        <v>0.2383</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2206</v>
+        <v>0.02563</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2162</v>
+        <v>0.1497</v>
       </c>
     </row>
     <row r="39">
@@ -2340,47 +2332,47 @@
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-8</t>
+          <t>ADOM-SL5-8-2024</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.927</v>
+        <v>5.496</v>
       </c>
       <c r="E39" t="n">
-        <v>17.6</v>
+        <v>30.88</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1687</v>
+        <v>1.204</v>
       </c>
       <c r="G39" t="n">
-        <v>7.08</v>
+        <v>7.7</v>
       </c>
       <c r="H39" t="n">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="I39" t="n">
-        <v>4.798</v>
+        <v>4.478</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8616</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>1.405</v>
+        <v>1.315</v>
       </c>
       <c r="L39" t="n">
-        <v>17.03</v>
+        <v>19.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1735</v>
+        <v>0.01653</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1125</v>
+        <v>0.2785</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1715</v>
+        <v>0.02824</v>
       </c>
       <c r="P39" t="n">
-        <v>0.2029</v>
+        <v>0.1583</v>
       </c>
     </row>
     <row r="40">
@@ -2388,58 +2380,1458 @@
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-9</t>
+          <t>ADOM-SL5-9-2024</t>
         </is>
       </c>
       <c r="D40" t="n">
+        <v>5.218</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="G40" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="H40" t="n">
+        <v>190</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.248</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.01437</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.02006</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.1195</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Storage 6</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-1-2024</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4.748</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8.269</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>150</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.017</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="L41" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.1175</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-10-2024</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="G42" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="H42" t="n">
+        <v>195</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L42" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.01917</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.2339</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-12-2024</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4.036</v>
+      </c>
+      <c r="E43" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>212</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.444</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.1783</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-13-2024</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4.213</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H44" t="n">
+        <v>181</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.7358</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="L44" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.1363</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-14-2024</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4.052</v>
+      </c>
+      <c r="E45" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="G45" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="H45" t="n">
+        <v>192</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.812</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="L45" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.2374</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.1337</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-15-2024</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="E46" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H46" t="n">
+        <v>190</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.741</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7741</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="L46" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.2009</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.1205</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-17-2024</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="H47" t="n">
+        <v>206</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.934</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="L47" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.01959</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.1168</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="n"/>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-18-2024</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G48" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="H48" t="n">
+        <v>196</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.579</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.7141</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="L48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.01277</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.02018</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-19-2024</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8.194000000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="H49" t="n">
+        <v>198</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.873</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8752</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L49" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.01355</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.1175</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="1" t="n"/>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-2-2024</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3.519</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.269</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="G50" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H50" t="n">
+        <v>202</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.015</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.9167999999999999</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L50" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.2004</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.1122</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-20-2024</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4.099</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8.194000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="G51" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="H51" t="n">
+        <v>192</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.946</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.9487</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L51" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.01266</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="n"/>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-3-2024</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5.395</v>
+      </c>
+      <c r="E52" t="n">
+        <v>9.866</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="G52" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H52" t="n">
+        <v>206</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5.044</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1.428</v>
+      </c>
+      <c r="L52" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.02675</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.1355</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="1" t="n"/>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-4-2024</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>3.941</v>
+      </c>
+      <c r="E53" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.796</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="H53" t="n">
+        <v>205</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7331</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1.384</v>
+      </c>
+      <c r="L53" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.02788</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.1734</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="n"/>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-7-2024</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4.546</v>
+      </c>
+      <c r="E54" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H54" t="n">
+        <v>204</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.832</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L54" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.01449</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.1334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-8-2024</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4.806</v>
+      </c>
+      <c r="E55" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H55" t="n">
+        <v>212</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4.677</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6365</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="L55" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.02608</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.1793</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n"/>
+      <c r="B56" s="1" t="n"/>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL6-9-2024</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4.368</v>
+      </c>
+      <c r="E56" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="G56" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H56" t="n">
+        <v>211</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4.726</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="L56" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.01745</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.02814</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.1984</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Storage 7</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-1-2024</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>159</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4.907</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7.805</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.07063999999999999</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.0767</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="n"/>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-10-2024</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="G58" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>183</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="L58" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.09435</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="1" t="n"/>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-11-2024</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="G59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>167</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4.632</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="L59" t="n">
+        <v>9.946999999999999</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.01652</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.08311</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="1" t="n"/>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-12-2024</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5.414</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>166</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="L60" t="n">
+        <v>8.965999999999999</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.0934</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.0796</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n"/>
+      <c r="B61" s="1" t="n"/>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-13-2024</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>5.881</v>
+      </c>
+      <c r="E61" t="n">
+        <v>8.726000000000001</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>154</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5.151</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9.407</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.07958</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n"/>
+      <c r="B62" s="1" t="n"/>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-2-2024</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="E62" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>136</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.636</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.08081000000000001</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.08382000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n"/>
+      <c r="B63" s="1" t="n"/>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-3-2024</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>6.289</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9.343999999999999</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>122</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4.996</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.596</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.413</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.07815</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.09153</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n"/>
+      <c r="B64" s="1" t="n"/>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-4-2024</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>6.527</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.9093</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>129</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L64" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.01291</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.06902</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.07485</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n"/>
+      <c r="B65" s="1" t="n"/>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-5-2024</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>5.399</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="G65" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="H65" t="n">
+        <v>116</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4.614</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L65" t="n">
+        <v>8.355</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.02225</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.1052</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n"/>
+      <c r="B66" s="1" t="n"/>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-6-2024</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4.509</v>
+      </c>
+      <c r="E66" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>163</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="L66" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.1102</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n"/>
+      <c r="B67" s="1" t="n"/>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-7-2024</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>4.642</v>
+      </c>
+      <c r="E67" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H67" t="n">
+        <v>177</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="L67" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.2268</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n"/>
+      <c r="B68" s="1" t="n"/>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-8-2024</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="E68" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="G68" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="H68" t="n">
+        <v>162</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4.798</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.8616</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="L68" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.02062</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n"/>
+      <c r="B69" s="1" t="n"/>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-9-2024</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>4.883</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E69" t="n">
         <v>17.91</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F69" t="n">
         <v>0.9068000000000001</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G69" t="n">
         <v>7</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H69" t="n">
         <v>155</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I69" t="n">
         <v>5.453</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J69" t="n">
         <v>1.314</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K69" t="n">
         <v>1.566</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L69" t="n">
         <v>8.696</v>
       </c>
-      <c r="M40" t="n">
-        <v>0.1853</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.1365</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.2275</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.2229</v>
+      <c r="M69" t="n">
+        <v>0.01096</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.09222</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.07461</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B9:B15"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A2:A40"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B16:B23"/>
-    <mergeCell ref="B32:B40"/>
-    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="B57:B69"/>
+    <mergeCell ref="B9:B18"/>
+    <mergeCell ref="B26:B40"/>
+    <mergeCell ref="B2:B8"/>
+    <mergeCell ref="A2:A69"/>
+    <mergeCell ref="B41:B56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
+++ b/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,22 +472,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>epsilon</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>C_org</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Suva</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>eH</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -544,47 +544,47 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-10-2024</t>
+          <t>ADOM-SL2-1-2024</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.615</v>
+        <v>3.922</v>
       </c>
       <c r="E2" t="n">
-        <v>31.55</v>
+        <v>0.1769</v>
       </c>
       <c r="F2" t="n">
-        <v>2.954</v>
+        <v>0.01005</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>1.701</v>
       </c>
       <c r="I2" t="n">
-        <v>4.18</v>
+        <v>5.416</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7188</v>
+        <v>1.34</v>
       </c>
       <c r="K2" t="n">
-        <v>1.294</v>
+        <v>1.549</v>
       </c>
       <c r="L2" t="n">
-        <v>19.57</v>
+        <v>10.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01501</v>
+        <v>0.01786</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4039</v>
+        <v>0.2104</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03374</v>
+        <v>0.03353</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2563</v>
+        <v>0.1187</v>
       </c>
     </row>
     <row r="3">
@@ -592,47 +592,47 @@
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-11-2024</t>
+          <t>ADOM-SL2-10-2024</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.519</v>
+        <v>3.615</v>
       </c>
       <c r="E3" t="n">
-        <v>22.91</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.383</v>
+        <v>0.04829</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>31.55</v>
       </c>
       <c r="H3" t="n">
-        <v>80</v>
+        <v>2.954</v>
       </c>
       <c r="I3" t="n">
-        <v>4.017</v>
+        <v>4.18</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5249</v>
+        <v>0.7188</v>
       </c>
       <c r="K3" t="n">
-        <v>1.261</v>
+        <v>1.294</v>
       </c>
       <c r="L3" t="n">
-        <v>24.11</v>
+        <v>19.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01329</v>
+        <v>0.01501</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7015</v>
+        <v>0.4039</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04513</v>
+        <v>0.03374</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4082</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="4">
@@ -640,47 +640,47 @@
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-3-2024</t>
+          <t>ADOM-SL2-11-2024</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.415</v>
+        <v>3.52</v>
       </c>
       <c r="E4" t="n">
-        <v>25.23</v>
+        <v>1.004</v>
       </c>
       <c r="F4" t="n">
-        <v>3.908</v>
+        <v>0.0518</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5</v>
+        <v>22.91</v>
       </c>
       <c r="H4" t="n">
-        <v>114</v>
+        <v>4.383</v>
       </c>
       <c r="I4" t="n">
-        <v>4.103</v>
+        <v>4.017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7317</v>
+        <v>0.5249</v>
       </c>
       <c r="K4" t="n">
-        <v>1.241</v>
+        <v>1.261</v>
       </c>
       <c r="L4" t="n">
-        <v>19.05</v>
+        <v>24.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01254</v>
+        <v>0.01329</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3408</v>
+        <v>0.7015</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02904</v>
+        <v>0.04513</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2159</v>
+        <v>0.4082</v>
       </c>
     </row>
     <row r="5">
@@ -688,47 +688,47 @@
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-4-2024</t>
+          <t>ADOM-SL2-2-2024</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.421</v>
+        <v>3.372</v>
       </c>
       <c r="E5" t="n">
-        <v>16.21</v>
+        <v>0.1735</v>
       </c>
       <c r="F5" t="n">
-        <v>2.677</v>
+        <v>0.01093</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>9.712999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>1.786</v>
       </c>
       <c r="I5" t="n">
-        <v>4.461</v>
+        <v>6.113</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9186</v>
+        <v>1.379</v>
       </c>
       <c r="K5" t="n">
-        <v>1.272</v>
+        <v>1.536</v>
       </c>
       <c r="L5" t="n">
-        <v>15.07</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01245</v>
+        <v>0.01609</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2744</v>
+        <v>0.2008</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03048</v>
+        <v>0.03077</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1607</v>
+        <v>0.1002</v>
       </c>
     </row>
     <row r="6">
@@ -736,47 +736,47 @@
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-5-2024</t>
+          <t>ADOM-SL2-3-2024</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.448</v>
+        <v>3.416</v>
       </c>
       <c r="E6" t="n">
-        <v>17.72</v>
+        <v>0.986</v>
       </c>
       <c r="F6" t="n">
-        <v>2.617</v>
+        <v>0.05506</v>
       </c>
       <c r="G6" t="n">
-        <v>5.3</v>
+        <v>25.23</v>
       </c>
       <c r="H6" t="n">
-        <v>140</v>
+        <v>3.908</v>
       </c>
       <c r="I6" t="n">
-        <v>4.007</v>
+        <v>4.103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.494</v>
+        <v>0.7317</v>
       </c>
       <c r="K6" t="n">
-        <v>1.216</v>
+        <v>1.241</v>
       </c>
       <c r="L6" t="n">
-        <v>27.43</v>
+        <v>19.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009778</v>
+        <v>0.01254</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4761</v>
+        <v>0.3408</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02557</v>
+        <v>0.02904</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2794</v>
+        <v>0.2159</v>
       </c>
     </row>
     <row r="7">
@@ -784,47 +784,47 @@
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-6-2024</t>
+          <t>ADOM-SL2-4-2024</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.818</v>
+        <v>3.421</v>
       </c>
       <c r="E7" t="n">
-        <v>13.71</v>
+        <v>0.434</v>
       </c>
       <c r="F7" t="n">
-        <v>2.647</v>
+        <v>0.03056</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>16.21</v>
       </c>
       <c r="H7" t="n">
-        <v>106</v>
+        <v>2.677</v>
       </c>
       <c r="I7" t="n">
-        <v>4.407</v>
+        <v>4.461</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7856</v>
+        <v>0.9186</v>
       </c>
       <c r="K7" t="n">
-        <v>1.289</v>
+        <v>1.272</v>
       </c>
       <c r="L7" t="n">
-        <v>17.41</v>
+        <v>15.07</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0155</v>
+        <v>0.01245</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3554</v>
+        <v>0.2744</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03228</v>
+        <v>0.03048</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2094</v>
+        <v>0.1607</v>
       </c>
     </row>
     <row r="8">
@@ -832,99 +832,95 @@
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL2-8-2024</t>
+          <t>ADOM-SL2-5-2024</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.846</v>
+        <v>3.449</v>
       </c>
       <c r="E8" t="n">
-        <v>11.77</v>
+        <v>0.4637</v>
       </c>
       <c r="F8" t="n">
-        <v>1.991</v>
+        <v>0.02791</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>17.72</v>
       </c>
       <c r="H8" t="n">
-        <v>208</v>
+        <v>2.617</v>
       </c>
       <c r="I8" t="n">
-        <v>4.929</v>
+        <v>4.007</v>
       </c>
       <c r="J8" t="n">
-        <v>1.142</v>
+        <v>0.494</v>
       </c>
       <c r="K8" t="n">
-        <v>1.413</v>
+        <v>1.216</v>
       </c>
       <c r="L8" t="n">
-        <v>12.35</v>
+        <v>27.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0213</v>
+        <v>0.009778</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2952</v>
+        <v>0.4761</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04065</v>
+        <v>0.02557</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1663</v>
+        <v>0.2794</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Storage 3</t>
-        </is>
-      </c>
+      <c r="B9" s="1" t="n"/>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-1-2024</t>
+          <t>ADOM-SL2-6-2024</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.531</v>
+        <v>3.819</v>
       </c>
       <c r="E9" t="n">
-        <v>1.633</v>
+        <v>0.3628</v>
       </c>
       <c r="F9" t="n">
-        <v>6.665</v>
+        <v>0.01928</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>13.71</v>
       </c>
       <c r="H9" t="n">
-        <v>190</v>
+        <v>2.646</v>
       </c>
       <c r="I9" t="n">
-        <v>4.586</v>
+        <v>4.407</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7396</v>
+        <v>0.7856</v>
       </c>
       <c r="K9" t="n">
-        <v>1.344</v>
+        <v>1.289</v>
       </c>
       <c r="L9" t="n">
-        <v>14.53</v>
+        <v>17.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03003</v>
+        <v>0.0155</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4922</v>
+        <v>0.3554</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04209</v>
+        <v>0.03228</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2892</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="10">
@@ -932,95 +928,99 @@
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-10-2024</t>
+          <t>ADOM-SL2-8-2024</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.143</v>
+        <v>3.848</v>
       </c>
       <c r="E10" t="n">
-        <v>9.173999999999999</v>
+        <v>0.2344</v>
       </c>
       <c r="F10" t="n">
-        <v>1.884</v>
+        <v>0.01323</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>11.77</v>
       </c>
       <c r="H10" t="n">
-        <v>190</v>
+        <v>1.991</v>
       </c>
       <c r="I10" t="n">
-        <v>4.182</v>
+        <v>4.929</v>
       </c>
       <c r="J10" t="n">
-        <v>0.611</v>
+        <v>1.142</v>
       </c>
       <c r="K10" t="n">
-        <v>1.262</v>
+        <v>1.413</v>
       </c>
       <c r="L10" t="n">
-        <v>22.1</v>
+        <v>12.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01817</v>
+        <v>0.0213</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5998</v>
+        <v>0.2952</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03844</v>
+        <v>0.04065</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3041</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Storage 3</t>
+        </is>
+      </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-11-2024</t>
+          <t>ADOM-SL3-1-2024</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.052</v>
+        <v>4.537</v>
       </c>
       <c r="E11" t="n">
-        <v>12.74</v>
+        <v>0.1088</v>
       </c>
       <c r="F11" t="n">
-        <v>2.827</v>
+        <v>0.005446</v>
       </c>
       <c r="G11" t="n">
-        <v>5.8</v>
+        <v>1.633</v>
       </c>
       <c r="H11" t="n">
-        <v>215</v>
+        <v>6.663</v>
       </c>
       <c r="I11" t="n">
-        <v>4.05</v>
+        <v>4.586</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5894</v>
+        <v>0.7396</v>
       </c>
       <c r="K11" t="n">
-        <v>1.242</v>
+        <v>1.344</v>
       </c>
       <c r="L11" t="n">
-        <v>24.79</v>
+        <v>14.53</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01296</v>
+        <v>0.03003</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3807</v>
+        <v>0.4922</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02466</v>
+        <v>0.04209</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2181</v>
+        <v>0.2892</v>
       </c>
     </row>
     <row r="12">
@@ -1028,47 +1028,47 @@
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-3-2024</t>
+          <t>ADOM-SL3-10-2024</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.765</v>
+        <v>4.149</v>
       </c>
       <c r="E12" t="n">
-        <v>2.368</v>
+        <v>0.1728</v>
       </c>
       <c r="F12" t="n">
-        <v>4.661</v>
+        <v>0.01178</v>
       </c>
       <c r="G12" t="n">
-        <v>7.3</v>
+        <v>9.173999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>146</v>
+        <v>1.883</v>
       </c>
       <c r="I12" t="n">
-        <v>4.975</v>
+        <v>4.182</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7894</v>
+        <v>0.611</v>
       </c>
       <c r="K12" t="n">
-        <v>1.413</v>
+        <v>1.262</v>
       </c>
       <c r="L12" t="n">
-        <v>14.41</v>
+        <v>22.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03233</v>
+        <v>0.01817</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5448</v>
+        <v>0.5998</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04971</v>
+        <v>0.03844</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2867</v>
+        <v>0.3041</v>
       </c>
     </row>
     <row r="13">
@@ -1076,47 +1076,47 @@
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-4-2024</t>
+          <t>ADOM-SL3-11-2024</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.777</v>
+        <v>4.054</v>
       </c>
       <c r="E13" t="n">
-        <v>2.572</v>
+        <v>0.3601</v>
       </c>
       <c r="F13" t="n">
-        <v>5.506</v>
+        <v>0.01602</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>12.74</v>
       </c>
       <c r="H13" t="n">
-        <v>161</v>
+        <v>2.827</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6982</v>
+        <v>0.5894</v>
       </c>
       <c r="K13" t="n">
-        <v>1.343</v>
+        <v>1.242</v>
       </c>
       <c r="L13" t="n">
-        <v>19.12</v>
+        <v>24.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03363</v>
+        <v>0.01296</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7332</v>
+        <v>0.3807</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05639</v>
+        <v>0.02466</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3795</v>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="14">
@@ -1124,47 +1124,47 @@
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-5-2024</t>
+          <t>ADOM-SL3-2-2024</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.558</v>
+        <v>3.966</v>
       </c>
       <c r="E14" t="n">
-        <v>3.152</v>
+        <v>0.1489</v>
       </c>
       <c r="F14" t="n">
-        <v>17.47</v>
+        <v>0.007368</v>
       </c>
       <c r="G14" t="n">
-        <v>6.9</v>
+        <v>5.964</v>
       </c>
       <c r="H14" t="n">
-        <v>177</v>
+        <v>2.496</v>
       </c>
       <c r="I14" t="n">
-        <v>4.655</v>
+        <v>5.22</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7415</v>
+        <v>0.8854</v>
       </c>
       <c r="K14" t="n">
-        <v>1.374</v>
+        <v>1.466</v>
       </c>
       <c r="L14" t="n">
-        <v>17.91</v>
+        <v>13.04</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02883</v>
+        <v>0.01704</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6204</v>
+        <v>0.3393</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05195</v>
+        <v>0.03119</v>
       </c>
       <c r="P14" t="n">
-        <v>0.321</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="15">
@@ -1172,47 +1172,47 @@
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-6-2024</t>
+          <t>ADOM-SL3-3-2024</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.257</v>
+        <v>4.771</v>
       </c>
       <c r="E15" t="n">
-        <v>4.184</v>
+        <v>0.1103</v>
       </c>
       <c r="F15" t="n">
-        <v>4.56</v>
+        <v>0.005521</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>2.368</v>
       </c>
       <c r="H15" t="n">
-        <v>180</v>
+        <v>4.66</v>
       </c>
       <c r="I15" t="n">
-        <v>4.515</v>
+        <v>4.975</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6903</v>
+        <v>0.7894</v>
       </c>
       <c r="K15" t="n">
-        <v>1.367</v>
+        <v>1.413</v>
       </c>
       <c r="L15" t="n">
-        <v>22.21</v>
+        <v>14.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0202</v>
+        <v>0.03233</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4521</v>
+        <v>0.5448</v>
       </c>
       <c r="O15" t="n">
-        <v>0.03297</v>
+        <v>0.04971</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2325</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="16">
@@ -1220,47 +1220,47 @@
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-7-2024</t>
+          <t>ADOM-SL3-4-2024</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.85</v>
+        <v>4.777</v>
       </c>
       <c r="E16" t="n">
-        <v>23.88</v>
+        <v>0.1416</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5437</v>
+        <v>0.00509</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1</v>
+        <v>2.572</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>5.506</v>
       </c>
       <c r="I16" t="n">
-        <v>3.638</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5859</v>
+        <v>0.6982</v>
       </c>
       <c r="K16" t="n">
-        <v>1.179</v>
+        <v>1.343</v>
       </c>
       <c r="L16" t="n">
-        <v>15.44</v>
+        <v>19.12</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008781000000000001</v>
+        <v>0.03363</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2504</v>
+        <v>0.7332</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01678</v>
+        <v>0.05639</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1793</v>
+        <v>0.3795</v>
       </c>
     </row>
     <row r="17">
@@ -1268,47 +1268,47 @@
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-8-2024</t>
+          <t>ADOM-SL3-5-2024</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.411</v>
+        <v>3.559</v>
       </c>
       <c r="E17" t="n">
-        <v>14.26</v>
+        <v>0.5507</v>
       </c>
       <c r="F17" t="n">
-        <v>6.031</v>
+        <v>0.02879</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>3.152</v>
       </c>
       <c r="H17" t="n">
-        <v>200</v>
+        <v>17.47</v>
       </c>
       <c r="I17" t="n">
-        <v>3.88</v>
+        <v>4.655</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.7415</v>
       </c>
       <c r="K17" t="n">
-        <v>1.237</v>
+        <v>1.374</v>
       </c>
       <c r="L17" t="n">
-        <v>24.09</v>
+        <v>17.91</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01058</v>
+        <v>0.02883</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3674</v>
+        <v>0.6204</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0211</v>
+        <v>0.05195</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2217</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="18">
@@ -1316,99 +1316,95 @@
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL3-9-2024</t>
+          <t>ADOM-SL3-6-2024</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.748</v>
+        <v>4.257</v>
       </c>
       <c r="E18" t="n">
-        <v>14.13</v>
+        <v>0.1908</v>
       </c>
       <c r="F18" t="n">
-        <v>3.548</v>
+        <v>0.008776000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>6.7</v>
+        <v>4.184</v>
       </c>
       <c r="H18" t="n">
-        <v>16</v>
+        <v>4.56</v>
       </c>
       <c r="I18" t="n">
-        <v>4.831</v>
+        <v>4.515</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7236</v>
+        <v>0.6903</v>
       </c>
       <c r="K18" t="n">
-        <v>1.398</v>
+        <v>1.367</v>
       </c>
       <c r="L18" t="n">
-        <v>16.62</v>
+        <v>22.21</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01484</v>
+        <v>0.0202</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4561</v>
+        <v>0.4521</v>
       </c>
       <c r="O18" t="n">
-        <v>0.03085</v>
+        <v>0.03297</v>
       </c>
       <c r="P18" t="n">
-        <v>0.213</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Storage 4</t>
-        </is>
-      </c>
+      <c r="B19" s="1" t="n"/>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-3-2024</t>
+          <t>ADOM-SL3-7-2024</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.319</v>
+        <v>4.854</v>
       </c>
       <c r="E19" t="n">
-        <v>1.963</v>
+        <v>0.1298</v>
       </c>
       <c r="F19" t="n">
-        <v>5.198</v>
+        <v>0.006544</v>
       </c>
       <c r="G19" t="n">
-        <v>8.6</v>
+        <v>23.88</v>
       </c>
       <c r="H19" t="n">
-        <v>150</v>
+        <v>0.5436</v>
       </c>
       <c r="I19" t="n">
-        <v>4.902</v>
+        <v>3.638</v>
       </c>
       <c r="J19" t="n">
-        <v>0.923</v>
+        <v>0.5859</v>
       </c>
       <c r="K19" t="n">
-        <v>1.368</v>
+        <v>1.179</v>
       </c>
       <c r="L19" t="n">
-        <v>12.77</v>
+        <v>15.44</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03168</v>
+        <v>0.008781000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3846</v>
+        <v>0.2504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04503</v>
+        <v>0.01678</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2469</v>
+        <v>0.1793</v>
       </c>
     </row>
     <row r="20">
@@ -1416,47 +1412,47 @@
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-4-2024</t>
+          <t>ADOM-SL3-8-2024</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4.524</v>
+        <v>3.444</v>
       </c>
       <c r="E20" t="n">
-        <v>2.861</v>
+        <v>0.857</v>
       </c>
       <c r="F20" t="n">
-        <v>3.65</v>
+        <v>0.0529</v>
       </c>
       <c r="G20" t="n">
-        <v>7.42</v>
+        <v>14.26</v>
       </c>
       <c r="H20" t="n">
-        <v>169</v>
+        <v>6.01</v>
       </c>
       <c r="I20" t="n">
-        <v>4.883</v>
+        <v>3.88</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7313</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.387</v>
+        <v>1.237</v>
       </c>
       <c r="L20" t="n">
-        <v>17.2</v>
+        <v>24.09</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03104</v>
+        <v>0.01058</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4965</v>
+        <v>0.3674</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04152</v>
+        <v>0.0211</v>
       </c>
       <c r="P20" t="n">
-        <v>0.275</v>
+        <v>0.2217</v>
       </c>
     </row>
     <row r="21">
@@ -1464,95 +1460,99 @@
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-5-2024</t>
+          <t>ADOM-SL3-9-2024</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.98</v>
+        <v>3.75</v>
       </c>
       <c r="E21" t="n">
-        <v>4.152</v>
+        <v>0.5012</v>
       </c>
       <c r="F21" t="n">
-        <v>2.604</v>
+        <v>0.02775</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2</v>
+        <v>14.13</v>
       </c>
       <c r="H21" t="n">
-        <v>170</v>
+        <v>3.547</v>
       </c>
       <c r="I21" t="n">
-        <v>4.957</v>
+        <v>4.831</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7618</v>
+        <v>0.7236</v>
       </c>
       <c r="K21" t="n">
-        <v>1.381</v>
+        <v>1.398</v>
       </c>
       <c r="L21" t="n">
-        <v>17.21</v>
+        <v>16.62</v>
       </c>
       <c r="M21" t="n">
-        <v>0.03206</v>
+        <v>0.01484</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5483</v>
+        <v>0.4561</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04622</v>
+        <v>0.03085</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2825</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Storage 4</t>
+        </is>
+      </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-6-2024</t>
+          <t>ADOM-SL4-1-2024</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.039</v>
+        <v>5.64</v>
       </c>
       <c r="E22" t="n">
-        <v>13.17</v>
+        <v>0.1188</v>
       </c>
       <c r="F22" t="n">
-        <v>1.163</v>
+        <v>0.003223</v>
       </c>
       <c r="G22" t="n">
-        <v>7.5</v>
+        <v>1.42</v>
       </c>
       <c r="H22" t="n">
-        <v>177</v>
+        <v>8.366</v>
       </c>
       <c r="I22" t="n">
-        <v>4.811</v>
+        <v>4.877</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9981</v>
+        <v>0.7191</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="L22" t="n">
-        <v>17.43</v>
+        <v>18.73</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02516</v>
+        <v>0.03396</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2948</v>
+        <v>0.6068</v>
       </c>
       <c r="O22" t="n">
-        <v>0.03727</v>
+        <v>0.05201</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1751</v>
+        <v>0.3037</v>
       </c>
     </row>
     <row r="23">
@@ -1560,47 +1560,47 @@
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-7-2024</t>
+          <t>ADOM-SL4-2-2024</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.656</v>
+        <v>4.922</v>
       </c>
       <c r="E23" t="n">
-        <v>3.639</v>
+        <v>0.116</v>
       </c>
       <c r="F23" t="n">
-        <v>2.726</v>
+        <v>0.003935</v>
       </c>
       <c r="G23" t="n">
-        <v>9.140000000000001</v>
+        <v>1.337</v>
       </c>
       <c r="H23" t="n">
-        <v>173</v>
+        <v>8.677</v>
       </c>
       <c r="I23" t="n">
-        <v>4.185</v>
+        <v>4.887</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.7934</v>
       </c>
       <c r="K23" t="n">
-        <v>1.356</v>
+        <v>1.387</v>
       </c>
       <c r="L23" t="n">
-        <v>11.2</v>
+        <v>16.62</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03249</v>
+        <v>0.03435</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3109</v>
+        <v>0.5283</v>
       </c>
       <c r="O23" t="n">
-        <v>0.03612</v>
+        <v>0.04806</v>
       </c>
       <c r="P23" t="n">
-        <v>0.259</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="24">
@@ -1608,47 +1608,47 @@
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-8-2024</t>
+          <t>ADOM-SL4-3-2024</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.047</v>
+        <v>5.319</v>
       </c>
       <c r="E24" t="n">
-        <v>3.263</v>
+        <v>0.102</v>
       </c>
       <c r="F24" t="n">
-        <v>3.467</v>
+        <v>0.003855</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>1.963</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>5.198</v>
       </c>
       <c r="I24" t="n">
-        <v>4.038</v>
+        <v>4.902</v>
       </c>
       <c r="J24" t="n">
-        <v>0.78</v>
+        <v>0.923</v>
       </c>
       <c r="K24" t="n">
-        <v>1.325</v>
+        <v>1.368</v>
       </c>
       <c r="L24" t="n">
-        <v>12.08</v>
+        <v>12.77</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03399</v>
+        <v>0.03168</v>
       </c>
       <c r="N24" t="n">
-        <v>0.374</v>
+        <v>0.3846</v>
       </c>
       <c r="O24" t="n">
-        <v>0.03697</v>
+        <v>0.04503</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3153</v>
+        <v>0.2469</v>
       </c>
     </row>
     <row r="25">
@@ -1656,99 +1656,95 @@
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL4-9-2024</t>
+          <t>ADOM-SL4-4-2024</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.71</v>
+        <v>4.524</v>
       </c>
       <c r="E25" t="n">
-        <v>3.979</v>
+        <v>0.1044</v>
       </c>
       <c r="F25" t="n">
-        <v>2.42</v>
+        <v>0.004531</v>
       </c>
       <c r="G25" t="n">
-        <v>8.199999999999999</v>
+        <v>2.861</v>
       </c>
       <c r="H25" t="n">
-        <v>150</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
-        <v>4.522</v>
+        <v>4.883</v>
       </c>
       <c r="J25" t="n">
-        <v>0.799</v>
+        <v>0.7313</v>
       </c>
       <c r="K25" t="n">
-        <v>1.354</v>
+        <v>1.387</v>
       </c>
       <c r="L25" t="n">
-        <v>13.05</v>
+        <v>17.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0.03198</v>
+        <v>0.03104</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4177</v>
+        <v>0.4965</v>
       </c>
       <c r="O25" t="n">
-        <v>0.03769</v>
+        <v>0.04152</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2848</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>Storage 5</t>
-        </is>
-      </c>
+      <c r="B26" s="1" t="n"/>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-1-2024</t>
+          <t>ADOM-SL4-5-2024</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.706</v>
+        <v>4.98</v>
       </c>
       <c r="E26" t="n">
-        <v>9.333</v>
+        <v>0.1081</v>
       </c>
       <c r="F26" t="n">
-        <v>1.266</v>
+        <v>0.003274</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>4.152</v>
       </c>
       <c r="H26" t="n">
-        <v>192</v>
+        <v>2.604</v>
       </c>
       <c r="I26" t="n">
-        <v>4.871</v>
+        <v>4.957</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3</v>
+        <v>0.7618</v>
       </c>
       <c r="K26" t="n">
-        <v>1.372</v>
+        <v>1.381</v>
       </c>
       <c r="L26" t="n">
-        <v>12.37</v>
+        <v>17.21</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0131</v>
+        <v>0.03206</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1064</v>
+        <v>0.5483</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02172</v>
+        <v>0.04622</v>
       </c>
       <c r="P26" t="n">
-        <v>0.08098</v>
+        <v>0.2825</v>
       </c>
     </row>
     <row r="27">
@@ -1756,47 +1752,47 @@
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-10-2024</t>
+          <t>ADOM-SL4-6-2024</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.616</v>
+        <v>5.039</v>
       </c>
       <c r="E27" t="n">
-        <v>25.65</v>
+        <v>0.1532</v>
       </c>
       <c r="F27" t="n">
-        <v>1.304</v>
+        <v>0.00374</v>
       </c>
       <c r="G27" t="n">
-        <v>7.65</v>
+        <v>13.17</v>
       </c>
       <c r="H27" t="n">
-        <v>183</v>
+        <v>1.163</v>
       </c>
       <c r="I27" t="n">
-        <v>4.542</v>
+        <v>4.811</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7412</v>
+        <v>0.9981</v>
       </c>
       <c r="K27" t="n">
-        <v>1.401</v>
+        <v>1.4</v>
       </c>
       <c r="L27" t="n">
-        <v>18.11</v>
+        <v>17.43</v>
       </c>
       <c r="M27" t="n">
-        <v>0.01442</v>
+        <v>0.02516</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2623</v>
+        <v>0.2948</v>
       </c>
       <c r="O27" t="n">
-        <v>0.02532</v>
+        <v>0.03727</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1481</v>
+        <v>0.1751</v>
       </c>
     </row>
     <row r="28">
@@ -1804,47 +1800,47 @@
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-11-2024</t>
+          <t>ADOM-SL4-7-2024</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.597</v>
+        <v>6.656</v>
       </c>
       <c r="E28" t="n">
-        <v>22.14</v>
+        <v>0.09919</v>
       </c>
       <c r="F28" t="n">
-        <v>1.72</v>
+        <v>0.00253</v>
       </c>
       <c r="G28" t="n">
-        <v>7.4</v>
+        <v>3.639</v>
       </c>
       <c r="H28" t="n">
-        <v>210</v>
+        <v>2.726</v>
       </c>
       <c r="I28" t="n">
-        <v>4.781</v>
+        <v>4.185</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7472</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>1.435</v>
+        <v>1.356</v>
       </c>
       <c r="L28" t="n">
-        <v>17.12</v>
+        <v>11.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0.01497</v>
+        <v>0.03249</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2813</v>
+        <v>0.3109</v>
       </c>
       <c r="O28" t="n">
-        <v>0.02632</v>
+        <v>0.03612</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1472</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="29">
@@ -1852,47 +1848,47 @@
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-12-2024</t>
+          <t>ADOM-SL4-8-2024</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5.3</v>
+        <v>6.047</v>
       </c>
       <c r="E29" t="n">
-        <v>22.78</v>
+        <v>0.1131</v>
       </c>
       <c r="F29" t="n">
-        <v>1.604</v>
+        <v>0.003446</v>
       </c>
       <c r="G29" t="n">
-        <v>7.4</v>
+        <v>3.263</v>
       </c>
       <c r="H29" t="n">
-        <v>204</v>
+        <v>3.466</v>
       </c>
       <c r="I29" t="n">
-        <v>4.654</v>
+        <v>4.038</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7778</v>
+        <v>0.78</v>
       </c>
       <c r="K29" t="n">
-        <v>1.411</v>
+        <v>1.325</v>
       </c>
       <c r="L29" t="n">
-        <v>16.82</v>
+        <v>12.08</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02469</v>
+        <v>0.03399</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4219</v>
+        <v>0.374</v>
       </c>
       <c r="O29" t="n">
-        <v>0.04129</v>
+        <v>0.03697</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2191</v>
+        <v>0.3153</v>
       </c>
     </row>
     <row r="30">
@@ -1900,95 +1896,99 @@
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-13-2024</t>
+          <t>ADOM-SL4-9-2024</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.702</v>
+        <v>5.71</v>
       </c>
       <c r="E30" t="n">
-        <v>26.39</v>
+        <v>0.09626999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.226</v>
+        <v>0.002824</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85</v>
+        <v>3.979</v>
       </c>
       <c r="H30" t="n">
-        <v>199</v>
+        <v>2.42</v>
       </c>
       <c r="I30" t="n">
-        <v>4.726</v>
+        <v>4.522</v>
       </c>
       <c r="J30" t="n">
-        <v>1.045</v>
+        <v>0.799</v>
       </c>
       <c r="K30" t="n">
-        <v>1.363</v>
+        <v>1.354</v>
       </c>
       <c r="L30" t="n">
-        <v>12.94</v>
+        <v>13.05</v>
       </c>
       <c r="M30" t="n">
-        <v>0.01272</v>
+        <v>0.03198</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1461</v>
+        <v>0.4177</v>
       </c>
       <c r="O30" t="n">
-        <v>0.02117</v>
+        <v>0.03769</v>
       </c>
       <c r="P30" t="n">
-        <v>0.09963</v>
+        <v>0.2848</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Storage 5</t>
+        </is>
+      </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-14-2024</t>
+          <t>ADOM-SL5-1-2024</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.676</v>
+        <v>5.708</v>
       </c>
       <c r="E31" t="n">
-        <v>11.99</v>
+        <v>0.1181</v>
       </c>
       <c r="F31" t="n">
-        <v>1.275</v>
+        <v>0.003114</v>
       </c>
       <c r="G31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.333</v>
       </c>
       <c r="H31" t="n">
-        <v>198</v>
+        <v>1.265</v>
       </c>
       <c r="I31" t="n">
-        <v>4.782</v>
+        <v>4.871</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9799</v>
+        <v>1.3</v>
       </c>
       <c r="K31" t="n">
-        <v>1.433</v>
+        <v>1.372</v>
       </c>
       <c r="L31" t="n">
-        <v>12.56</v>
+        <v>12.37</v>
       </c>
       <c r="M31" t="n">
-        <v>0.02255</v>
+        <v>0.0131</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2943</v>
+        <v>0.1064</v>
       </c>
       <c r="O31" t="n">
-        <v>0.03781</v>
+        <v>0.02172</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1677</v>
+        <v>0.08098</v>
       </c>
     </row>
     <row r="32">
@@ -1996,47 +1996,47 @@
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-15-2024</t>
+          <t>ADOM-SL5-10-2024</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.506</v>
+        <v>4.616</v>
       </c>
       <c r="E32" t="n">
-        <v>12.19</v>
+        <v>0.3344</v>
       </c>
       <c r="F32" t="n">
-        <v>1.405</v>
+        <v>0.0107</v>
       </c>
       <c r="G32" t="n">
-        <v>8.800000000000001</v>
+        <v>25.65</v>
       </c>
       <c r="H32" t="n">
-        <v>195</v>
+        <v>1.304</v>
       </c>
       <c r="I32" t="n">
-        <v>4.796</v>
+        <v>4.542</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8965</v>
+        <v>0.7412</v>
       </c>
       <c r="K32" t="n">
-        <v>1.418</v>
+        <v>1.401</v>
       </c>
       <c r="L32" t="n">
-        <v>16.65</v>
+        <v>18.11</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01976</v>
+        <v>0.01442</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2949</v>
+        <v>0.2623</v>
       </c>
       <c r="O32" t="n">
-        <v>0.03546</v>
+        <v>0.02532</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1708</v>
+        <v>0.1481</v>
       </c>
     </row>
     <row r="33">
@@ -2044,47 +2044,47 @@
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-2-2024</t>
+          <t>ADOM-SL5-11-2024</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.865</v>
+        <v>4.597</v>
       </c>
       <c r="E33" t="n">
-        <v>9.198</v>
+        <v>0.3808</v>
       </c>
       <c r="F33" t="n">
-        <v>1.234</v>
+        <v>0.009214999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>8.199999999999999</v>
+        <v>22.14</v>
       </c>
       <c r="H33" t="n">
-        <v>186</v>
+        <v>1.72</v>
       </c>
       <c r="I33" t="n">
-        <v>5.367</v>
+        <v>4.781</v>
       </c>
       <c r="J33" t="n">
-        <v>1.22</v>
+        <v>0.7472</v>
       </c>
       <c r="K33" t="n">
-        <v>1.461</v>
+        <v>1.435</v>
       </c>
       <c r="L33" t="n">
-        <v>10.07</v>
+        <v>17.12</v>
       </c>
       <c r="M33" t="n">
-        <v>0.01306</v>
+        <v>0.01497</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1156</v>
+        <v>0.2813</v>
       </c>
       <c r="O33" t="n">
-        <v>0.02109</v>
+        <v>0.02632</v>
       </c>
       <c r="P33" t="n">
-        <v>0.08235000000000001</v>
+        <v>0.1472</v>
       </c>
     </row>
     <row r="34">
@@ -2092,47 +2092,47 @@
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-3-2024</t>
+          <t>ADOM-SL5-12-2024</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.707</v>
+        <v>5.3</v>
       </c>
       <c r="E34" t="n">
-        <v>9.935</v>
+        <v>0.3655</v>
       </c>
       <c r="F34" t="n">
-        <v>1.28</v>
+        <v>0.008168999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>7.8</v>
+        <v>22.78</v>
       </c>
       <c r="H34" t="n">
-        <v>205</v>
+        <v>1.604</v>
       </c>
       <c r="I34" t="n">
-        <v>4.745</v>
+        <v>4.654</v>
       </c>
       <c r="J34" t="n">
-        <v>1.199</v>
+        <v>0.7778</v>
       </c>
       <c r="K34" t="n">
-        <v>1.308</v>
+        <v>1.411</v>
       </c>
       <c r="L34" t="n">
-        <v>12.26</v>
+        <v>16.82</v>
       </c>
       <c r="M34" t="n">
-        <v>0.01505</v>
+        <v>0.02469</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1372</v>
+        <v>0.4219</v>
       </c>
       <c r="O34" t="n">
-        <v>0.02366</v>
+        <v>0.04129</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1005</v>
+        <v>0.2191</v>
       </c>
     </row>
     <row r="35">
@@ -2140,47 +2140,47 @@
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-4-2024</t>
+          <t>ADOM-SL5-13-2024</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.405</v>
+        <v>4.702</v>
       </c>
       <c r="E35" t="n">
-        <v>12.02</v>
+        <v>0.3236</v>
       </c>
       <c r="F35" t="n">
-        <v>1.544</v>
+        <v>0.01274</v>
       </c>
       <c r="G35" t="n">
-        <v>7.8</v>
+        <v>26.39</v>
       </c>
       <c r="H35" t="n">
-        <v>205</v>
+        <v>1.226</v>
       </c>
       <c r="I35" t="n">
-        <v>4.65</v>
+        <v>4.726</v>
       </c>
       <c r="J35" t="n">
-        <v>1.049</v>
+        <v>1.045</v>
       </c>
       <c r="K35" t="n">
-        <v>1.378</v>
+        <v>1.363</v>
       </c>
       <c r="L35" t="n">
-        <v>14.47</v>
+        <v>12.94</v>
       </c>
       <c r="M35" t="n">
-        <v>0.01422</v>
+        <v>0.01272</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1637</v>
+        <v>0.1461</v>
       </c>
       <c r="O35" t="n">
-        <v>0.02361</v>
+        <v>0.02117</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1096</v>
+        <v>0.09963</v>
       </c>
     </row>
     <row r="36">
@@ -2188,47 +2188,47 @@
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-5-2024</t>
+          <t>ADOM-SL5-14-2024</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5.543</v>
+        <v>5.679</v>
       </c>
       <c r="E36" t="n">
-        <v>13.1</v>
+        <v>0.1528</v>
       </c>
       <c r="F36" t="n">
-        <v>1.377</v>
+        <v>0.00409</v>
       </c>
       <c r="G36" t="n">
-        <v>7.7</v>
+        <v>11.99</v>
       </c>
       <c r="H36" t="n">
-        <v>209</v>
+        <v>1.275</v>
       </c>
       <c r="I36" t="n">
-        <v>4.73</v>
+        <v>4.782</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8583</v>
+        <v>0.9799</v>
       </c>
       <c r="K36" t="n">
-        <v>1.425</v>
+        <v>1.433</v>
       </c>
       <c r="L36" t="n">
-        <v>16.5</v>
+        <v>12.56</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01625</v>
+        <v>0.02255</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2341</v>
+        <v>0.2943</v>
       </c>
       <c r="O36" t="n">
-        <v>0.02594</v>
+        <v>0.03781</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1384</v>
+        <v>0.1677</v>
       </c>
     </row>
     <row r="37">
@@ -2236,47 +2236,47 @@
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-6-2024</t>
+          <t>ADOM-SL5-15-2024</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4.912</v>
+        <v>5.507</v>
       </c>
       <c r="E37" t="n">
-        <v>13.3</v>
+        <v>0.1713</v>
       </c>
       <c r="F37" t="n">
-        <v>1.827</v>
+        <v>0.003964</v>
       </c>
       <c r="G37" t="n">
-        <v>7.3</v>
+        <v>12.19</v>
       </c>
       <c r="H37" t="n">
-        <v>212</v>
+        <v>1.405</v>
       </c>
       <c r="I37" t="n">
-        <v>4.582</v>
+        <v>4.796</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7392</v>
+        <v>0.8965</v>
       </c>
       <c r="K37" t="n">
-        <v>1.373</v>
+        <v>1.418</v>
       </c>
       <c r="L37" t="n">
-        <v>17.77</v>
+        <v>16.65</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01715</v>
+        <v>0.01976</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2918</v>
+        <v>0.2949</v>
       </c>
       <c r="O37" t="n">
-        <v>0.02782</v>
+        <v>0.03546</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1624</v>
+        <v>0.1708</v>
       </c>
     </row>
     <row r="38">
@@ -2284,47 +2284,47 @@
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-7-2024</t>
+          <t>ADOM-SL5-2-2024</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.153</v>
+        <v>5.868</v>
       </c>
       <c r="E38" t="n">
-        <v>18.97</v>
+        <v>0.1135</v>
       </c>
       <c r="F38" t="n">
-        <v>1.438</v>
+        <v>0.003273</v>
       </c>
       <c r="G38" t="n">
-        <v>7.5</v>
+        <v>9.198</v>
       </c>
       <c r="H38" t="n">
-        <v>214</v>
+        <v>1.234</v>
       </c>
       <c r="I38" t="n">
-        <v>4.345</v>
+        <v>5.367</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8197</v>
+        <v>1.22</v>
       </c>
       <c r="K38" t="n">
-        <v>1.314</v>
+        <v>1.461</v>
       </c>
       <c r="L38" t="n">
-        <v>15.52</v>
+        <v>10.07</v>
       </c>
       <c r="M38" t="n">
-        <v>0.01612</v>
+        <v>0.01306</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2383</v>
+        <v>0.1156</v>
       </c>
       <c r="O38" t="n">
-        <v>0.02563</v>
+        <v>0.02109</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1497</v>
+        <v>0.08235000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2332,47 +2332,47 @@
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-8-2024</t>
+          <t>ADOM-SL5-3-2024</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.496</v>
+        <v>5.709</v>
       </c>
       <c r="E39" t="n">
-        <v>30.88</v>
+        <v>0.1272</v>
       </c>
       <c r="F39" t="n">
-        <v>1.204</v>
+        <v>0.003229</v>
       </c>
       <c r="G39" t="n">
-        <v>7.7</v>
+        <v>9.935</v>
       </c>
       <c r="H39" t="n">
-        <v>212</v>
+        <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>4.478</v>
+        <v>4.745</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7344000000000001</v>
+        <v>1.199</v>
       </c>
       <c r="K39" t="n">
-        <v>1.315</v>
+        <v>1.308</v>
       </c>
       <c r="L39" t="n">
-        <v>19.45</v>
+        <v>12.26</v>
       </c>
       <c r="M39" t="n">
-        <v>0.01653</v>
+        <v>0.01505</v>
       </c>
       <c r="N39" t="n">
-        <v>0.2785</v>
+        <v>0.1372</v>
       </c>
       <c r="O39" t="n">
-        <v>0.02824</v>
+        <v>0.02366</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1583</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="40">
@@ -2380,99 +2380,95 @@
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL5-9-2024</t>
+          <t>ADOM-SL5-4-2024</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.218</v>
+        <v>5.406</v>
       </c>
       <c r="E40" t="n">
-        <v>13.81</v>
+        <v>0.1856</v>
       </c>
       <c r="F40" t="n">
-        <v>1.252</v>
+        <v>0.004595</v>
       </c>
       <c r="G40" t="n">
-        <v>9.01</v>
+        <v>12.02</v>
       </c>
       <c r="H40" t="n">
-        <v>190</v>
+        <v>1.544</v>
       </c>
       <c r="I40" t="n">
-        <v>4.248</v>
+        <v>4.65</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8599</v>
+        <v>1.049</v>
       </c>
       <c r="K40" t="n">
-        <v>1.3</v>
+        <v>1.378</v>
       </c>
       <c r="L40" t="n">
-        <v>15.53</v>
+        <v>14.47</v>
       </c>
       <c r="M40" t="n">
-        <v>0.01437</v>
+        <v>0.01422</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1587</v>
+        <v>0.1637</v>
       </c>
       <c r="O40" t="n">
-        <v>0.02006</v>
+        <v>0.02361</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1195</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Storage 6</t>
-        </is>
-      </c>
+      <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-1-2024</t>
+          <t>ADOM-SL5-5-2024</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.748</v>
+        <v>5.546</v>
       </c>
       <c r="E41" t="n">
-        <v>8.269</v>
+        <v>0.1804</v>
       </c>
       <c r="F41" t="n">
-        <v>0.153</v>
+        <v>0.004438</v>
       </c>
       <c r="G41" t="n">
-        <v>7.4</v>
+        <v>13.1</v>
       </c>
       <c r="H41" t="n">
-        <v>150</v>
+        <v>1.377</v>
       </c>
       <c r="I41" t="n">
-        <v>5.017</v>
+        <v>4.73</v>
       </c>
       <c r="J41" t="n">
-        <v>1.024</v>
+        <v>0.8583</v>
       </c>
       <c r="K41" t="n">
-        <v>1.471</v>
+        <v>1.425</v>
       </c>
       <c r="L41" t="n">
-        <v>13.43</v>
+        <v>16.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0.01484</v>
+        <v>0.01625</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1988</v>
+        <v>0.2341</v>
       </c>
       <c r="O41" t="n">
-        <v>0.02347</v>
+        <v>0.02594</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1175</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="42">
@@ -2480,47 +2476,47 @@
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-10-2024</t>
+          <t>ADOM-SL5-6-2024</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.885</v>
+        <v>4.912</v>
       </c>
       <c r="E42" t="n">
-        <v>16.81</v>
+        <v>0.243</v>
       </c>
       <c r="F42" t="n">
-        <v>2.038</v>
+        <v>0.009627</v>
       </c>
       <c r="G42" t="n">
-        <v>7.87</v>
+        <v>13.3</v>
       </c>
       <c r="H42" t="n">
-        <v>195</v>
+        <v>1.827</v>
       </c>
       <c r="I42" t="n">
-        <v>4.498</v>
+        <v>4.582</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5382</v>
+        <v>0.7392</v>
       </c>
       <c r="K42" t="n">
-        <v>1.35</v>
+        <v>1.373</v>
       </c>
       <c r="L42" t="n">
-        <v>27.56</v>
+        <v>17.77</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01917</v>
+        <v>0.01715</v>
       </c>
       <c r="N42" t="n">
-        <v>0.4621</v>
+        <v>0.2918</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0305</v>
+        <v>0.02782</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2339</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="43">
@@ -2528,47 +2524,47 @@
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-12-2024</t>
+          <t>ADOM-SL5-7-2024</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4.036</v>
+        <v>5.154</v>
       </c>
       <c r="E43" t="n">
-        <v>26.7</v>
+        <v>0.2727</v>
       </c>
       <c r="F43" t="n">
-        <v>1.495</v>
+        <v>0.007115</v>
       </c>
       <c r="G43" t="n">
-        <v>7.3</v>
+        <v>18.97</v>
       </c>
       <c r="H43" t="n">
-        <v>212</v>
+        <v>1.438</v>
       </c>
       <c r="I43" t="n">
-        <v>4.444</v>
+        <v>4.345</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6009</v>
+        <v>0.8197</v>
       </c>
       <c r="K43" t="n">
-        <v>1.362</v>
+        <v>1.314</v>
       </c>
       <c r="L43" t="n">
-        <v>22.95</v>
+        <v>15.52</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01514</v>
+        <v>0.01612</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3342</v>
+        <v>0.2383</v>
       </c>
       <c r="O43" t="n">
-        <v>0.02309</v>
+        <v>0.02563</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1783</v>
+        <v>0.1497</v>
       </c>
     </row>
     <row r="44">
@@ -2576,47 +2572,47 @@
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-13-2024</t>
+          <t>ADOM-SL5-8-2024</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.213</v>
+        <v>5.496</v>
       </c>
       <c r="E44" t="n">
-        <v>10.86</v>
+        <v>0.3718</v>
       </c>
       <c r="F44" t="n">
-        <v>1.449</v>
+        <v>0.009441</v>
       </c>
       <c r="G44" t="n">
-        <v>8.31</v>
+        <v>30.88</v>
       </c>
       <c r="H44" t="n">
-        <v>181</v>
+        <v>1.204</v>
       </c>
       <c r="I44" t="n">
-        <v>4.685</v>
+        <v>4.478</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7358</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>1.383</v>
+        <v>1.315</v>
       </c>
       <c r="L44" t="n">
-        <v>15.76</v>
+        <v>19.45</v>
       </c>
       <c r="M44" t="n">
-        <v>0.01339</v>
+        <v>0.01653</v>
       </c>
       <c r="N44" t="n">
-        <v>0.2432</v>
+        <v>0.2785</v>
       </c>
       <c r="O44" t="n">
-        <v>0.02141</v>
+        <v>0.02824</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1363</v>
+        <v>0.1583</v>
       </c>
     </row>
     <row r="45">
@@ -2624,95 +2620,99 @@
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-14-2024</t>
+          <t>ADOM-SL5-9-2024</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.052</v>
+        <v>5.22</v>
       </c>
       <c r="E45" t="n">
-        <v>14.61</v>
+        <v>0.1729</v>
       </c>
       <c r="F45" t="n">
-        <v>1.326</v>
+        <v>0.004236</v>
       </c>
       <c r="G45" t="n">
-        <v>7.66</v>
+        <v>13.81</v>
       </c>
       <c r="H45" t="n">
-        <v>192</v>
+        <v>1.252</v>
       </c>
       <c r="I45" t="n">
-        <v>4.812</v>
+        <v>4.248</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8599</v>
       </c>
       <c r="K45" t="n">
-        <v>1.454</v>
+        <v>1.3</v>
       </c>
       <c r="L45" t="n">
-        <v>15.47</v>
+        <v>15.53</v>
       </c>
       <c r="M45" t="n">
-        <v>0.01373</v>
+        <v>0.01437</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2374</v>
+        <v>0.1587</v>
       </c>
       <c r="O45" t="n">
-        <v>0.02165</v>
+        <v>0.02006</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1337</v>
+        <v>0.1195</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="n"/>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>Storage 6</t>
+        </is>
+      </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-15-2024</t>
+          <t>ADOM-SL6-1-2024</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.133</v>
+        <v>4.75</v>
       </c>
       <c r="E46" t="n">
-        <v>15.56</v>
+        <v>0.01265</v>
       </c>
       <c r="F46" t="n">
-        <v>1.18</v>
+        <v>0.0005391</v>
       </c>
       <c r="G46" t="n">
-        <v>7.52</v>
+        <v>8.269</v>
       </c>
       <c r="H46" t="n">
-        <v>190</v>
+        <v>0.153</v>
       </c>
       <c r="I46" t="n">
-        <v>4.741</v>
+        <v>5.017</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7741</v>
+        <v>1.024</v>
       </c>
       <c r="K46" t="n">
-        <v>1.415</v>
+        <v>1.471</v>
       </c>
       <c r="L46" t="n">
-        <v>13.87</v>
+        <v>13.43</v>
       </c>
       <c r="M46" t="n">
-        <v>0.01198</v>
+        <v>0.01484</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2009</v>
+        <v>0.1988</v>
       </c>
       <c r="O46" t="n">
-        <v>0.019</v>
+        <v>0.02347</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1205</v>
+        <v>0.1175</v>
       </c>
     </row>
     <row r="47">
@@ -2720,47 +2720,47 @@
       <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-17-2024</t>
+          <t>ADOM-SL6-10-2024</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.179</v>
+        <v>4.888</v>
       </c>
       <c r="E47" t="n">
-        <v>17.32</v>
+        <v>0.3426</v>
       </c>
       <c r="F47" t="n">
-        <v>1.215</v>
+        <v>0.01535</v>
       </c>
       <c r="G47" t="n">
-        <v>7.23</v>
+        <v>16.81</v>
       </c>
       <c r="H47" t="n">
-        <v>206</v>
+        <v>2.038</v>
       </c>
       <c r="I47" t="n">
-        <v>4.934</v>
+        <v>4.498</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8121</v>
+        <v>0.5382</v>
       </c>
       <c r="K47" t="n">
-        <v>1.442</v>
+        <v>1.35</v>
       </c>
       <c r="L47" t="n">
-        <v>13.19</v>
+        <v>27.56</v>
       </c>
       <c r="M47" t="n">
-        <v>0.01224</v>
+        <v>0.01917</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2064</v>
+        <v>0.4621</v>
       </c>
       <c r="O47" t="n">
-        <v>0.01959</v>
+        <v>0.0305</v>
       </c>
       <c r="P47" t="n">
-        <v>0.1168</v>
+        <v>0.2339</v>
       </c>
     </row>
     <row r="48">
@@ -2768,47 +2768,47 @@
       <c r="B48" s="1" t="n"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-18-2024</t>
+          <t>ADOM-SL6-12-2024</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.34</v>
+        <v>4.038</v>
       </c>
       <c r="E48" t="n">
-        <v>9.82</v>
+        <v>0.3991</v>
       </c>
       <c r="F48" t="n">
-        <v>1.66</v>
+        <v>0.02143</v>
       </c>
       <c r="G48" t="n">
-        <v>7.33</v>
+        <v>26.7</v>
       </c>
       <c r="H48" t="n">
-        <v>196</v>
+        <v>1.495</v>
       </c>
       <c r="I48" t="n">
-        <v>4.579</v>
+        <v>4.444</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7141</v>
+        <v>0.6009</v>
       </c>
       <c r="K48" t="n">
-        <v>1.321</v>
+        <v>1.362</v>
       </c>
       <c r="L48" t="n">
-        <v>16</v>
+        <v>22.95</v>
       </c>
       <c r="M48" t="n">
-        <v>0.01277</v>
+        <v>0.01514</v>
       </c>
       <c r="N48" t="n">
-        <v>0.235</v>
+        <v>0.3342</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02018</v>
+        <v>0.02309</v>
       </c>
       <c r="P48" t="n">
-        <v>0.138</v>
+        <v>0.1783</v>
       </c>
     </row>
     <row r="49">
@@ -2816,47 +2816,47 @@
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-19-2024</t>
+          <t>ADOM-SL6-13-2024</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.417</v>
+        <v>4.22</v>
       </c>
       <c r="E49" t="n">
-        <v>8.194000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="F49" t="n">
-        <v>1.636</v>
+        <v>0.01275</v>
       </c>
       <c r="G49" t="n">
-        <v>7.57</v>
+        <v>10.86</v>
       </c>
       <c r="H49" t="n">
-        <v>198</v>
+        <v>1.448</v>
       </c>
       <c r="I49" t="n">
-        <v>4.873</v>
+        <v>4.685</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8752</v>
+        <v>0.7358</v>
       </c>
       <c r="K49" t="n">
-        <v>1.45</v>
+        <v>1.383</v>
       </c>
       <c r="L49" t="n">
-        <v>13.04</v>
+        <v>15.76</v>
       </c>
       <c r="M49" t="n">
-        <v>0.01355</v>
+        <v>0.01339</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1965</v>
+        <v>0.2432</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0201</v>
+        <v>0.02141</v>
       </c>
       <c r="P49" t="n">
-        <v>0.1175</v>
+        <v>0.1363</v>
       </c>
     </row>
     <row r="50">
@@ -2864,47 +2864,47 @@
       <c r="B50" s="1" t="n"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-2-2024</t>
+          <t>ADOM-SL6-14-2024</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3.519</v>
+        <v>4.055</v>
       </c>
       <c r="E50" t="n">
-        <v>8.269</v>
+        <v>0.1936</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1775</v>
+        <v>0.01388</v>
       </c>
       <c r="G50" t="n">
-        <v>7.19</v>
+        <v>14.61</v>
       </c>
       <c r="H50" t="n">
-        <v>202</v>
+        <v>1.325</v>
       </c>
       <c r="I50" t="n">
-        <v>5.015</v>
+        <v>4.812</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>1.49</v>
+        <v>1.454</v>
       </c>
       <c r="L50" t="n">
-        <v>12.84</v>
+        <v>15.47</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01272</v>
+        <v>0.01373</v>
       </c>
       <c r="N50" t="n">
-        <v>0.2004</v>
+        <v>0.2374</v>
       </c>
       <c r="O50" t="n">
-        <v>0.02204</v>
+        <v>0.02165</v>
       </c>
       <c r="P50" t="n">
-        <v>0.1122</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="51">
@@ -2912,47 +2912,47 @@
       <c r="B51" s="1" t="n"/>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-20-2024</t>
+          <t>ADOM-SL6-15-2024</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.099</v>
+        <v>4.136</v>
       </c>
       <c r="E51" t="n">
-        <v>8.194000000000001</v>
+        <v>0.1835</v>
       </c>
       <c r="F51" t="n">
-        <v>1.363</v>
+        <v>0.01357</v>
       </c>
       <c r="G51" t="n">
-        <v>7.68</v>
+        <v>15.56</v>
       </c>
       <c r="H51" t="n">
-        <v>192</v>
+        <v>1.179</v>
       </c>
       <c r="I51" t="n">
-        <v>4.946</v>
+        <v>4.741</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9487</v>
+        <v>0.7741</v>
       </c>
       <c r="K51" t="n">
-        <v>1.49</v>
+        <v>1.415</v>
       </c>
       <c r="L51" t="n">
-        <v>11.4</v>
+        <v>13.87</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01266</v>
+        <v>0.01198</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1686</v>
+        <v>0.2009</v>
       </c>
       <c r="O51" t="n">
-        <v>0.01851</v>
+        <v>0.019</v>
       </c>
       <c r="P51" t="n">
-        <v>0.103</v>
+        <v>0.1205</v>
       </c>
     </row>
     <row r="52">
@@ -2960,47 +2960,47 @@
       <c r="B52" s="1" t="n"/>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-3-2024</t>
+          <t>ADOM-SL6-17-2024</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5.395</v>
+        <v>3.181</v>
       </c>
       <c r="E52" t="n">
-        <v>9.866</v>
+        <v>0.2105</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1336</v>
+        <v>0.01731</v>
       </c>
       <c r="G52" t="n">
-        <v>7.19</v>
+        <v>17.32</v>
       </c>
       <c r="H52" t="n">
-        <v>206</v>
+        <v>1.215</v>
       </c>
       <c r="I52" t="n">
-        <v>5.044</v>
+        <v>4.934</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8489</v>
+        <v>0.8121</v>
       </c>
       <c r="K52" t="n">
-        <v>1.428</v>
+        <v>1.442</v>
       </c>
       <c r="L52" t="n">
-        <v>15.27</v>
+        <v>13.19</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0158</v>
+        <v>0.01224</v>
       </c>
       <c r="N52" t="n">
-        <v>0.2613</v>
+        <v>0.2064</v>
       </c>
       <c r="O52" t="n">
-        <v>0.02675</v>
+        <v>0.01959</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1355</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="53">
@@ -3008,47 +3008,47 @@
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-4-2024</t>
+          <t>ADOM-SL6-18-2024</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.941</v>
+        <v>4.344</v>
       </c>
       <c r="E53" t="n">
-        <v>14.82</v>
+        <v>0.163</v>
       </c>
       <c r="F53" t="n">
-        <v>1.796</v>
+        <v>0.01298</v>
       </c>
       <c r="G53" t="n">
-        <v>7.21</v>
+        <v>9.82</v>
       </c>
       <c r="H53" t="n">
-        <v>205</v>
+        <v>1.66</v>
       </c>
       <c r="I53" t="n">
-        <v>4.533</v>
+        <v>4.579</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7331</v>
+        <v>0.7141</v>
       </c>
       <c r="K53" t="n">
-        <v>1.384</v>
+        <v>1.321</v>
       </c>
       <c r="L53" t="n">
-        <v>16.18</v>
+        <v>16</v>
       </c>
       <c r="M53" t="n">
-        <v>0.01532</v>
+        <v>0.01277</v>
       </c>
       <c r="N53" t="n">
-        <v>0.3169</v>
+        <v>0.235</v>
       </c>
       <c r="O53" t="n">
-        <v>0.02788</v>
+        <v>0.02018</v>
       </c>
       <c r="P53" t="n">
-        <v>0.1734</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="54">
@@ -3056,47 +3056,47 @@
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-7-2024</t>
+          <t>ADOM-SL6-19-2024</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.546</v>
+        <v>4.425</v>
       </c>
       <c r="E54" t="n">
-        <v>14.98</v>
+        <v>0.134</v>
       </c>
       <c r="F54" t="n">
-        <v>1.248</v>
+        <v>0.01029</v>
       </c>
       <c r="G54" t="n">
-        <v>7.42</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>204</v>
+        <v>1.635</v>
       </c>
       <c r="I54" t="n">
-        <v>4.832</v>
+        <v>4.873</v>
       </c>
       <c r="J54" t="n">
-        <v>0.876</v>
+        <v>0.8752</v>
       </c>
       <c r="K54" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="L54" t="n">
-        <v>11.82</v>
+        <v>13.04</v>
       </c>
       <c r="M54" t="n">
-        <v>0.01449</v>
+        <v>0.01355</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2321</v>
+        <v>0.1965</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02347</v>
+        <v>0.0201</v>
       </c>
       <c r="P54" t="n">
-        <v>0.1334</v>
+        <v>0.1175</v>
       </c>
     </row>
     <row r="55">
@@ -3104,47 +3104,47 @@
       <c r="B55" s="1" t="n"/>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-8-2024</t>
+          <t>ADOM-SL6-2-2024</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.806</v>
+        <v>5.382</v>
       </c>
       <c r="E55" t="n">
-        <v>13.24</v>
+        <v>0.0131</v>
       </c>
       <c r="F55" t="n">
-        <v>1.67</v>
+        <v>0.0003527</v>
       </c>
       <c r="G55" t="n">
-        <v>7.17</v>
+        <v>8.269</v>
       </c>
       <c r="H55" t="n">
-        <v>212</v>
+        <v>0.1585</v>
       </c>
       <c r="I55" t="n">
-        <v>4.677</v>
+        <v>5.015</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6365</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>1.413</v>
+        <v>1.49</v>
       </c>
       <c r="L55" t="n">
-        <v>20.41</v>
+        <v>12.84</v>
       </c>
       <c r="M55" t="n">
-        <v>0.01572</v>
+        <v>0.01272</v>
       </c>
       <c r="N55" t="n">
-        <v>0.3427</v>
+        <v>0.2004</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02608</v>
+        <v>0.02204</v>
       </c>
       <c r="P55" t="n">
-        <v>0.1793</v>
+        <v>0.1122</v>
       </c>
     </row>
     <row r="56">
@@ -3152,99 +3152,95 @@
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL6-9-2024</t>
+          <t>ADOM-SL6-20-2024</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.368</v>
+        <v>4.108</v>
       </c>
       <c r="E56" t="n">
-        <v>14.38</v>
+        <v>0.1116</v>
       </c>
       <c r="F56" t="n">
-        <v>1.784</v>
+        <v>0.009842</v>
       </c>
       <c r="G56" t="n">
-        <v>7.42</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>211</v>
+        <v>1.362</v>
       </c>
       <c r="I56" t="n">
-        <v>4.726</v>
+        <v>4.946</v>
       </c>
       <c r="J56" t="n">
-        <v>0.6029</v>
+        <v>0.9487</v>
       </c>
       <c r="K56" t="n">
-        <v>1.416</v>
+        <v>1.49</v>
       </c>
       <c r="L56" t="n">
-        <v>24.27</v>
+        <v>11.4</v>
       </c>
       <c r="M56" t="n">
-        <v>0.01745</v>
+        <v>0.01266</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3916</v>
+        <v>0.1686</v>
       </c>
       <c r="O56" t="n">
-        <v>0.02814</v>
+        <v>0.01851</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1984</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>Storage 7</t>
-        </is>
-      </c>
+      <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-1-2024</t>
+          <t>ADOM-SL6-21-2024</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.1</v>
+        <v>4.67</v>
       </c>
       <c r="E57" t="n">
-        <v>11.87</v>
+        <v>0.1906</v>
       </c>
       <c r="F57" t="n">
-        <v>1.203</v>
+        <v>0.01357</v>
       </c>
       <c r="G57" t="n">
-        <v>8.5</v>
+        <v>13.03</v>
       </c>
       <c r="H57" t="n">
-        <v>159</v>
+        <v>1.463</v>
       </c>
       <c r="I57" t="n">
-        <v>4.907</v>
+        <v>4.865</v>
       </c>
       <c r="J57" t="n">
-        <v>1.499</v>
+        <v>0.994</v>
       </c>
       <c r="K57" t="n">
-        <v>1.464</v>
+        <v>1.405</v>
       </c>
       <c r="L57" t="n">
-        <v>7.805</v>
+        <v>12.3</v>
       </c>
       <c r="M57" t="n">
-        <v>0.01261</v>
+        <v>0.01183</v>
       </c>
       <c r="N57" t="n">
-        <v>0.07063999999999999</v>
+        <v>0.1798</v>
       </c>
       <c r="O57" t="n">
-        <v>0.0198</v>
+        <v>0.02104</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0767</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="58">
@@ -3252,47 +3248,47 @@
       <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-10-2024</t>
+          <t>ADOM-SL6-3-2024</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.739</v>
+        <v>5.398</v>
       </c>
       <c r="E58" t="n">
-        <v>10.67</v>
+        <v>0.01318</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2225</v>
+        <v>0.0003946</v>
       </c>
       <c r="G58" t="n">
-        <v>7.5</v>
+        <v>9.866</v>
       </c>
       <c r="H58" t="n">
-        <v>183</v>
+        <v>0.1336</v>
       </c>
       <c r="I58" t="n">
-        <v>4.488</v>
+        <v>5.044</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9808</v>
+        <v>0.8489</v>
       </c>
       <c r="K58" t="n">
-        <v>1.358</v>
+        <v>1.428</v>
       </c>
       <c r="L58" t="n">
-        <v>11.07</v>
+        <v>15.27</v>
       </c>
       <c r="M58" t="n">
-        <v>0.01091</v>
+        <v>0.0158</v>
       </c>
       <c r="N58" t="n">
-        <v>0.12</v>
+        <v>0.2613</v>
       </c>
       <c r="O58" t="n">
-        <v>0.01647</v>
+        <v>0.02675</v>
       </c>
       <c r="P58" t="n">
-        <v>0.09435</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="59">
@@ -3300,47 +3296,47 @@
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-11-2024</t>
+          <t>ADOM-SL6-4-2024</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5.39</v>
+        <v>3.946</v>
       </c>
       <c r="E59" t="n">
-        <v>10.42</v>
+        <v>0.266</v>
       </c>
       <c r="F59" t="n">
-        <v>1.094</v>
+        <v>0.01664</v>
       </c>
       <c r="G59" t="n">
-        <v>8.5</v>
+        <v>14.82</v>
       </c>
       <c r="H59" t="n">
-        <v>167</v>
+        <v>1.795</v>
       </c>
       <c r="I59" t="n">
-        <v>4.632</v>
+        <v>4.533</v>
       </c>
       <c r="J59" t="n">
-        <v>1.197</v>
+        <v>0.7331</v>
       </c>
       <c r="K59" t="n">
-        <v>1.369</v>
+        <v>1.384</v>
       </c>
       <c r="L59" t="n">
-        <v>9.946999999999999</v>
+        <v>16.18</v>
       </c>
       <c r="M59" t="n">
-        <v>0.01144</v>
+        <v>0.01532</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0939</v>
+        <v>0.3169</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01652</v>
+        <v>0.02788</v>
       </c>
       <c r="P59" t="n">
-        <v>0.08311</v>
+        <v>0.1734</v>
       </c>
     </row>
     <row r="60">
@@ -3348,47 +3344,47 @@
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-12-2024</t>
+          <t>ADOM-SL6-5-2024</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.414</v>
+        <v>3.489</v>
       </c>
       <c r="E60" t="n">
-        <v>9.82</v>
+        <v>0.2382</v>
       </c>
       <c r="F60" t="n">
-        <v>1.295</v>
+        <v>0.01646</v>
       </c>
       <c r="G60" t="n">
-        <v>8.800000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="H60" t="n">
-        <v>166</v>
+        <v>1.96</v>
       </c>
       <c r="I60" t="n">
-        <v>5.26</v>
+        <v>4.506</v>
       </c>
       <c r="J60" t="n">
-        <v>1.054</v>
+        <v>0.7862</v>
       </c>
       <c r="K60" t="n">
-        <v>1.462</v>
+        <v>1.353</v>
       </c>
       <c r="L60" t="n">
-        <v>8.965999999999999</v>
+        <v>15.17</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01027</v>
+        <v>0.01143</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0934</v>
+        <v>0.1807</v>
       </c>
       <c r="O60" t="n">
-        <v>0.0144</v>
+        <v>0.0188</v>
       </c>
       <c r="P60" t="n">
-        <v>0.0796</v>
+        <v>0.1109</v>
       </c>
     </row>
     <row r="61">
@@ -3396,47 +3392,47 @@
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-13-2024</t>
+          <t>ADOM-SL6-6-2024</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5.881</v>
+        <v>3.902</v>
       </c>
       <c r="E61" t="n">
-        <v>8.726000000000001</v>
+        <v>0.2284</v>
       </c>
       <c r="F61" t="n">
-        <v>1.258</v>
+        <v>0.01857</v>
       </c>
       <c r="G61" t="n">
-        <v>8.869999999999999</v>
+        <v>14.83</v>
       </c>
       <c r="H61" t="n">
-        <v>154</v>
+        <v>1.54</v>
       </c>
       <c r="I61" t="n">
-        <v>5.151</v>
+        <v>4.768</v>
       </c>
       <c r="J61" t="n">
-        <v>1.106</v>
+        <v>0.8988</v>
       </c>
       <c r="K61" t="n">
-        <v>1.36</v>
+        <v>1.398</v>
       </c>
       <c r="L61" t="n">
-        <v>9.407</v>
+        <v>14.31</v>
       </c>
       <c r="M61" t="n">
-        <v>0.01108</v>
+        <v>0.01221</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1015</v>
+        <v>0.1758</v>
       </c>
       <c r="O61" t="n">
-        <v>0.01592</v>
+        <v>0.02042</v>
       </c>
       <c r="P61" t="n">
-        <v>0.07958</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="62">
@@ -3444,47 +3440,47 @@
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-2-2024</t>
+          <t>ADOM-SL6-7-2024</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6.06</v>
+        <v>4.552</v>
       </c>
       <c r="E62" t="n">
-        <v>11.14</v>
+        <v>0.1868</v>
       </c>
       <c r="F62" t="n">
-        <v>1.085</v>
+        <v>0.01116</v>
       </c>
       <c r="G62" t="n">
-        <v>8.869999999999999</v>
+        <v>14.98</v>
       </c>
       <c r="H62" t="n">
-        <v>136</v>
+        <v>1.247</v>
       </c>
       <c r="I62" t="n">
-        <v>4.991</v>
+        <v>4.832</v>
       </c>
       <c r="J62" t="n">
-        <v>1.504</v>
+        <v>0.876</v>
       </c>
       <c r="K62" t="n">
-        <v>1.388</v>
+        <v>1.46</v>
       </c>
       <c r="L62" t="n">
-        <v>7.636</v>
+        <v>11.82</v>
       </c>
       <c r="M62" t="n">
-        <v>0.01446</v>
+        <v>0.01449</v>
       </c>
       <c r="N62" t="n">
-        <v>0.08081000000000001</v>
+        <v>0.2321</v>
       </c>
       <c r="O62" t="n">
-        <v>0.02147</v>
+        <v>0.02347</v>
       </c>
       <c r="P62" t="n">
-        <v>0.08382000000000001</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="63">
@@ -3492,47 +3488,47 @@
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-3-2024</t>
+          <t>ADOM-SL6-8-2024</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6.289</v>
+        <v>4.811</v>
       </c>
       <c r="E63" t="n">
-        <v>9.343999999999999</v>
+        <v>0.2211</v>
       </c>
       <c r="F63" t="n">
-        <v>1.057</v>
+        <v>0.01195</v>
       </c>
       <c r="G63" t="n">
-        <v>8.5</v>
+        <v>13.24</v>
       </c>
       <c r="H63" t="n">
-        <v>122</v>
+        <v>1.67</v>
       </c>
       <c r="I63" t="n">
-        <v>4.996</v>
+        <v>4.677</v>
       </c>
       <c r="J63" t="n">
-        <v>1.596</v>
+        <v>0.6365</v>
       </c>
       <c r="K63" t="n">
-        <v>1.44</v>
+        <v>1.413</v>
       </c>
       <c r="L63" t="n">
-        <v>6.413</v>
+        <v>20.41</v>
       </c>
       <c r="M63" t="n">
-        <v>0.01615</v>
+        <v>0.01572</v>
       </c>
       <c r="N63" t="n">
-        <v>0.07815</v>
+        <v>0.3427</v>
       </c>
       <c r="O63" t="n">
-        <v>0.02522</v>
+        <v>0.02608</v>
       </c>
       <c r="P63" t="n">
-        <v>0.09153</v>
+        <v>0.1793</v>
       </c>
     </row>
     <row r="64">
@@ -3540,95 +3536,99 @@
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-4-2024</t>
+          <t>ADOM-SL6-9-2024</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6.527</v>
+        <v>4.372</v>
       </c>
       <c r="E64" t="n">
-        <v>10.34</v>
+        <v>0.2564</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9093</v>
+        <v>0.01579</v>
       </c>
       <c r="G64" t="n">
-        <v>8.6</v>
+        <v>14.38</v>
       </c>
       <c r="H64" t="n">
-        <v>129</v>
+        <v>1.783</v>
       </c>
       <c r="I64" t="n">
-        <v>4.851</v>
+        <v>4.726</v>
       </c>
       <c r="J64" t="n">
-        <v>1.463</v>
+        <v>0.6029</v>
       </c>
       <c r="K64" t="n">
-        <v>1.318</v>
+        <v>1.416</v>
       </c>
       <c r="L64" t="n">
-        <v>7.69</v>
+        <v>24.27</v>
       </c>
       <c r="M64" t="n">
-        <v>0.01291</v>
+        <v>0.01745</v>
       </c>
       <c r="N64" t="n">
-        <v>0.06902</v>
+        <v>0.3916</v>
       </c>
       <c r="O64" t="n">
-        <v>0.01816</v>
+        <v>0.02814</v>
       </c>
       <c r="P64" t="n">
-        <v>0.07485</v>
+        <v>0.1984</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
-      <c r="B65" s="1" t="n"/>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Storage 7</t>
+        </is>
+      </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-5-2024</t>
+          <t>ADOM-SL7-1-2024</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5.399</v>
+        <v>5.803</v>
       </c>
       <c r="E65" t="n">
-        <v>16.6</v>
+        <v>0.1193</v>
       </c>
       <c r="F65" t="n">
-        <v>1.007</v>
+        <v>0.004075</v>
       </c>
       <c r="G65" t="n">
-        <v>7.16</v>
+        <v>11.87</v>
       </c>
       <c r="H65" t="n">
-        <v>116</v>
+        <v>1.005</v>
       </c>
       <c r="I65" t="n">
-        <v>4.614</v>
+        <v>4.907</v>
       </c>
       <c r="J65" t="n">
-        <v>1.246</v>
+        <v>1.499</v>
       </c>
       <c r="K65" t="n">
-        <v>1.42</v>
+        <v>1.464</v>
       </c>
       <c r="L65" t="n">
-        <v>8.355</v>
+        <v>7.805</v>
       </c>
       <c r="M65" t="n">
-        <v>0.01582</v>
+        <v>0.01261</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1188</v>
+        <v>0.07063999999999999</v>
       </c>
       <c r="O65" t="n">
-        <v>0.02225</v>
+        <v>0.0198</v>
       </c>
       <c r="P65" t="n">
-        <v>0.1052</v>
+        <v>0.0767</v>
       </c>
     </row>
     <row r="66">
@@ -3636,47 +3636,47 @@
       <c r="B66" s="1" t="n"/>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-6-2024</t>
+          <t>ADOM-SL7-10-2024</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4.509</v>
+        <v>1.74</v>
       </c>
       <c r="E66" t="n">
-        <v>15.6</v>
+        <v>0.02372</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9937</v>
+        <v>0.01126</v>
       </c>
       <c r="G66" t="n">
-        <v>7.2</v>
+        <v>10.67</v>
       </c>
       <c r="H66" t="n">
-        <v>163</v>
+        <v>0.2223</v>
       </c>
       <c r="I66" t="n">
-        <v>4.498</v>
+        <v>4.488</v>
       </c>
       <c r="J66" t="n">
-        <v>1.071</v>
+        <v>0.9808</v>
       </c>
       <c r="K66" t="n">
-        <v>1.391</v>
+        <v>1.358</v>
       </c>
       <c r="L66" t="n">
-        <v>10.94</v>
+        <v>11.07</v>
       </c>
       <c r="M66" t="n">
-        <v>0.01438</v>
+        <v>0.01091</v>
       </c>
       <c r="N66" t="n">
-        <v>0.1447</v>
+        <v>0.12</v>
       </c>
       <c r="O66" t="n">
-        <v>0.0227</v>
+        <v>0.01647</v>
       </c>
       <c r="P66" t="n">
-        <v>0.1102</v>
+        <v>0.09435</v>
       </c>
     </row>
     <row r="67">
@@ -3684,47 +3684,47 @@
       <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-7-2024</t>
+          <t>ADOM-SL7-11-2024</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4.642</v>
+        <v>5.391</v>
       </c>
       <c r="E67" t="n">
-        <v>17.99</v>
+        <v>0.114</v>
       </c>
       <c r="F67" t="n">
-        <v>1.46</v>
+        <v>0.004794</v>
       </c>
       <c r="G67" t="n">
-        <v>7.11</v>
+        <v>10.42</v>
       </c>
       <c r="H67" t="n">
-        <v>177</v>
+        <v>1.094</v>
       </c>
       <c r="I67" t="n">
-        <v>4.018</v>
+        <v>4.632</v>
       </c>
       <c r="J67" t="n">
-        <v>0.5760999999999999</v>
+        <v>1.197</v>
       </c>
       <c r="K67" t="n">
-        <v>1.236</v>
+        <v>1.369</v>
       </c>
       <c r="L67" t="n">
-        <v>20.63</v>
+        <v>9.946999999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01256</v>
+        <v>0.01144</v>
       </c>
       <c r="N67" t="n">
-        <v>0.4002</v>
+        <v>0.0939</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0263</v>
+        <v>0.01652</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2268</v>
+        <v>0.08311</v>
       </c>
     </row>
     <row r="68">
@@ -3732,47 +3732,47 @@
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>ADOM-SL7-8-2024</t>
+          <t>ADOM-SL7-12-2024</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.926</v>
+        <v>5.426</v>
       </c>
       <c r="E68" t="n">
-        <v>17.6</v>
+        <v>0.1271</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1688</v>
+        <v>0.004576</v>
       </c>
       <c r="G68" t="n">
-        <v>7.08</v>
+        <v>9.82</v>
       </c>
       <c r="H68" t="n">
-        <v>162</v>
+        <v>1.295</v>
       </c>
       <c r="I68" t="n">
-        <v>4.798</v>
+        <v>5.26</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8616</v>
+        <v>1.054</v>
       </c>
       <c r="K68" t="n">
-        <v>1.405</v>
+        <v>1.462</v>
       </c>
       <c r="L68" t="n">
-        <v>17.03</v>
+        <v>8.965999999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>0.01115</v>
+        <v>0.01027</v>
       </c>
       <c r="N68" t="n">
-        <v>0.1655</v>
+        <v>0.0934</v>
       </c>
       <c r="O68" t="n">
-        <v>0.02062</v>
+        <v>0.0144</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1065</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="69">
@@ -3780,58 +3780,5263 @@
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="1" t="inlineStr">
         <is>
+          <t>ADOM-SL7-13-2024</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5.882</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.003406</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.726000000000001</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5.151</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L69" t="n">
+        <v>9.407</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.07958</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n"/>
+      <c r="B70" s="1" t="n"/>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-2-2024</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>6.062</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.004467</v>
+      </c>
+      <c r="G70" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4.991</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7.636</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.08081000000000001</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.02147</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.08382000000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n"/>
+      <c r="B71" s="1" t="n"/>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-3-2024</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.09873</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.002933</v>
+      </c>
+      <c r="G71" t="n">
+        <v>9.343999999999999</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="I71" t="n">
+        <v>4.996</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.596</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6.413</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.07815</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.09153</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n"/>
+      <c r="B72" s="1" t="n"/>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-4-2024</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>6.529</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.09402000000000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.003077</v>
+      </c>
+      <c r="G72" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.9093</v>
+      </c>
+      <c r="I72" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="L72" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.01291</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.06902</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.07485</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n"/>
+      <c r="B73" s="1" t="n"/>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-5-2024</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.005082</v>
+      </c>
+      <c r="G73" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="I73" t="n">
+        <v>4.614</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L73" t="n">
+        <v>8.355</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.02225</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.1052</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n"/>
+      <c r="B74" s="1" t="n"/>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-6-2024</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4.513</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.006872</v>
+      </c>
+      <c r="G74" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9935</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="L74" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.01438</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.1102</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n"/>
+      <c r="B75" s="1" t="n"/>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-7-2024</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>4.642</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.007806</v>
+      </c>
+      <c r="G75" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I75" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="L75" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.2268</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="n"/>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>ADOM-SL7-8-2024</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="G76" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4.798</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.8616</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="L76" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.02062</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n"/>
+      <c r="B77" s="1" t="n"/>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
           <t>ADOM-SL7-9-2024</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D77" t="n">
         <v>4.883</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E77" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.007055</v>
+      </c>
+      <c r="G77" t="n">
         <v>17.91</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H77" t="n">
         <v>0.9068000000000001</v>
       </c>
-      <c r="G69" t="n">
-        <v>7</v>
-      </c>
-      <c r="H69" t="n">
-        <v>155</v>
-      </c>
-      <c r="I69" t="n">
+      <c r="I77" t="n">
         <v>5.453</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J77" t="n">
         <v>1.314</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K77" t="n">
         <v>1.566</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L77" t="n">
         <v>8.696</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M77" t="n">
         <v>0.01096</v>
       </c>
-      <c r="N69" t="n">
+      <c r="N77" t="n">
         <v>0.09222</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O77" t="n">
         <v>0.01639</v>
       </c>
-      <c r="P69" t="n">
+      <c r="P77" t="n">
         <v>0.07461</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>CHA-GL02-2024</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="G78" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="H78" t="n">
+        <v>5.008</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.9008</v>
+      </c>
+      <c r="L78" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.02959</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.7493</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n"/>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>CHF-GL02-2024</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="G79" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.9609</v>
+      </c>
+      <c r="L79" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.04117</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.8119</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n"/>
+      <c r="B80" s="1" t="n"/>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>CHF-GL98-2024</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="G80" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H80" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.8186</v>
+      </c>
+      <c r="L80" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.006153</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.3863</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n"/>
+      <c r="B81" s="1" t="n"/>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>CHF-LDE00-2024</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2.712</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.8376</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.07933</v>
+      </c>
+      <c r="G81" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.739</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.2151</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.9026</v>
+      </c>
+      <c r="L81" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.02753</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>Lg</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>Lg</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>LG-10-1-16-2024</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.002724</v>
+      </c>
+      <c r="G82" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4.162</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.403</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="L82" t="n">
+        <v>5.571</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.07426000000000001</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.2274</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n"/>
+      <c r="B83" s="1" t="n"/>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>LG-10-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.007274</v>
+      </c>
+      <c r="G83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="I83" t="n">
+        <v>4.388</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.767</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="L83" t="n">
+        <v>4.391</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.07319000000000001</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.1543</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.1983</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n"/>
+      <c r="B84" s="1" t="n"/>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>LG-10-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2.889</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.04909</v>
+      </c>
+      <c r="G84" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4.222</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="L84" t="n">
+        <v>5.692</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.08835999999999999</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.2559</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n"/>
+      <c r="B85" s="1" t="n"/>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>LG-10-2-16-2024</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="G85" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="H85" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="I85" t="n">
+        <v>4.888</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="L85" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.2135</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n"/>
+      <c r="B86" s="1" t="n"/>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>LG-10-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5.171</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.007901999999999999</v>
+      </c>
+      <c r="G86" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I86" t="n">
+        <v>4.972</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="L86" t="n">
+        <v>8.073</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.07555000000000001</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.2323</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n"/>
+      <c r="B87" s="1" t="n"/>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>LG-10-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.05234</v>
+      </c>
+      <c r="G87" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.575</v>
+      </c>
+      <c r="I87" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2.696</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="L87" t="n">
+        <v>5.885</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.06283</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.07634000000000001</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.1739</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n"/>
+      <c r="B88" s="1" t="n"/>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>LG-11-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.05519</v>
+      </c>
+      <c r="G88" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="L88" t="n">
+        <v>5.558</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.06026</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.05921</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.1642</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n"/>
+      <c r="B89" s="1" t="n"/>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>LG-11-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3.136</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="G89" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="I89" t="n">
+        <v>4.177</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="L89" t="n">
+        <v>5.997</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.1926</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n"/>
+      <c r="B90" s="1" t="n"/>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>LG-12-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3.349</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.06026</v>
+      </c>
+      <c r="G90" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4.097</v>
+      </c>
+      <c r="I90" t="n">
+        <v>4.192</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="L90" t="n">
+        <v>6.294</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.05157</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.1615</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n"/>
+      <c r="B91" s="1" t="n"/>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>LG-12-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.06231</v>
+      </c>
+      <c r="G91" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4.191</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2.349</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="L91" t="n">
+        <v>6.857</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.04496</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.09797</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.1458</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="n"/>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>LG-13-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.008043</v>
+      </c>
+      <c r="G92" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4.878</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2.494</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1.609</v>
+      </c>
+      <c r="L92" t="n">
+        <v>5.761</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.2128</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n"/>
+      <c r="B93" s="1" t="n"/>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>LG-13-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="G93" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.488</v>
+      </c>
+      <c r="I93" t="n">
+        <v>4.361</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L93" t="n">
+        <v>6.412</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.06673</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.1655</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n"/>
+      <c r="B94" s="1" t="n"/>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>LG-13-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5236</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="G94" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="I94" t="n">
+        <v>4.553</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2.262</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="L94" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.04095</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.09035</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.07837</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.1207</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n"/>
+      <c r="B95" s="1" t="n"/>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>LG-13-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3.394</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.06633</v>
+      </c>
+      <c r="G95" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4.361</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4.616</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2.256</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L95" t="n">
+        <v>7.395</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.09973</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.1293</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n"/>
+      <c r="B96" s="1" t="n"/>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>LG-14-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.02765</v>
+      </c>
+      <c r="G96" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3.145</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5.094</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="L96" t="n">
+        <v>5.496</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.2078</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n"/>
+      <c r="B97" s="1" t="n"/>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>LG-14-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3.726</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="G97" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4.183</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1.392</v>
+      </c>
+      <c r="L97" t="n">
+        <v>9.038</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.05642</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.09624000000000001</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.1956</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n"/>
+      <c r="B98" s="1" t="n"/>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>LG-15-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>5.525</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.004419</v>
+      </c>
+      <c r="G98" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="I98" t="n">
+        <v>5.543</v>
+      </c>
+      <c r="J98" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="L98" t="n">
+        <v>5.788</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.2096</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.1963</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n"/>
+      <c r="B99" s="1" t="n"/>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>LG-15-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>4.044</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.8752</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.03343</v>
+      </c>
+      <c r="G99" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3.887</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1.819</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="L99" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.2179</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.1967</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n"/>
+      <c r="B100" s="1" t="n"/>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>LG-15-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.05922</v>
+      </c>
+      <c r="G100" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="H100" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="I100" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2.353</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="L100" t="n">
+        <v>6.234</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n"/>
+      <c r="B101" s="1" t="n"/>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>LG-15-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3.722</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.04554</v>
+      </c>
+      <c r="G101" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3.548</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="L101" t="n">
+        <v>8.657</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.06505</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.2277</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.2374</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n"/>
+      <c r="B102" s="1" t="n"/>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>LG-16-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8618</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="G102" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3.121</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3.903</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="L102" t="n">
+        <v>8.393000000000001</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.2646</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n"/>
+      <c r="B103" s="1" t="n"/>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>LG-16-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="G103" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.435</v>
+      </c>
+      <c r="I103" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1.458</v>
+      </c>
+      <c r="L103" t="n">
+        <v>9.237</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.05599</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.09891999999999999</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.1844</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n"/>
+      <c r="B104" s="1" t="n"/>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>LG-17-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>5.058</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.004904</v>
+      </c>
+      <c r="G104" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="I104" t="n">
+        <v>5.269</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2.463</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L104" t="n">
+        <v>6.079</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.2028</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n"/>
+      <c r="B105" s="1" t="n"/>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>LG-17-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.7854</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.02972</v>
+      </c>
+      <c r="G105" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="I105" t="n">
+        <v>4.424</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="L105" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.09678</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.2314</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n"/>
+      <c r="B106" s="1" t="n"/>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>LG-17-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4.057</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.007482</v>
+      </c>
+      <c r="G106" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3.436</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1.846</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L106" t="n">
+        <v>6.587</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.06019</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.2357</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n"/>
+      <c r="B107" s="1" t="n"/>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>LG-17-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3.834</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.03788</v>
+      </c>
+      <c r="G107" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3.407</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3.781</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7.078</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.07042</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n"/>
+      <c r="B108" s="1" t="n"/>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>LG-3-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>4.008</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.8508</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="G108" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="I108" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2.771</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1.709</v>
+      </c>
+      <c r="L108" t="n">
+        <v>4.863</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n"/>
+      <c r="B109" s="1" t="n"/>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>LG-4-1-16-2024</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>4.981</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.06689000000000001</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.004775</v>
+      </c>
+      <c r="G109" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6.107</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1.704</v>
+      </c>
+      <c r="L109" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.07063</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.09666</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.1253</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n"/>
+      <c r="B110" s="1" t="n"/>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>LG-4-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>7.516</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.004728</v>
+      </c>
+      <c r="G110" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="I110" t="n">
+        <v>5.662</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.648</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="L110" t="n">
+        <v>4.251</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.08895</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.09549000000000001</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.1577</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n"/>
+      <c r="B111" s="1" t="n"/>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>LG-4-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3.928</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.01867</v>
+      </c>
+      <c r="G111" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3.387</v>
+      </c>
+      <c r="I111" t="n">
+        <v>5.464</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2.316</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="L111" t="n">
+        <v>6.067</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.09704</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.181</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n"/>
+      <c r="B112" s="1" t="n"/>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>LG-4-2-16-2024</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.5876</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="G112" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4.064</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5.858</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2.447</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="L112" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.2158</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.2416</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n"/>
+      <c r="B113" s="1" t="n"/>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>LG-4-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3.417</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="G113" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3.939</v>
+      </c>
+      <c r="I113" t="n">
+        <v>4.996</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.009</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="L113" t="n">
+        <v>7.213</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.09946000000000001</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.2556</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n"/>
+      <c r="B114" s="1" t="n"/>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>LG-4-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3.326</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="G114" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="L114" t="n">
+        <v>5.003</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.2453</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n"/>
+      <c r="B115" s="1" t="n"/>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>LG-5-1-16-2024</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>4.879</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.006472</v>
+      </c>
+      <c r="G115" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.8263</v>
+      </c>
+      <c r="I115" t="n">
+        <v>5.412</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5.907</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.2605</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n"/>
+      <c r="B116" s="1" t="n"/>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>LG-5-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>5.168</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.005762</v>
+      </c>
+      <c r="G116" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5.273</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2.761</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="L116" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.07464</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.07047</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.1511</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n"/>
+      <c r="B117" s="1" t="n"/>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>LG-5-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8505</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.02097</v>
+      </c>
+      <c r="G117" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3.645</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5.234</v>
+      </c>
+      <c r="J117" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1.639</v>
+      </c>
+      <c r="L117" t="n">
+        <v>5.561</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.2196</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n"/>
+      <c r="B118" s="1" t="n"/>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>LG-5-2-16-2024</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.5577</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="G118" t="n">
+        <v>7.952</v>
+      </c>
+      <c r="H118" t="n">
+        <v>7.013</v>
+      </c>
+      <c r="I118" t="n">
+        <v>4.354</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1.489</v>
+      </c>
+      <c r="L118" t="n">
+        <v>5.421</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.4461</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n"/>
+      <c r="B119" s="1" t="n"/>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>LG-5-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>5.049</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.005638</v>
+      </c>
+      <c r="G119" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="I119" t="n">
+        <v>4.945</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="L119" t="n">
+        <v>5.927</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.2595</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n"/>
+      <c r="B120" s="1" t="n"/>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>LG-5-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3.128</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.03949</v>
+      </c>
+      <c r="G120" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4.587</v>
+      </c>
+      <c r="I120" t="n">
+        <v>4.566</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2.468</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="L120" t="n">
+        <v>5.529</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.08975</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.2161</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n"/>
+      <c r="B121" s="1" t="n"/>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>LG-6-1-16-2024</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.006114</v>
+      </c>
+      <c r="G121" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.7934</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L121" t="n">
+        <v>4.801</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.08964</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.1788</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n"/>
+      <c r="B122" s="1" t="n"/>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>LG-6-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3.277</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.03334</v>
+      </c>
+      <c r="G122" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="H122" t="n">
+        <v>3.843</v>
+      </c>
+      <c r="I122" t="n">
+        <v>4.772</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="L122" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.2281</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n"/>
+      <c r="B123" s="1" t="n"/>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>LG-6-2-16-2024</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="G123" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="H123" t="n">
+        <v>5.742</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5.695</v>
+      </c>
+      <c r="J123" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1.819</v>
+      </c>
+      <c r="L123" t="n">
+        <v>5.477</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.1976</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2615</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n"/>
+      <c r="B124" s="1" t="n"/>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>LG-6-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>6.048</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.005982</v>
+      </c>
+      <c r="G124" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5.192</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2.122</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="L124" t="n">
+        <v>7.033</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.2531</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n"/>
+      <c r="B125" s="1" t="n"/>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>LG-6-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.04204</v>
+      </c>
+      <c r="G125" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4.405</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="J125" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="L125" t="n">
+        <v>4.249</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.09351</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n"/>
+      <c r="B126" s="1" t="n"/>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>LG-7-1-16-2024</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>5.215</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.1187</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.005857</v>
+      </c>
+      <c r="G126" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.8280999999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>5.208</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="L126" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.09601999999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.2683</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n"/>
+      <c r="B127" s="1" t="n"/>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>LG-7-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>4.899</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.005617</v>
+      </c>
+      <c r="G127" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="I127" t="n">
+        <v>4.958</v>
+      </c>
+      <c r="J127" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="L127" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.09816999999999999</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.2356</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n"/>
+      <c r="B128" s="1" t="n"/>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>LG-7-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3.092</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="G128" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.182</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5.095</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2.569</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4.773</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n"/>
+      <c r="B129" s="1" t="n"/>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>LG-7-2-16-2024</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>3.053</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.7719</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H129" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="I129" t="n">
+        <v>5.114</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.468</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.05365</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.07344000000000001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.1227</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n"/>
+      <c r="B130" s="1" t="n"/>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>LG-7-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.6593</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.02688</v>
+      </c>
+      <c r="G130" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="H130" t="n">
+        <v>5.385</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1.702</v>
+      </c>
+      <c r="L130" t="n">
+        <v>6.031</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.09941999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2496</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n"/>
+      <c r="B131" s="1" t="n"/>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>LG-7-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="G131" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="I131" t="n">
+        <v>4.274</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4.856</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.05949</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.06022</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.1169</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.1526</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n"/>
+      <c r="B132" s="1" t="n"/>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>LG-8-1-16-2024</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.005433</v>
+      </c>
+      <c r="G132" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="I132" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.224</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="L132" t="n">
+        <v>6.368</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.2606</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n"/>
+      <c r="B133" s="1" t="n"/>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>LG-8-1-17-2024</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>4.722</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.006029</v>
+      </c>
+      <c r="G133" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="I133" t="n">
+        <v>4.688</v>
+      </c>
+      <c r="J133" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="L133" t="n">
+        <v>2.736</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.09868</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.2432</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n"/>
+      <c r="B134" s="1" t="n"/>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>LG-8-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2.953</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.04272</v>
+      </c>
+      <c r="G134" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="H134" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="I134" t="n">
+        <v>4.794</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="L134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.07743999999999999</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.2239</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n"/>
+      <c r="B135" s="1" t="n"/>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>LG-8-2-16-2024</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2.994</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6889</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="G135" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="H135" t="n">
+        <v>5.712</v>
+      </c>
+      <c r="I135" t="n">
+        <v>5.419</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2.523</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L135" t="n">
+        <v>5.101</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.2349</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.2087</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.2602</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n"/>
+      <c r="B136" s="1" t="n"/>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>LG-8-2-17-2024</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.007592</v>
+      </c>
+      <c r="G136" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="I136" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2.637</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4.487</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.08495</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.2175</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n"/>
+      <c r="B137" s="1" t="n"/>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>LG-8-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="G137" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="H137" t="n">
+        <v>4.663</v>
+      </c>
+      <c r="I137" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="L137" t="n">
+        <v>7.038</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.06751</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2401</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n"/>
+      <c r="B138" s="1" t="n"/>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>LG-9-1-30-2024</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.03873</v>
+      </c>
+      <c r="G138" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3.918</v>
+      </c>
+      <c r="I138" t="n">
+        <v>4.327</v>
+      </c>
+      <c r="J138" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="L138" t="n">
+        <v>5.591</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.09265</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.2572</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n"/>
+      <c r="B139" s="1" t="n"/>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>LG-9-2-30-2024</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.04929</v>
+      </c>
+      <c r="G139" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4.637</v>
+      </c>
+      <c r="I139" t="n">
+        <v>4.046</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="L139" t="n">
+        <v>6.559</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.06923</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.2302</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n"/>
+      <c r="B140" s="1" t="n"/>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>LG-LST-30-2024</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.007342</v>
+      </c>
+      <c r="G140" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="I140" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="J140" t="n">
+        <v>4.827</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2.221</v>
+      </c>
+      <c r="L140" t="n">
+        <v>5.282</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.07496999999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n"/>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>Lst</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>LST-L-SPB wosalt-2024</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.005158</v>
+      </c>
+      <c r="G141" t="n">
+        <v>3.744</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4.061</v>
+      </c>
+      <c r="I141" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="J141" t="n">
+        <v>5.092</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L141" t="n">
+        <v>4.022</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.005862</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.03033</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n"/>
+      <c r="B142" s="1" t="n"/>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>LST-L-Syas wosalt-2024</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>6.937</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.2413</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.008756999999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4.845</v>
+      </c>
+      <c r="H142" t="n">
+        <v>4.981</v>
+      </c>
+      <c r="I142" t="n">
+        <v>6.302</v>
+      </c>
+      <c r="J142" t="n">
+        <v>3.397</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L142" t="n">
+        <v>4.063</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.1458</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n"/>
+      <c r="B143" s="1" t="n"/>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>LST-L-VLK wosalt-2024</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.003376</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4.678</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3.809</v>
+      </c>
+      <c r="I143" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="J143" t="n">
+        <v>5.113</v>
+      </c>
+      <c r="K143" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L143" t="n">
+        <v>4.015</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.04277</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n"/>
+      <c r="B144" s="1" t="n"/>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>LST-Perm-2024</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>9.382</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.006164</v>
+      </c>
+      <c r="G144" t="n">
+        <v>8.936999999999999</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="I144" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="J144" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="L144" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.02709</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.02837</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n"/>
+      <c r="B145" s="1" t="n"/>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>LST-S-SBP-2024</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.00363</v>
+      </c>
+      <c r="G145" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="I145" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="J145" t="n">
+        <v>5.513</v>
+      </c>
+      <c r="K145" t="n">
+        <v>3.185</v>
+      </c>
+      <c r="L145" t="n">
+        <v>3.282</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.6964</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n"/>
+      <c r="B146" s="1" t="n"/>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>LST-S-SOKOL-2024</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>8.752000000000001</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.07364</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.003127</v>
+      </c>
+      <c r="G146" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="I146" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="J146" t="n">
+        <v>5.234</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2.909</v>
+      </c>
+      <c r="L146" t="n">
+        <v>3.448</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.6268</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n"/>
+      <c r="B147" s="1" t="n"/>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>LST-S-SYAS-2024</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>6.195</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.06691999999999999</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.003871</v>
+      </c>
+      <c r="G147" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="I147" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="L147" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n"/>
+      <c r="B148" s="1" t="n"/>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>LST-S-VLK-2024</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="G148" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="I148" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4.664</v>
+      </c>
+      <c r="K148" t="n">
+        <v>2.772</v>
+      </c>
+      <c r="L148" t="n">
+        <v>4.541</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0.04429</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n"/>
+      <c r="B149" s="1" t="n"/>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>LST-Spb-2024</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.002694</v>
+      </c>
+      <c r="G149" t="n">
+        <v>7.756</v>
+      </c>
+      <c r="H149" t="n">
+        <v>7.453</v>
+      </c>
+      <c r="I149" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5.104</v>
+      </c>
+      <c r="K149" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="L149" t="n">
+        <v>4.822</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.05239</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n"/>
+      <c r="B150" s="1" t="n"/>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>LST-Syas-2024</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.01031</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7.879</v>
+      </c>
+      <c r="H150" t="n">
+        <v>9.010999999999999</v>
+      </c>
+      <c r="I150" t="n">
+        <v>8.718999999999999</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3.348</v>
+      </c>
+      <c r="K150" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="L150" t="n">
+        <v>4.842</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.06468</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.06106</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0.05925</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0.04836</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n"/>
+      <c r="B151" s="1" t="n"/>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>LST-Vlk-2024</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.005551</v>
+      </c>
+      <c r="G151" t="n">
+        <v>7.527</v>
+      </c>
+      <c r="H151" t="n">
+        <v>6.055</v>
+      </c>
+      <c r="I151" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="J151" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="K151" t="n">
+        <v>3.166</v>
+      </c>
+      <c r="L151" t="n">
+        <v>7.112</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0.09801</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0.0003387</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>Peat</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>PFA</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>PFA-Sk3-00-2024</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.01813</v>
+      </c>
+      <c r="G152" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="I152" t="n">
+        <v>3.456</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="L152" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0.5018</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n"/>
+      <c r="B153" s="1" t="n"/>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>PFA-T1098-2024</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>3.984</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="G153" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2.189</v>
+      </c>
+      <c r="I153" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="L153" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.04987</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0.5279</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n"/>
+      <c r="B154" s="1" t="n"/>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>PFA-T598-2024</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>3.862</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="G154" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I154" t="n">
+        <v>3.326</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="L154" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0.6487000000000001</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0.3899</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n"/>
+      <c r="B155" s="1" t="n"/>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>PFA-T5H98-2024</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>3.806</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="G155" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="I155" t="n">
+        <v>3.566</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="L155" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0.6773</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0.3447</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n"/>
+      <c r="B156" s="1" t="n"/>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>PFA-T698-2024</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>3.612</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="G156" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I156" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L156" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0.5536</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.03096</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0.3059</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n"/>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>PHA</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>PHA-Sk3-00-2024</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2.921</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.02443</v>
+      </c>
+      <c r="G157" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="I157" t="n">
+        <v>2.398</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="L157" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.008383</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0.1763</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n"/>
+      <c r="B158" s="1" t="n"/>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>PHA-T598-2024</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2.633</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.6589</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.06308</v>
+      </c>
+      <c r="G158" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3.702</v>
+      </c>
+      <c r="I158" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.8227</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="L158" t="n">
+        <v>6.519</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.01172</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0.08062</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0.1564</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n"/>
+      <c r="B159" s="1" t="n"/>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>PHA-T698-2024</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2.437</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.07134</v>
+      </c>
+      <c r="G159" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2.827</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.7543</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.9704</v>
+      </c>
+      <c r="L159" t="n">
+        <v>8.807</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.02074</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.1498</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n"/>
+      <c r="B160" s="1" t="n"/>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>PHA-TTL98-2024</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.7224</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.06916</v>
+      </c>
+      <c r="G160" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="H160" t="n">
+        <v>3.932</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2.009</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="L160" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.01211</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.02291</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.1834</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n"/>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>PHF</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>PHF-Sk300-2024</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2.988</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.8065</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.06529</v>
+      </c>
+      <c r="G161" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="H161" t="n">
+        <v>4.665</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2.161</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="L161" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.01136</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.3162</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n"/>
+      <c r="B162" s="1" t="n"/>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>PHF-T10L98-2024</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>3.044</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.03023</v>
+      </c>
+      <c r="G162" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2.436</v>
+      </c>
+      <c r="I162" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="L162" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0.008867999999999999</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.2005</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n"/>
+      <c r="B163" s="1" t="n"/>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>PHF-T698-2024</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.05425</v>
+      </c>
+      <c r="G163" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H163" t="n">
+        <v>3.493</v>
+      </c>
+      <c r="I163" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="L163" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.006822</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.1262</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n"/>
+      <c r="B164" s="1" t="n"/>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>PHF-T7H98-2024</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="G164" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="L164" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0.01158</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0.1782</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n"/>
+      <c r="B165" s="1" t="n"/>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>PHF-TTL98-2024</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.6227</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="G165" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4.023</v>
+      </c>
+      <c r="I165" t="n">
+        <v>2.364</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="L165" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.007385</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.01448</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.2255</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>SFA</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>SFA-PW04-2024</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>3.653</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="G166" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="I166" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="L166" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0.4105</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n"/>
+      <c r="B167" s="1" t="n"/>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>SFA-PW16-2024</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>4.404</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="G167" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="H167" t="n">
+        <v>2.966</v>
+      </c>
+      <c r="I167" t="n">
+        <v>3.266</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="L167" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.03856</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0.5037</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n"/>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>SHA</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>SHA-CtK04-2024</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.07627</v>
+      </c>
+      <c r="G168" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="H168" t="n">
+        <v>4.281</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="L168" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.007764</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.01517</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n"/>
+      <c r="B169" s="1" t="n"/>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>SHA-CtK15-2024</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="G169" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="H169" t="n">
+        <v>5.904</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.9705</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="L169" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.8178</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n"/>
+      <c r="B170" s="1" t="n"/>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>SHA-CtV98-2024</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.03995</v>
+      </c>
+      <c r="G170" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="H170" t="n">
+        <v>2.891</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="L170" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0.01096</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0.3621</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n"/>
+      <c r="B171" s="1" t="n"/>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>SHA-PW04-2024</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2.713</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="G171" t="n">
+        <v>5.504</v>
+      </c>
+      <c r="H171" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2.166</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.8058999999999999</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="L171" t="n">
+        <v>7.659</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.005618</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0.03432</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.009009</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.07371</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n"/>
+      <c r="B172" s="1" t="n"/>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>SHA-PW16-2024</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.6297</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.07641000000000001</v>
+      </c>
+      <c r="G172" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="H172" t="n">
+        <v>4.232</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.6784</v>
+      </c>
+      <c r="L172" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.009627</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0.7187</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n"/>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>SHF</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>SHF-CmK98-2024</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2.178</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.03157</v>
+      </c>
+      <c r="G173" t="n">
+        <v>3.479</v>
+      </c>
+      <c r="H173" t="n">
+        <v>5.258</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0.9616</v>
+      </c>
+      <c r="L173" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0.006766</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0.2692</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n"/>
+      <c r="B174" s="1" t="n"/>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>SHF-CtL00-2024</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2.991</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.03917</v>
+      </c>
+      <c r="G174" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L174" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0.008279</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.2328</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n"/>
+      <c r="B175" s="1" t="n"/>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>SHF-Ctv98-2024</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="G175" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="L175" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0.005621</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.1932</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0.01346</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.4354</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n"/>
+      <c r="B176" s="1" t="n"/>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>SHF-PW04-2024</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>3.382</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="G176" t="n">
+        <v>4.598</v>
+      </c>
+      <c r="H176" t="n">
+        <v>4.505</v>
+      </c>
+      <c r="I176" t="n">
+        <v>3.081</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="L176" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0.007718</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0.01447</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0.2081</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="B57:B69"/>
-    <mergeCell ref="B9:B18"/>
-    <mergeCell ref="B26:B40"/>
-    <mergeCell ref="B2:B8"/>
-    <mergeCell ref="A2:A69"/>
-    <mergeCell ref="B41:B56"/>
+  <mergeCells count="20">
+    <mergeCell ref="B31:B45"/>
+    <mergeCell ref="A82:A151"/>
+    <mergeCell ref="B11:B21"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="B168:B172"/>
+    <mergeCell ref="A152:A165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="B157:B160"/>
+    <mergeCell ref="B46:B64"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B82:B140"/>
+    <mergeCell ref="B65:B77"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="B141:B151"/>
+    <mergeCell ref="B161:B165"/>
+    <mergeCell ref="B152:B156"/>
+    <mergeCell ref="A2:A77"/>
+    <mergeCell ref="B173:B176"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="A166:A176"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
+++ b/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P176"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.922</v>
+        <v>3.921</v>
       </c>
       <c r="E2" t="n">
         <v>0.1769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01005</v>
+        <v>116.4</v>
       </c>
       <c r="G2" t="n">
         <v>10.4</v>
@@ -602,7 +602,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04829</v>
+        <v>90.3</v>
       </c>
       <c r="G3" t="n">
         <v>31.55</v>
@@ -650,7 +650,7 @@
         <v>1.004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0518</v>
+        <v>95.12</v>
       </c>
       <c r="G4" t="n">
         <v>22.91</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.372</v>
+        <v>3.371</v>
       </c>
       <c r="E5" t="n">
         <v>0.1735</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01093</v>
+        <v>121.7</v>
       </c>
       <c r="G5" t="n">
         <v>9.712999999999999</v>
@@ -746,7 +746,7 @@
         <v>0.986</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05506</v>
+        <v>95.16</v>
       </c>
       <c r="G6" t="n">
         <v>25.23</v>
@@ -794,7 +794,7 @@
         <v>0.434</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03056</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
         <v>16.21</v>
@@ -842,7 +842,7 @@
         <v>0.4637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02791</v>
+        <v>108.6</v>
       </c>
       <c r="G8" t="n">
         <v>17.72</v>
@@ -890,7 +890,7 @@
         <v>0.3628</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01928</v>
+        <v>104.5</v>
       </c>
       <c r="G9" t="n">
         <v>13.71</v>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.848</v>
+        <v>3.847</v>
       </c>
       <c r="E10" t="n">
         <v>0.2344</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01323</v>
+        <v>110.9</v>
       </c>
       <c r="G10" t="n">
         <v>11.77</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.537</v>
+        <v>4.535</v>
       </c>
       <c r="E11" t="n">
         <v>0.1088</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005446</v>
+        <v>136.3</v>
       </c>
       <c r="G11" t="n">
         <v>1.633</v>
@@ -1038,7 +1038,7 @@
         <v>0.1728</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01178</v>
+        <v>146.9</v>
       </c>
       <c r="G12" t="n">
         <v>9.173999999999999</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.054</v>
+        <v>4.053</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3601</v>
+        <v>0.3602</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01602</v>
+        <v>98.88</v>
       </c>
       <c r="G13" t="n">
         <v>12.74</v>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.966</v>
+        <v>3.965</v>
       </c>
       <c r="E14" t="n">
         <v>0.1489</v>
       </c>
       <c r="F14" t="n">
-        <v>0.007368</v>
+        <v>122.2</v>
       </c>
       <c r="G14" t="n">
         <v>5.964</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.771</v>
+        <v>4.769</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1103</v>
+        <v>0.1104</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005521</v>
+        <v>129</v>
       </c>
       <c r="G15" t="n">
         <v>2.368</v>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.777</v>
+        <v>4.776</v>
       </c>
       <c r="E16" t="n">
         <v>0.1416</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00509</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>2.572</v>
@@ -1275,10 +1275,10 @@
         <v>3.559</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5507</v>
+        <v>0.5508</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02879</v>
+        <v>94.58</v>
       </c>
       <c r="G17" t="n">
         <v>3.152</v>
@@ -1326,7 +1326,7 @@
         <v>0.1908</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008776000000000001</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>4.184</v>
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4.854</v>
+        <v>4.852</v>
       </c>
       <c r="E19" t="n">
         <v>0.1298</v>
       </c>
       <c r="F19" t="n">
-        <v>0.006544</v>
+        <v>125.8</v>
       </c>
       <c r="G19" t="n">
         <v>23.88</v>
@@ -1422,7 +1422,7 @@
         <v>0.857</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0529</v>
+        <v>109.6</v>
       </c>
       <c r="G20" t="n">
         <v>14.26</v>
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3.75</v>
+        <v>3.749</v>
       </c>
       <c r="E21" t="n">
         <v>0.5012</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02775</v>
+        <v>114.5</v>
       </c>
       <c r="G21" t="n">
         <v>14.13</v>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.64</v>
+        <v>5.638</v>
       </c>
       <c r="E22" t="n">
         <v>0.1188</v>
       </c>
       <c r="F22" t="n">
-        <v>0.003223</v>
+        <v>86.27</v>
       </c>
       <c r="G22" t="n">
         <v>1.42</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.922</v>
+        <v>4.92</v>
       </c>
       <c r="E23" t="n">
         <v>0.116</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003935</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>1.337</v>
       </c>
       <c r="H23" t="n">
-        <v>8.677</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>4.887</v>
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5.319</v>
+        <v>5.317</v>
       </c>
       <c r="E24" t="n">
         <v>0.102</v>
       </c>
       <c r="F24" t="n">
-        <v>0.003855</v>
+        <v>94.91</v>
       </c>
       <c r="G24" t="n">
         <v>1.963</v>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.524</v>
+        <v>4.522</v>
       </c>
       <c r="E25" t="n">
         <v>0.1044</v>
       </c>
       <c r="F25" t="n">
-        <v>0.004531</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>2.861</v>
@@ -1708,19 +1708,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4.98</v>
+        <v>4.978</v>
       </c>
       <c r="E26" t="n">
         <v>0.1081</v>
       </c>
       <c r="F26" t="n">
-        <v>0.003274</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>4.152</v>
       </c>
       <c r="H26" t="n">
-        <v>2.604</v>
+        <v>2.605</v>
       </c>
       <c r="I26" t="n">
         <v>4.957</v>
@@ -1756,13 +1756,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5.039</v>
+        <v>5.038</v>
       </c>
       <c r="E27" t="n">
         <v>0.1532</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00374</v>
+        <v>77.37</v>
       </c>
       <c r="G27" t="n">
         <v>13.17</v>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.656</v>
+        <v>6.652</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09919</v>
+        <v>0.0992</v>
       </c>
       <c r="F28" t="n">
-        <v>0.00253</v>
+        <v>84.53</v>
       </c>
       <c r="G28" t="n">
         <v>3.639</v>
@@ -1852,19 +1852,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.047</v>
+        <v>6.044</v>
       </c>
       <c r="E29" t="n">
         <v>0.1131</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003446</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>3.263</v>
       </c>
       <c r="H29" t="n">
-        <v>3.466</v>
+        <v>3.467</v>
       </c>
       <c r="I29" t="n">
         <v>4.038</v>
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5.71</v>
+        <v>5.707</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09626999999999999</v>
+        <v>0.09628</v>
       </c>
       <c r="F30" t="n">
-        <v>0.002824</v>
+        <v>85.89</v>
       </c>
       <c r="G30" t="n">
         <v>3.979</v>
@@ -1952,19 +1952,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.708</v>
+        <v>5.705</v>
       </c>
       <c r="E31" t="n">
         <v>0.1181</v>
       </c>
       <c r="F31" t="n">
-        <v>0.003114</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>9.333</v>
       </c>
       <c r="H31" t="n">
-        <v>1.265</v>
+        <v>1.266</v>
       </c>
       <c r="I31" t="n">
         <v>4.871</v>
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.616</v>
+        <v>4.615</v>
       </c>
       <c r="E32" t="n">
         <v>0.3344</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0107</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>25.65</v>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.597</v>
+        <v>4.596</v>
       </c>
       <c r="E33" t="n">
         <v>0.3808</v>
       </c>
       <c r="F33" t="n">
-        <v>0.009214999999999999</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>22.14</v>
@@ -2096,13 +2096,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.3</v>
+        <v>5.299</v>
       </c>
       <c r="E34" t="n">
         <v>0.3655</v>
       </c>
       <c r="F34" t="n">
-        <v>0.008168999999999999</v>
+        <v>78.83</v>
       </c>
       <c r="G34" t="n">
         <v>22.78</v>
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.702</v>
+        <v>4.701</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3236</v>
+        <v>0.3237</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01274</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>26.39</v>
@@ -2192,13 +2192,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5.679</v>
+        <v>5.677</v>
       </c>
       <c r="E36" t="n">
         <v>0.1528</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00409</v>
+        <v>87.69</v>
       </c>
       <c r="G36" t="n">
         <v>11.99</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.507</v>
+        <v>5.505</v>
       </c>
       <c r="E37" t="n">
         <v>0.1713</v>
       </c>
       <c r="F37" t="n">
-        <v>0.003964</v>
+        <v>79.47</v>
       </c>
       <c r="G37" t="n">
         <v>12.19</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.868</v>
+        <v>5.866</v>
       </c>
       <c r="E38" t="n">
         <v>0.1135</v>
       </c>
       <c r="F38" t="n">
-        <v>0.003273</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>9.198</v>
@@ -2336,13 +2336,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.709</v>
+        <v>5.706</v>
       </c>
       <c r="E39" t="n">
         <v>0.1272</v>
       </c>
       <c r="F39" t="n">
-        <v>0.003229</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>9.935</v>
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.406</v>
+        <v>5.404</v>
       </c>
       <c r="E40" t="n">
         <v>0.1856</v>
       </c>
       <c r="F40" t="n">
-        <v>0.004595</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G40" t="n">
         <v>12.02</v>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5.546</v>
+        <v>5.544</v>
       </c>
       <c r="E41" t="n">
         <v>0.1804</v>
       </c>
       <c r="F41" t="n">
-        <v>0.004438</v>
+        <v>85.17</v>
       </c>
       <c r="G41" t="n">
         <v>13.1</v>
@@ -2480,13 +2480,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.912</v>
+        <v>4.911</v>
       </c>
       <c r="E42" t="n">
         <v>0.243</v>
       </c>
       <c r="F42" t="n">
-        <v>0.009627</v>
+        <v>89.36</v>
       </c>
       <c r="G42" t="n">
         <v>13.3</v>
@@ -2528,13 +2528,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.154</v>
+        <v>5.153</v>
       </c>
       <c r="E43" t="n">
         <v>0.2727</v>
       </c>
       <c r="F43" t="n">
-        <v>0.007115</v>
+        <v>77.94</v>
       </c>
       <c r="G43" t="n">
         <v>18.97</v>
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.496</v>
+        <v>5.495</v>
       </c>
       <c r="E44" t="n">
         <v>0.3718</v>
       </c>
       <c r="F44" t="n">
-        <v>0.009441</v>
+        <v>75.53</v>
       </c>
       <c r="G44" t="n">
         <v>30.88</v>
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5.22</v>
+        <v>5.218</v>
       </c>
       <c r="E45" t="n">
         <v>0.1729</v>
       </c>
       <c r="F45" t="n">
-        <v>0.004236</v>
+        <v>80.28</v>
       </c>
       <c r="G45" t="n">
         <v>13.81</v>
@@ -2676,19 +2676,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.75</v>
+        <v>4.734</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01265</v>
+        <v>0.01266</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0005391</v>
+        <v>105.3</v>
       </c>
       <c r="G46" t="n">
         <v>8.269</v>
       </c>
       <c r="H46" t="n">
-        <v>0.153</v>
+        <v>0.1531</v>
       </c>
       <c r="I46" t="n">
         <v>5.017</v>
@@ -2730,7 +2730,7 @@
         <v>0.3426</v>
       </c>
       <c r="F47" t="n">
-        <v>0.01535</v>
+        <v>129.1</v>
       </c>
       <c r="G47" t="n">
         <v>16.81</v>
@@ -2778,7 +2778,7 @@
         <v>0.3991</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02143</v>
+        <v>126.4</v>
       </c>
       <c r="G48" t="n">
         <v>26.7</v>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.22</v>
+        <v>4.219</v>
       </c>
       <c r="E49" t="n">
         <v>0.1573</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01275</v>
+        <v>163.4</v>
       </c>
       <c r="G49" t="n">
         <v>10.86</v>
@@ -2868,13 +2868,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4.055</v>
+        <v>4.054</v>
       </c>
       <c r="E50" t="n">
         <v>0.1936</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01388</v>
+        <v>143.3</v>
       </c>
       <c r="G50" t="n">
         <v>14.61</v>
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.136</v>
+        <v>4.135</v>
       </c>
       <c r="E51" t="n">
         <v>0.1835</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01357</v>
+        <v>145.5</v>
       </c>
       <c r="G51" t="n">
         <v>15.56</v>
@@ -2970,7 +2970,7 @@
         <v>0.2105</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01731</v>
+        <v>132.2</v>
       </c>
       <c r="G52" t="n">
         <v>17.32</v>
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.344</v>
+        <v>4.343</v>
       </c>
       <c r="E53" t="n">
         <v>0.163</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01298</v>
+        <v>168.7</v>
       </c>
       <c r="G53" t="n">
         <v>9.82</v>
@@ -3060,13 +3060,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.425</v>
+        <v>4.423</v>
       </c>
       <c r="E54" t="n">
         <v>0.134</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01029</v>
+        <v>162</v>
       </c>
       <c r="G54" t="n">
         <v>8.194000000000001</v>
@@ -3108,19 +3108,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5.382</v>
+        <v>5.361</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0131</v>
+        <v>0.01311</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0003527</v>
+        <v>92.19</v>
       </c>
       <c r="G55" t="n">
         <v>8.269</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1585</v>
+        <v>0.1586</v>
       </c>
       <c r="I55" t="n">
         <v>5.015</v>
@@ -3156,13 +3156,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.108</v>
+        <v>4.107</v>
       </c>
       <c r="E56" t="n">
         <v>0.1116</v>
       </c>
       <c r="F56" t="n">
-        <v>0.009842</v>
+        <v>178.4</v>
       </c>
       <c r="G56" t="n">
         <v>8.194000000000001</v>
@@ -3204,13 +3204,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.67</v>
+        <v>4.669</v>
       </c>
       <c r="E57" t="n">
         <v>0.1906</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01357</v>
+        <v>166.4</v>
       </c>
       <c r="G57" t="n">
         <v>13.03</v>
@@ -3252,19 +3252,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5.398</v>
+        <v>5.377</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01318</v>
+        <v>0.01319</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0003946</v>
+        <v>101.1</v>
       </c>
       <c r="G58" t="n">
         <v>9.866</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1336</v>
+        <v>0.1337</v>
       </c>
       <c r="I58" t="n">
         <v>5.044</v>
@@ -3306,7 +3306,7 @@
         <v>0.266</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01664</v>
+        <v>134.6</v>
       </c>
       <c r="G59" t="n">
         <v>14.82</v>
@@ -3354,7 +3354,7 @@
         <v>0.2382</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01646</v>
+        <v>125</v>
       </c>
       <c r="G60" t="n">
         <v>12.15</v>
@@ -3402,7 +3402,7 @@
         <v>0.2284</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01857</v>
+        <v>142.8</v>
       </c>
       <c r="G61" t="n">
         <v>14.83</v>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.552</v>
+        <v>4.551</v>
       </c>
       <c r="E62" t="n">
         <v>0.1868</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01116</v>
+        <v>137</v>
       </c>
       <c r="G62" t="n">
         <v>14.98</v>
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4.811</v>
+        <v>4.81</v>
       </c>
       <c r="E63" t="n">
         <v>0.2211</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01195</v>
+        <v>139.3</v>
       </c>
       <c r="G63" t="n">
         <v>13.24</v>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4.372</v>
+        <v>4.371</v>
       </c>
       <c r="E64" t="n">
         <v>0.2564</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01579</v>
+        <v>136.5</v>
       </c>
       <c r="G64" t="n">
         <v>14.38</v>
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5.803</v>
+        <v>5.8</v>
       </c>
       <c r="E65" t="n">
         <v>0.1193</v>
       </c>
       <c r="F65" t="n">
-        <v>0.004075</v>
+        <v>90.19</v>
       </c>
       <c r="G65" t="n">
         <v>11.87</v>
@@ -3640,19 +3640,19 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.74</v>
+        <v>1.739</v>
       </c>
       <c r="E66" t="n">
-        <v>0.02372</v>
+        <v>0.02373</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01126</v>
+        <v>213.5</v>
       </c>
       <c r="G66" t="n">
         <v>10.67</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2223</v>
+        <v>0.2224</v>
       </c>
       <c r="I66" t="n">
         <v>4.488</v>
@@ -3688,13 +3688,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5.391</v>
+        <v>5.389</v>
       </c>
       <c r="E67" t="n">
         <v>0.114</v>
       </c>
       <c r="F67" t="n">
-        <v>0.004794</v>
+        <v>98.52</v>
       </c>
       <c r="G67" t="n">
         <v>10.42</v>
@@ -3736,13 +3736,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5.426</v>
+        <v>5.424</v>
       </c>
       <c r="E68" t="n">
         <v>0.1271</v>
       </c>
       <c r="F68" t="n">
-        <v>0.004576</v>
+        <v>86.84</v>
       </c>
       <c r="G68" t="n">
         <v>9.82</v>
@@ -3784,19 +3784,19 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5.882</v>
+        <v>5.879</v>
       </c>
       <c r="E69" t="n">
         <v>0.1097</v>
       </c>
       <c r="F69" t="n">
-        <v>0.003406</v>
+        <v>88.66</v>
       </c>
       <c r="G69" t="n">
         <v>8.726000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>1.257</v>
+        <v>1.258</v>
       </c>
       <c r="I69" t="n">
         <v>5.151</v>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6.062</v>
+        <v>6.059</v>
       </c>
       <c r="E70" t="n">
         <v>0.1209</v>
       </c>
       <c r="F70" t="n">
-        <v>0.004467</v>
+        <v>94.37</v>
       </c>
       <c r="G70" t="n">
         <v>11.14</v>
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6.29</v>
+        <v>6.287</v>
       </c>
       <c r="E71" t="n">
-        <v>0.09873</v>
+        <v>0.09873999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>0.002933</v>
+        <v>92.2</v>
       </c>
       <c r="G71" t="n">
         <v>9.343999999999999</v>
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6.529</v>
+        <v>6.524</v>
       </c>
       <c r="E72" t="n">
-        <v>0.09402000000000001</v>
+        <v>0.09403</v>
       </c>
       <c r="F72" t="n">
-        <v>0.003077</v>
+        <v>90.37</v>
       </c>
       <c r="G72" t="n">
         <v>10.34</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9093</v>
+        <v>0.9094</v>
       </c>
       <c r="I72" t="n">
         <v>4.851</v>
@@ -3976,13 +3976,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5.4</v>
+        <v>5.398</v>
       </c>
       <c r="E73" t="n">
         <v>0.1671</v>
       </c>
       <c r="F73" t="n">
-        <v>0.005082</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="G73" t="n">
         <v>16.6</v>
@@ -4024,19 +4024,19 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.513</v>
+        <v>4.511</v>
       </c>
       <c r="E74" t="n">
         <v>0.155</v>
       </c>
       <c r="F74" t="n">
-        <v>0.006872</v>
+        <v>85.52</v>
       </c>
       <c r="G74" t="n">
         <v>15.6</v>
       </c>
       <c r="H74" t="n">
-        <v>0.9935</v>
+        <v>0.9936</v>
       </c>
       <c r="I74" t="n">
         <v>4.498</v>
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4.642</v>
+        <v>4.641</v>
       </c>
       <c r="E75" t="n">
         <v>0.2627</v>
       </c>
       <c r="F75" t="n">
-        <v>0.007806</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="G75" t="n">
         <v>17.99</v>
@@ -4120,19 +4120,19 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.927</v>
+        <v>1.926</v>
       </c>
       <c r="E76" t="n">
-        <v>0.02968</v>
+        <v>0.02969</v>
       </c>
       <c r="F76" t="n">
-        <v>0.01141</v>
+        <v>190.9</v>
       </c>
       <c r="G76" t="n">
         <v>17.6</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1686</v>
+        <v>0.1687</v>
       </c>
       <c r="I76" t="n">
         <v>4.798</v>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4.883</v>
+        <v>4.882</v>
       </c>
       <c r="E77" t="n">
         <v>0.1624</v>
       </c>
       <c r="F77" t="n">
-        <v>0.007055</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="G77" t="n">
         <v>17.91</v>
@@ -4230,7 +4230,7 @@
         <v>1.308</v>
       </c>
       <c r="F78" t="n">
-        <v>0.153</v>
+        <v>94.66</v>
       </c>
       <c r="G78" t="n">
         <v>26.12</v>
@@ -4282,7 +4282,7 @@
         <v>1.033</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1178</v>
+        <v>99.09</v>
       </c>
       <c r="G79" t="n">
         <v>24.06</v>
@@ -4330,7 +4330,7 @@
         <v>1.308</v>
       </c>
       <c r="F80" t="n">
-        <v>0.153</v>
+        <v>94.66</v>
       </c>
       <c r="G80" t="n">
         <v>20.3</v>
@@ -4378,7 +4378,7 @@
         <v>0.8376</v>
       </c>
       <c r="F81" t="n">
-        <v>0.07933</v>
+        <v>94.48</v>
       </c>
       <c r="G81" t="n">
         <v>22.4</v>
@@ -4428,19 +4428,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2.458</v>
+        <v>2.456</v>
       </c>
       <c r="E82" t="n">
-        <v>0.02545</v>
+        <v>0.02546</v>
       </c>
       <c r="F82" t="n">
-        <v>0.002724</v>
+        <v>198.6</v>
       </c>
       <c r="G82" t="n">
         <v>13.36</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1905</v>
+        <v>0.1906</v>
       </c>
       <c r="I82" t="n">
         <v>4.162</v>
@@ -4476,13 +4476,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4.37</v>
+        <v>4.369</v>
       </c>
       <c r="E83" t="n">
         <v>0.1263</v>
       </c>
       <c r="F83" t="n">
-        <v>0.007274</v>
+        <v>123</v>
       </c>
       <c r="G83" t="n">
         <v>12.5</v>
@@ -4530,7 +4530,7 @@
         <v>1.11</v>
       </c>
       <c r="F84" t="n">
-        <v>0.04909</v>
+        <v>86.25</v>
       </c>
       <c r="G84" t="n">
         <v>23.87</v>
@@ -4578,7 +4578,7 @@
         <v>1.181</v>
       </c>
       <c r="F85" t="n">
-        <v>0.04732</v>
+        <v>80.86</v>
       </c>
       <c r="G85" t="n">
         <v>9.41</v>
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5.171</v>
+        <v>5.17</v>
       </c>
       <c r="E86" t="n">
         <v>0.1991</v>
       </c>
       <c r="F86" t="n">
-        <v>0.007901999999999999</v>
+        <v>108.1</v>
       </c>
       <c r="G86" t="n">
         <v>12.07</v>
@@ -4674,7 +4674,7 @@
         <v>1.088</v>
       </c>
       <c r="F87" t="n">
-        <v>0.05234</v>
+        <v>86.98</v>
       </c>
       <c r="G87" t="n">
         <v>23.78</v>
@@ -4722,7 +4722,7 @@
         <v>1.088</v>
       </c>
       <c r="F88" t="n">
-        <v>0.05519</v>
+        <v>87.83</v>
       </c>
       <c r="G88" t="n">
         <v>24.34</v>
@@ -4770,13 +4770,13 @@
         <v>1.113</v>
       </c>
       <c r="F89" t="n">
-        <v>0.05846</v>
+        <v>89.88</v>
       </c>
       <c r="G89" t="n">
         <v>23.1</v>
       </c>
       <c r="H89" t="n">
-        <v>4.818</v>
+        <v>4.819</v>
       </c>
       <c r="I89" t="n">
         <v>4.177</v>
@@ -4818,7 +4818,7 @@
         <v>1.086</v>
       </c>
       <c r="F90" t="n">
-        <v>0.06026</v>
+        <v>86.25</v>
       </c>
       <c r="G90" t="n">
         <v>26.5</v>
@@ -4866,7 +4866,7 @@
         <v>1.071</v>
       </c>
       <c r="F91" t="n">
-        <v>0.06231</v>
+        <v>85.88</v>
       </c>
       <c r="G91" t="n">
         <v>23.58</v>
@@ -4908,19 +4908,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4.56</v>
+        <v>4.558</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1221</v>
+        <v>0.1222</v>
       </c>
       <c r="F92" t="n">
-        <v>0.008043</v>
+        <v>142.9</v>
       </c>
       <c r="G92" t="n">
         <v>12.32</v>
       </c>
       <c r="H92" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9915</v>
       </c>
       <c r="I92" t="n">
         <v>4.878</v>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3.73</v>
+        <v>3.729</v>
       </c>
       <c r="E93" t="n">
         <v>0.9746</v>
       </c>
       <c r="F93" t="n">
-        <v>0.05202</v>
+        <v>88.14</v>
       </c>
       <c r="G93" t="n">
         <v>27.94</v>
@@ -5010,7 +5010,7 @@
         <v>0.5236</v>
       </c>
       <c r="F94" t="n">
-        <v>0.02957</v>
+        <v>95.66</v>
       </c>
       <c r="G94" t="n">
         <v>11.74</v>
@@ -5058,7 +5058,7 @@
         <v>1.064</v>
       </c>
       <c r="F95" t="n">
-        <v>0.06633</v>
+        <v>91.14</v>
       </c>
       <c r="G95" t="n">
         <v>24.4</v>
@@ -5106,7 +5106,7 @@
         <v>0.8487</v>
       </c>
       <c r="F96" t="n">
-        <v>0.02765</v>
+        <v>83.38</v>
       </c>
       <c r="G96" t="n">
         <v>26.99</v>
@@ -5154,7 +5154,7 @@
         <v>0.9449</v>
       </c>
       <c r="F97" t="n">
-        <v>0.04064</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="G97" t="n">
         <v>25.82</v>
@@ -5196,13 +5196,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5.525</v>
+        <v>5.522</v>
       </c>
       <c r="E98" t="n">
         <v>0.1095</v>
       </c>
       <c r="F98" t="n">
-        <v>0.004419</v>
+        <v>131.7</v>
       </c>
       <c r="G98" t="n">
         <v>10.52</v>
@@ -5250,7 +5250,7 @@
         <v>0.8752</v>
       </c>
       <c r="F99" t="n">
-        <v>0.03343</v>
+        <v>86.56</v>
       </c>
       <c r="G99" t="n">
         <v>27.01</v>
@@ -5298,7 +5298,7 @@
         <v>1.172</v>
       </c>
       <c r="F100" t="n">
-        <v>0.05922</v>
+        <v>85.14</v>
       </c>
       <c r="G100" t="n">
         <v>10.78</v>
@@ -5346,7 +5346,7 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>0.04554</v>
+        <v>88.78</v>
       </c>
       <c r="G101" t="n">
         <v>26.57</v>
@@ -5394,7 +5394,7 @@
         <v>0.8618</v>
       </c>
       <c r="F102" t="n">
-        <v>0.03202</v>
+        <v>91.2</v>
       </c>
       <c r="G102" t="n">
         <v>27.62</v>
@@ -5439,10 +5439,10 @@
         <v>4.06</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9133</v>
+        <v>0.9134</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0384</v>
+        <v>86.13</v>
       </c>
       <c r="G103" t="n">
         <v>26.59</v>
@@ -5484,13 +5484,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5.058</v>
+        <v>5.055</v>
       </c>
       <c r="E104" t="n">
         <v>0.1039</v>
       </c>
       <c r="F104" t="n">
-        <v>0.004904</v>
+        <v>126.6</v>
       </c>
       <c r="G104" t="n">
         <v>12.03</v>
@@ -5538,7 +5538,7 @@
         <v>0.7854</v>
       </c>
       <c r="F105" t="n">
-        <v>0.02972</v>
+        <v>92.05</v>
       </c>
       <c r="G105" t="n">
         <v>27.26</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4.057</v>
+        <v>4.056</v>
       </c>
       <c r="E106" t="n">
         <v>0.1285</v>
       </c>
       <c r="F106" t="n">
-        <v>0.007482</v>
+        <v>114</v>
       </c>
       <c r="G106" t="n">
         <v>11.59</v>
@@ -5634,7 +5634,7 @@
         <v>0.8751</v>
       </c>
       <c r="F107" t="n">
-        <v>0.03788</v>
+        <v>85.77</v>
       </c>
       <c r="G107" t="n">
         <v>25.68</v>
@@ -5682,7 +5682,7 @@
         <v>0.8508</v>
       </c>
       <c r="F108" t="n">
-        <v>0.02009</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="G108" t="n">
         <v>24.7</v>
@@ -5724,19 +5724,19 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4.981</v>
+        <v>4.978</v>
       </c>
       <c r="E109" t="n">
-        <v>0.06689000000000001</v>
+        <v>0.0669</v>
       </c>
       <c r="F109" t="n">
-        <v>0.004775</v>
+        <v>147.7</v>
       </c>
       <c r="G109" t="n">
         <v>13.67</v>
       </c>
       <c r="H109" t="n">
-        <v>0.4893</v>
+        <v>0.4894</v>
       </c>
       <c r="I109" t="n">
         <v>6.107</v>
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>7.516</v>
+        <v>7.512</v>
       </c>
       <c r="E110" t="n">
         <v>0.1769</v>
       </c>
       <c r="F110" t="n">
-        <v>0.004728</v>
+        <v>117.7</v>
       </c>
       <c r="G110" t="n">
         <v>15.93</v>
@@ -5826,7 +5826,7 @@
         <v>0.8197</v>
       </c>
       <c r="F111" t="n">
-        <v>0.01867</v>
+        <v>81.98</v>
       </c>
       <c r="G111" t="n">
         <v>24.2</v>
@@ -5874,7 +5874,7 @@
         <v>0.5876</v>
       </c>
       <c r="F112" t="n">
-        <v>0.01729</v>
+        <v>89.8</v>
       </c>
       <c r="G112" t="n">
         <v>14.46</v>
@@ -5922,7 +5922,7 @@
         <v>0.5745</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0184</v>
+        <v>84.2</v>
       </c>
       <c r="G113" t="n">
         <v>14.58</v>
@@ -5970,7 +5970,7 @@
         <v>0.919</v>
       </c>
       <c r="F114" t="n">
-        <v>0.02982</v>
+        <v>83.84</v>
       </c>
       <c r="G114" t="n">
         <v>26.56</v>
@@ -6012,19 +6012,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4.879</v>
+        <v>4.877</v>
       </c>
       <c r="E115" t="n">
         <v>0.1164</v>
       </c>
       <c r="F115" t="n">
-        <v>0.006472</v>
+        <v>127.2</v>
       </c>
       <c r="G115" t="n">
         <v>14.09</v>
       </c>
       <c r="H115" t="n">
-        <v>0.8263</v>
+        <v>0.8264</v>
       </c>
       <c r="I115" t="n">
         <v>5.412</v>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5.168</v>
+        <v>5.166</v>
       </c>
       <c r="E116" t="n">
         <v>0.1129</v>
       </c>
       <c r="F116" t="n">
-        <v>0.005762</v>
+        <v>133.7</v>
       </c>
       <c r="G116" t="n">
         <v>15.66</v>
@@ -6108,13 +6108,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3.69</v>
+        <v>3.689</v>
       </c>
       <c r="E117" t="n">
         <v>0.8505</v>
       </c>
       <c r="F117" t="n">
-        <v>0.02097</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="G117" t="n">
         <v>23.34</v>
@@ -6162,13 +6162,13 @@
         <v>0.5577</v>
       </c>
       <c r="F118" t="n">
-        <v>0.01846</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="G118" t="n">
         <v>7.952</v>
       </c>
       <c r="H118" t="n">
-        <v>7.013</v>
+        <v>7.014</v>
       </c>
       <c r="I118" t="n">
         <v>4.354</v>
@@ -6204,19 +6204,19 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5.049</v>
+        <v>5.047</v>
       </c>
       <c r="E119" t="n">
         <v>0.1212</v>
       </c>
       <c r="F119" t="n">
-        <v>0.005638</v>
+        <v>123.2</v>
       </c>
       <c r="G119" t="n">
         <v>14.05</v>
       </c>
       <c r="H119" t="n">
-        <v>0.8623</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="I119" t="n">
         <v>4.945</v>
@@ -6258,7 +6258,7 @@
         <v>1.075</v>
       </c>
       <c r="F120" t="n">
-        <v>0.03949</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="G120" t="n">
         <v>23.43</v>
@@ -6300,19 +6300,19 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5.54</v>
+        <v>5.538</v>
       </c>
       <c r="E121" t="n">
         <v>0.1482</v>
       </c>
       <c r="F121" t="n">
-        <v>0.006114</v>
+        <v>118.6</v>
       </c>
       <c r="G121" t="n">
         <v>18.68</v>
       </c>
       <c r="H121" t="n">
-        <v>0.7934</v>
+        <v>0.7935</v>
       </c>
       <c r="I121" t="n">
         <v>5.77</v>
@@ -6354,7 +6354,7 @@
         <v>1.1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.03334</v>
+        <v>85.55</v>
       </c>
       <c r="G122" t="n">
         <v>28.62</v>
@@ -6402,7 +6402,7 @@
         <v>0.6988</v>
       </c>
       <c r="F123" t="n">
-        <v>0.02293</v>
+        <v>85.72</v>
       </c>
       <c r="G123" t="n">
         <v>12.17</v>
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6.048</v>
+        <v>6.045</v>
       </c>
       <c r="E124" t="n">
         <v>0.1652</v>
       </c>
       <c r="F124" t="n">
-        <v>0.005982</v>
+        <v>118.4</v>
       </c>
       <c r="G124" t="n">
         <v>12.84</v>
@@ -6498,7 +6498,7 @@
         <v>1.045</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04204</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G125" t="n">
         <v>23.72</v>
@@ -6540,19 +6540,19 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5.215</v>
+        <v>5.213</v>
       </c>
       <c r="E126" t="n">
         <v>0.1187</v>
       </c>
       <c r="F126" t="n">
-        <v>0.005857</v>
+        <v>126.3</v>
       </c>
       <c r="G126" t="n">
         <v>14.33</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8282</v>
       </c>
       <c r="I126" t="n">
         <v>5.208</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4.899</v>
+        <v>4.897</v>
       </c>
       <c r="E127" t="n">
         <v>0.1171</v>
       </c>
       <c r="F127" t="n">
-        <v>0.005617</v>
+        <v>116.3</v>
       </c>
       <c r="G127" t="n">
         <v>11.24</v>
@@ -6642,7 +6642,7 @@
         <v>0.993</v>
       </c>
       <c r="F128" t="n">
-        <v>0.03565</v>
+        <v>83.22</v>
       </c>
       <c r="G128" t="n">
         <v>23.75</v>
@@ -6690,7 +6690,7 @@
         <v>0.7719</v>
       </c>
       <c r="F129" t="n">
-        <v>0.03166</v>
+        <v>86.13</v>
       </c>
       <c r="G129" t="n">
         <v>7.54</v>
@@ -6738,7 +6738,7 @@
         <v>0.6593</v>
       </c>
       <c r="F130" t="n">
-        <v>0.02688</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="G130" t="n">
         <v>12.24</v>
@@ -6786,7 +6786,7 @@
         <v>1.013</v>
       </c>
       <c r="F131" t="n">
-        <v>0.04294</v>
+        <v>84.16</v>
       </c>
       <c r="G131" t="n">
         <v>23.93</v>
@@ -6828,13 +6828,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4.58</v>
+        <v>4.578</v>
       </c>
       <c r="E132" t="n">
         <v>0.1216</v>
       </c>
       <c r="F132" t="n">
-        <v>0.005433</v>
+        <v>118.1</v>
       </c>
       <c r="G132" t="n">
         <v>11.39</v>
@@ -6876,13 +6876,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4.722</v>
+        <v>4.721</v>
       </c>
       <c r="E133" t="n">
         <v>0.1305</v>
       </c>
       <c r="F133" t="n">
-        <v>0.006029</v>
+        <v>111.3</v>
       </c>
       <c r="G133" t="n">
         <v>12.51</v>
@@ -6930,7 +6930,7 @@
         <v>1.023</v>
       </c>
       <c r="F134" t="n">
-        <v>0.04272</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="G134" t="n">
         <v>23.92</v>
@@ -6978,7 +6978,7 @@
         <v>0.6889</v>
       </c>
       <c r="F135" t="n">
-        <v>0.02587</v>
+        <v>89.89</v>
       </c>
       <c r="G135" t="n">
         <v>12.06</v>
@@ -7020,13 +7020,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4.088</v>
+        <v>4.087</v>
       </c>
       <c r="E136" t="n">
         <v>0.1202</v>
       </c>
       <c r="F136" t="n">
-        <v>0.007592</v>
+        <v>128.9</v>
       </c>
       <c r="G136" t="n">
         <v>11.95</v>
@@ -7074,7 +7074,7 @@
         <v>1.094</v>
       </c>
       <c r="F137" t="n">
-        <v>0.04755</v>
+        <v>83.86</v>
       </c>
       <c r="G137" t="n">
         <v>23.46</v>
@@ -7122,7 +7122,7 @@
         <v>0.989</v>
       </c>
       <c r="F138" t="n">
-        <v>0.03873</v>
+        <v>84.89</v>
       </c>
       <c r="G138" t="n">
         <v>25.24</v>
@@ -7170,7 +7170,7 @@
         <v>1.07</v>
       </c>
       <c r="F139" t="n">
-        <v>0.04929</v>
+        <v>86.03</v>
       </c>
       <c r="G139" t="n">
         <v>23.08</v>
@@ -7218,7 +7218,7 @@
         <v>0.8712</v>
       </c>
       <c r="F140" t="n">
-        <v>0.007342</v>
+        <v>82.13</v>
       </c>
       <c r="G140" t="n">
         <v>64.95999999999999</v>
@@ -7270,7 +7270,7 @@
         <v>0.152</v>
       </c>
       <c r="F141" t="n">
-        <v>0.005158</v>
+        <v>123.4</v>
       </c>
       <c r="G141" t="n">
         <v>3.744</v>
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6.937</v>
+        <v>6.935</v>
       </c>
       <c r="E142" t="n">
         <v>0.2413</v>
       </c>
       <c r="F142" t="n">
-        <v>0.008756999999999999</v>
+        <v>104.9</v>
       </c>
       <c r="G142" t="n">
         <v>4.845</v>
@@ -7360,13 +7360,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>13.72</v>
+        <v>13.71</v>
       </c>
       <c r="E143" t="n">
         <v>0.1782</v>
       </c>
       <c r="F143" t="n">
-        <v>0.003376</v>
+        <v>109.4</v>
       </c>
       <c r="G143" t="n">
         <v>4.678</v>
@@ -7404,47 +7404,47 @@
       <c r="B144" s="1" t="n"/>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>LST-Perm-2024</t>
+          <t>LST-S-SBP-2024</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>9.382</v>
+        <v>12.34</v>
       </c>
       <c r="E144" t="n">
-        <v>0.311</v>
+        <v>0.1112</v>
       </c>
       <c r="F144" t="n">
-        <v>0.006164</v>
+        <v>127.6</v>
       </c>
       <c r="G144" t="n">
-        <v>8.936999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="H144" t="n">
-        <v>3.48</v>
+        <v>0.4002</v>
       </c>
       <c r="I144" t="n">
-        <v>11.16</v>
+        <v>20.04</v>
       </c>
       <c r="J144" t="n">
-        <v>2.35</v>
+        <v>5.513</v>
       </c>
       <c r="K144" t="n">
-        <v>1.886</v>
+        <v>3.185</v>
       </c>
       <c r="L144" t="n">
-        <v>5.01</v>
+        <v>3.282</v>
       </c>
       <c r="M144" t="n">
-        <v>0.01572</v>
+        <v>0.7336</v>
       </c>
       <c r="N144" t="n">
-        <v>0.1036</v>
+        <v>0.1566</v>
       </c>
       <c r="O144" t="n">
-        <v>0.02709</v>
+        <v>0.6964</v>
       </c>
       <c r="P144" t="n">
-        <v>0.02837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -7452,44 +7452,44 @@
       <c r="B145" s="1" t="n"/>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>LST-S-SBP-2024</t>
+          <t>LST-S-SOKOL-2024</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>12.36</v>
+        <v>8.74</v>
       </c>
       <c r="E145" t="n">
-        <v>0.1112</v>
+        <v>0.07364999999999999</v>
       </c>
       <c r="F145" t="n">
-        <v>0.00363</v>
+        <v>151.3</v>
       </c>
       <c r="G145" t="n">
-        <v>27.78</v>
+        <v>17.87</v>
       </c>
       <c r="H145" t="n">
-        <v>0.4001</v>
+        <v>0.4121</v>
       </c>
       <c r="I145" t="n">
-        <v>20.04</v>
+        <v>17.72</v>
       </c>
       <c r="J145" t="n">
-        <v>5.513</v>
+        <v>5.234</v>
       </c>
       <c r="K145" t="n">
-        <v>3.185</v>
+        <v>2.909</v>
       </c>
       <c r="L145" t="n">
-        <v>3.282</v>
+        <v>3.448</v>
       </c>
       <c r="M145" t="n">
-        <v>0.7336</v>
+        <v>0.6268</v>
       </c>
       <c r="N145" t="n">
-        <v>0.1566</v>
+        <v>0.1403</v>
       </c>
       <c r="O145" t="n">
-        <v>0.6964</v>
+        <v>0.591</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -7500,47 +7500,47 @@
       <c r="B146" s="1" t="n"/>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>LST-S-SOKOL-2024</t>
+          <t>LST-S-SYAS-2024</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>8.752000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="E146" t="n">
-        <v>0.07364</v>
+        <v>0.06693</v>
       </c>
       <c r="F146" t="n">
-        <v>0.003127</v>
+        <v>141.7</v>
       </c>
       <c r="G146" t="n">
-        <v>17.87</v>
+        <v>21.31</v>
       </c>
       <c r="H146" t="n">
-        <v>0.4121</v>
+        <v>0.3141</v>
       </c>
       <c r="I146" t="n">
-        <v>17.72</v>
+        <v>6.15</v>
       </c>
       <c r="J146" t="n">
-        <v>5.234</v>
+        <v>3.06</v>
       </c>
       <c r="K146" t="n">
-        <v>2.909</v>
+        <v>1.652</v>
       </c>
       <c r="L146" t="n">
-        <v>3.448</v>
+        <v>4.407</v>
       </c>
       <c r="M146" t="n">
-        <v>0.6268</v>
+        <v>0.3889</v>
       </c>
       <c r="N146" t="n">
-        <v>0.1403</v>
+        <v>0.4246</v>
       </c>
       <c r="O146" t="n">
-        <v>0.591</v>
+        <v>0.4324</v>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>0.3517</v>
       </c>
     </row>
     <row r="147">
@@ -7548,95 +7548,103 @@
       <c r="B147" s="1" t="n"/>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>LST-S-SYAS-2024</t>
+          <t>LST-S-VLK-2024</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>6.195</v>
+        <v>10.65</v>
       </c>
       <c r="E147" t="n">
-        <v>0.06691999999999999</v>
+        <v>0.1869</v>
       </c>
       <c r="F147" t="n">
-        <v>0.003871</v>
+        <v>110.2</v>
       </c>
       <c r="G147" t="n">
-        <v>21.31</v>
+        <v>49.88</v>
       </c>
       <c r="H147" t="n">
-        <v>0.314</v>
+        <v>0.3747</v>
       </c>
       <c r="I147" t="n">
-        <v>6.15</v>
+        <v>16.39</v>
       </c>
       <c r="J147" t="n">
-        <v>3.06</v>
+        <v>4.664</v>
       </c>
       <c r="K147" t="n">
-        <v>1.652</v>
+        <v>2.772</v>
       </c>
       <c r="L147" t="n">
-        <v>4.407</v>
+        <v>4.541</v>
       </c>
       <c r="M147" t="n">
-        <v>0.3889</v>
+        <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>0.4246</v>
+        <v>0.4621</v>
       </c>
       <c r="O147" t="n">
-        <v>0.4324</v>
+        <v>1</v>
       </c>
       <c r="P147" t="n">
-        <v>0.3517</v>
+        <v>0.04429</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n"/>
-      <c r="B148" s="1" t="n"/>
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Peat</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>PFA</t>
+        </is>
+      </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>LST-S-VLK-2024</t>
+          <t>PFA-Sk3-00-2024</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.66</v>
+        <v>4.12</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1869</v>
+        <v>0.4922</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00487</v>
+        <v>90.7</v>
       </c>
       <c r="G148" t="n">
-        <v>49.88</v>
+        <v>20.37</v>
       </c>
       <c r="H148" t="n">
-        <v>0.3746</v>
+        <v>2.416</v>
       </c>
       <c r="I148" t="n">
-        <v>16.39</v>
+        <v>3.456</v>
       </c>
       <c r="J148" t="n">
-        <v>4.664</v>
+        <v>0.3283</v>
       </c>
       <c r="K148" t="n">
-        <v>2.772</v>
+        <v>1.163</v>
       </c>
       <c r="L148" t="n">
-        <v>4.541</v>
+        <v>39.39</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>0.02127</v>
       </c>
       <c r="N148" t="n">
-        <v>0.4621</v>
+        <v>0.798</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>0.03787</v>
       </c>
       <c r="P148" t="n">
-        <v>0.04429</v>
+        <v>0.5018</v>
       </c>
     </row>
     <row r="149">
@@ -7644,47 +7652,47 @@
       <c r="B149" s="1" t="n"/>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>LST-Spb-2024</t>
+          <t>PFA-T1098-2024</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>20.7</v>
+        <v>3.984</v>
       </c>
       <c r="E149" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5406</v>
       </c>
       <c r="F149" t="n">
-        <v>0.002694</v>
+        <v>89.53</v>
       </c>
       <c r="G149" t="n">
-        <v>7.756</v>
+        <v>24.7</v>
       </c>
       <c r="H149" t="n">
-        <v>7.453</v>
+        <v>2.189</v>
       </c>
       <c r="I149" t="n">
-        <v>18.04</v>
+        <v>3.422</v>
       </c>
       <c r="J149" t="n">
-        <v>5.104</v>
+        <v>0.3552</v>
       </c>
       <c r="K149" t="n">
-        <v>2.961</v>
+        <v>1.104</v>
       </c>
       <c r="L149" t="n">
-        <v>4.822</v>
+        <v>47.43</v>
       </c>
       <c r="M149" t="n">
-        <v>0.1296</v>
+        <v>0.02917</v>
       </c>
       <c r="N149" t="n">
-        <v>0.05239</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>0.1015</v>
+        <v>0.04987</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>0.5279</v>
       </c>
     </row>
     <row r="150">
@@ -7692,47 +7700,47 @@
       <c r="B150" s="1" t="n"/>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>LST-Syas-2024</t>
+          <t>PFA-T598-2024</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>8.567</v>
+        <v>3.861</v>
       </c>
       <c r="E150" t="n">
-        <v>0.71</v>
+        <v>0.4808</v>
       </c>
       <c r="F150" t="n">
-        <v>0.01031</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="G150" t="n">
-        <v>7.879</v>
+        <v>21.18</v>
       </c>
       <c r="H150" t="n">
-        <v>9.010999999999999</v>
+        <v>2.27</v>
       </c>
       <c r="I150" t="n">
-        <v>8.718999999999999</v>
+        <v>3.326</v>
       </c>
       <c r="J150" t="n">
-        <v>3.348</v>
+        <v>0.5</v>
       </c>
       <c r="K150" t="n">
-        <v>2.099</v>
+        <v>1.103</v>
       </c>
       <c r="L150" t="n">
-        <v>4.842</v>
+        <v>23.19</v>
       </c>
       <c r="M150" t="n">
-        <v>0.06468</v>
+        <v>0.01905</v>
       </c>
       <c r="N150" t="n">
-        <v>0.06106</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="O150" t="n">
-        <v>0.05925</v>
+        <v>0.03697</v>
       </c>
       <c r="P150" t="n">
-        <v>0.04836</v>
+        <v>0.3899</v>
       </c>
     </row>
     <row r="151">
@@ -7740,151 +7748,147 @@
       <c r="B151" s="1" t="n"/>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>LST-Vlk-2024</t>
+          <t>PFA-T5H98-2024</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>23.74</v>
+        <v>3.806</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4558</v>
+        <v>0.3614</v>
       </c>
       <c r="F151" t="n">
-        <v>0.005551</v>
+        <v>103.5</v>
       </c>
       <c r="G151" t="n">
-        <v>7.527</v>
+        <v>23.11</v>
       </c>
       <c r="H151" t="n">
-        <v>6.055</v>
+        <v>1.564</v>
       </c>
       <c r="I151" t="n">
-        <v>17.01</v>
+        <v>3.566</v>
       </c>
       <c r="J151" t="n">
-        <v>4.348</v>
+        <v>0.4333</v>
       </c>
       <c r="K151" t="n">
-        <v>3.166</v>
+        <v>1.176</v>
       </c>
       <c r="L151" t="n">
-        <v>7.112</v>
+        <v>39.53</v>
       </c>
       <c r="M151" t="n">
-        <v>0.1214</v>
+        <v>0.01463</v>
       </c>
       <c r="N151" t="n">
-        <v>0.09801</v>
+        <v>0.6773</v>
       </c>
       <c r="O151" t="n">
-        <v>0.093</v>
+        <v>0.0362</v>
       </c>
       <c r="P151" t="n">
-        <v>0.0003387</v>
+        <v>0.3447</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>Peat</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="inlineStr">
-        <is>
-          <t>PFA</t>
-        </is>
-      </c>
+      <c r="A152" s="1" t="n"/>
+      <c r="B152" s="1" t="n"/>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>PFA-Sk3-00-2024</t>
+          <t>PFA-T698-2024</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4.12</v>
+        <v>3.612</v>
       </c>
       <c r="E152" t="n">
-        <v>0.4921</v>
+        <v>0.4165</v>
       </c>
       <c r="F152" t="n">
-        <v>0.01813</v>
+        <v>97.56</v>
       </c>
       <c r="G152" t="n">
-        <v>20.37</v>
+        <v>24.08</v>
       </c>
       <c r="H152" t="n">
-        <v>2.416</v>
+        <v>1.73</v>
       </c>
       <c r="I152" t="n">
-        <v>3.456</v>
+        <v>3.449</v>
       </c>
       <c r="J152" t="n">
-        <v>0.3283</v>
+        <v>0.4345</v>
       </c>
       <c r="K152" t="n">
-        <v>1.163</v>
+        <v>1.148</v>
       </c>
       <c r="L152" t="n">
-        <v>39.39</v>
+        <v>43.54</v>
       </c>
       <c r="M152" t="n">
-        <v>0.02127</v>
+        <v>0.01256</v>
       </c>
       <c r="N152" t="n">
-        <v>0.798</v>
+        <v>0.5536</v>
       </c>
       <c r="O152" t="n">
-        <v>0.03787</v>
+        <v>0.03096</v>
       </c>
       <c r="P152" t="n">
-        <v>0.5018</v>
+        <v>0.3059</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n"/>
-      <c r="B153" s="1" t="n"/>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>PHA</t>
+        </is>
+      </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>PFA-T1098-2024</t>
+          <t>PHA-Sk3-00-2024</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3.984</v>
+        <v>2.921</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5406</v>
+        <v>0.2902</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0194</v>
+        <v>100.2</v>
       </c>
       <c r="G153" t="n">
-        <v>24.7</v>
+        <v>20.37</v>
       </c>
       <c r="H153" t="n">
-        <v>2.189</v>
+        <v>1.425</v>
       </c>
       <c r="I153" t="n">
-        <v>3.422</v>
+        <v>2.398</v>
       </c>
       <c r="J153" t="n">
-        <v>0.3552</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="K153" t="n">
-        <v>1.104</v>
+        <v>1.036</v>
       </c>
       <c r="L153" t="n">
-        <v>47.43</v>
+        <v>14.04</v>
       </c>
       <c r="M153" t="n">
-        <v>0.02917</v>
+        <v>0.008383</v>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>0.1423</v>
       </c>
       <c r="O153" t="n">
-        <v>0.04987</v>
+        <v>0.01393</v>
       </c>
       <c r="P153" t="n">
-        <v>0.5279</v>
+        <v>0.1763</v>
       </c>
     </row>
     <row r="154">
@@ -7892,47 +7896,47 @@
       <c r="B154" s="1" t="n"/>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>PFA-T598-2024</t>
+          <t>PHA-T598-2024</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3.862</v>
+        <v>2.633</v>
       </c>
       <c r="E154" t="n">
-        <v>0.4807</v>
+        <v>0.659</v>
       </c>
       <c r="F154" t="n">
-        <v>0.02112</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="G154" t="n">
-        <v>21.18</v>
+        <v>17.8</v>
       </c>
       <c r="H154" t="n">
-        <v>2.27</v>
+        <v>3.702</v>
       </c>
       <c r="I154" t="n">
-        <v>3.326</v>
+        <v>2.017</v>
       </c>
       <c r="J154" t="n">
-        <v>0.5</v>
+        <v>0.8227</v>
       </c>
       <c r="K154" t="n">
-        <v>1.103</v>
+        <v>1.016</v>
       </c>
       <c r="L154" t="n">
-        <v>23.19</v>
+        <v>6.519</v>
       </c>
       <c r="M154" t="n">
-        <v>0.01905</v>
+        <v>0.01172</v>
       </c>
       <c r="N154" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.08062</v>
       </c>
       <c r="O154" t="n">
-        <v>0.03697</v>
+        <v>0.01381</v>
       </c>
       <c r="P154" t="n">
-        <v>0.3899</v>
+        <v>0.1564</v>
       </c>
     </row>
     <row r="155">
@@ -7940,47 +7944,47 @@
       <c r="B155" s="1" t="n"/>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>PFA-T5H98-2024</t>
+          <t>PHA-T698-2024</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.806</v>
+        <v>2.437</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3613</v>
+        <v>0.6341</v>
       </c>
       <c r="F155" t="n">
-        <v>0.01845</v>
+        <v>97.69</v>
       </c>
       <c r="G155" t="n">
-        <v>23.11</v>
+        <v>22.43</v>
       </c>
       <c r="H155" t="n">
-        <v>1.564</v>
+        <v>2.827</v>
       </c>
       <c r="I155" t="n">
-        <v>3.566</v>
+        <v>1.737</v>
       </c>
       <c r="J155" t="n">
-        <v>0.4333</v>
+        <v>0.7543</v>
       </c>
       <c r="K155" t="n">
-        <v>1.176</v>
+        <v>0.9704</v>
       </c>
       <c r="L155" t="n">
-        <v>39.53</v>
+        <v>8.807</v>
       </c>
       <c r="M155" t="n">
-        <v>0.01463</v>
+        <v>0.01102</v>
       </c>
       <c r="N155" t="n">
-        <v>0.6773</v>
+        <v>0.0664</v>
       </c>
       <c r="O155" t="n">
-        <v>0.0362</v>
+        <v>0.02074</v>
       </c>
       <c r="P155" t="n">
-        <v>0.3447</v>
+        <v>0.1498</v>
       </c>
     </row>
     <row r="156">
@@ -7988,99 +7992,99 @@
       <c r="B156" s="1" t="n"/>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>PFA-T698-2024</t>
+          <t>PHA-TTL98-2024</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.612</v>
+        <v>2.655</v>
       </c>
       <c r="E156" t="n">
-        <v>0.4165</v>
+        <v>0.7224</v>
       </c>
       <c r="F156" t="n">
-        <v>0.02146</v>
+        <v>94.67</v>
       </c>
       <c r="G156" t="n">
-        <v>24.08</v>
+        <v>18.37</v>
       </c>
       <c r="H156" t="n">
-        <v>1.73</v>
+        <v>3.932</v>
       </c>
       <c r="I156" t="n">
-        <v>3.449</v>
+        <v>2.009</v>
       </c>
       <c r="J156" t="n">
-        <v>0.4345</v>
+        <v>0.681</v>
       </c>
       <c r="K156" t="n">
-        <v>1.148</v>
+        <v>0.9859</v>
       </c>
       <c r="L156" t="n">
-        <v>43.54</v>
+        <v>10.83</v>
       </c>
       <c r="M156" t="n">
-        <v>0.01256</v>
+        <v>0.01211</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5536</v>
+        <v>0.1012</v>
       </c>
       <c r="O156" t="n">
-        <v>0.03096</v>
+        <v>0.02291</v>
       </c>
       <c r="P156" t="n">
-        <v>0.3059</v>
+        <v>0.1834</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n"/>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>PHA</t>
+          <t>PHF</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>PHA-Sk3-00-2024</t>
+          <t>PHF-Sk300-2024</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2.921</v>
+        <v>2.988</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2902</v>
+        <v>0.8065</v>
       </c>
       <c r="F157" t="n">
-        <v>0.02443</v>
+        <v>93.8</v>
       </c>
       <c r="G157" t="n">
-        <v>20.37</v>
+        <v>17.29</v>
       </c>
       <c r="H157" t="n">
-        <v>1.425</v>
+        <v>4.665</v>
       </c>
       <c r="I157" t="n">
-        <v>2.398</v>
+        <v>2.161</v>
       </c>
       <c r="J157" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.3623</v>
       </c>
       <c r="K157" t="n">
-        <v>1.036</v>
+        <v>1.002</v>
       </c>
       <c r="L157" t="n">
-        <v>14.04</v>
+        <v>14.89</v>
       </c>
       <c r="M157" t="n">
-        <v>0.008383</v>
+        <v>0.01136</v>
       </c>
       <c r="N157" t="n">
-        <v>0.1423</v>
+        <v>0.2497</v>
       </c>
       <c r="O157" t="n">
-        <v>0.01393</v>
+        <v>0.01749</v>
       </c>
       <c r="P157" t="n">
-        <v>0.1763</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="158">
@@ -8088,47 +8092,47 @@
       <c r="B158" s="1" t="n"/>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>PHA-T598-2024</t>
+          <t>PHF-T10L98-2024</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.633</v>
+        <v>3.044</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6589</v>
+        <v>0.4048</v>
       </c>
       <c r="F158" t="n">
-        <v>0.06308</v>
+        <v>101.7</v>
       </c>
       <c r="G158" t="n">
-        <v>17.8</v>
+        <v>16.62</v>
       </c>
       <c r="H158" t="n">
-        <v>3.702</v>
+        <v>2.436</v>
       </c>
       <c r="I158" t="n">
-        <v>2.017</v>
+        <v>2.417</v>
       </c>
       <c r="J158" t="n">
-        <v>0.8227</v>
+        <v>0.4001</v>
       </c>
       <c r="K158" t="n">
-        <v>1.016</v>
+        <v>1.018</v>
       </c>
       <c r="L158" t="n">
-        <v>6.519</v>
+        <v>19.65</v>
       </c>
       <c r="M158" t="n">
-        <v>0.01172</v>
+        <v>0.008867999999999999</v>
       </c>
       <c r="N158" t="n">
-        <v>0.08062</v>
+        <v>0.1954</v>
       </c>
       <c r="O158" t="n">
-        <v>0.01381</v>
+        <v>0.0164</v>
       </c>
       <c r="P158" t="n">
-        <v>0.1564</v>
+        <v>0.2005</v>
       </c>
     </row>
     <row r="159">
@@ -8136,47 +8140,47 @@
       <c r="B159" s="1" t="n"/>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>PHA-T698-2024</t>
+          <t>PHF-T698-2024</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2.437</v>
+        <v>2.64</v>
       </c>
       <c r="E159" t="n">
-        <v>0.6341</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="F159" t="n">
-        <v>0.07134</v>
+        <v>100.8</v>
       </c>
       <c r="G159" t="n">
-        <v>22.43</v>
+        <v>15.6</v>
       </c>
       <c r="H159" t="n">
-        <v>2.827</v>
+        <v>3.493</v>
       </c>
       <c r="I159" t="n">
-        <v>1.737</v>
+        <v>2.429</v>
       </c>
       <c r="J159" t="n">
-        <v>0.7543</v>
+        <v>0.5766</v>
       </c>
       <c r="K159" t="n">
-        <v>0.9704</v>
+        <v>1.084</v>
       </c>
       <c r="L159" t="n">
-        <v>8.807</v>
+        <v>15.2</v>
       </c>
       <c r="M159" t="n">
-        <v>0.01102</v>
+        <v>0.006822</v>
       </c>
       <c r="N159" t="n">
-        <v>0.0664</v>
+        <v>0.1216</v>
       </c>
       <c r="O159" t="n">
-        <v>0.02074</v>
+        <v>0.01349</v>
       </c>
       <c r="P159" t="n">
-        <v>0.1498</v>
+        <v>0.1262</v>
       </c>
     </row>
     <row r="160">
@@ -8184,99 +8188,103 @@
       <c r="B160" s="1" t="n"/>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>PHA-TTL98-2024</t>
+          <t>PHF-T7H98-2024</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2.655</v>
+        <v>2.76</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7224</v>
+        <v>0.55</v>
       </c>
       <c r="F160" t="n">
-        <v>0.06916</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>18.37</v>
+        <v>14.55</v>
       </c>
       <c r="H160" t="n">
-        <v>3.932</v>
+        <v>3.78</v>
       </c>
       <c r="I160" t="n">
-        <v>2.009</v>
+        <v>2.66</v>
       </c>
       <c r="J160" t="n">
-        <v>0.681</v>
+        <v>0.5457</v>
       </c>
       <c r="K160" t="n">
-        <v>0.9859</v>
+        <v>1.101</v>
       </c>
       <c r="L160" t="n">
-        <v>10.83</v>
+        <v>14.81</v>
       </c>
       <c r="M160" t="n">
-        <v>0.01211</v>
+        <v>0.01158</v>
       </c>
       <c r="N160" t="n">
-        <v>0.1012</v>
+        <v>0.1739</v>
       </c>
       <c r="O160" t="n">
-        <v>0.02291</v>
+        <v>0.01575</v>
       </c>
       <c r="P160" t="n">
-        <v>0.1834</v>
+        <v>0.1782</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n"/>
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>PHF</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>PHF-Sk300-2024</t>
+          <t>SFA-PW04-2024</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2.988</v>
+        <v>3.653</v>
       </c>
       <c r="E161" t="n">
-        <v>0.8065</v>
+        <v>0.3846</v>
       </c>
       <c r="F161" t="n">
-        <v>0.06529</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G161" t="n">
-        <v>17.29</v>
+        <v>23.13</v>
       </c>
       <c r="H161" t="n">
-        <v>4.665</v>
+        <v>1.663</v>
       </c>
       <c r="I161" t="n">
-        <v>2.161</v>
+        <v>2.694</v>
       </c>
       <c r="J161" t="n">
-        <v>0.3623</v>
+        <v>0.3183</v>
       </c>
       <c r="K161" t="n">
-        <v>1.002</v>
+        <v>0.9565</v>
       </c>
       <c r="L161" t="n">
-        <v>14.89</v>
+        <v>46.24</v>
       </c>
       <c r="M161" t="n">
-        <v>0.01136</v>
+        <v>0.0162</v>
       </c>
       <c r="N161" t="n">
-        <v>0.2497</v>
+        <v>0.4161</v>
       </c>
       <c r="O161" t="n">
-        <v>0.01749</v>
+        <v>0.0236</v>
       </c>
       <c r="P161" t="n">
-        <v>0.3162</v>
+        <v>0.4105</v>
       </c>
     </row>
     <row r="162">
@@ -8284,95 +8292,99 @@
       <c r="B162" s="1" t="n"/>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>PHF-T10L98-2024</t>
+          <t>SFA-PW16-2024</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3.044</v>
+        <v>4.403</v>
       </c>
       <c r="E162" t="n">
-        <v>0.4048</v>
+        <v>0.5484</v>
       </c>
       <c r="F162" t="n">
-        <v>0.03023</v>
+        <v>90.84</v>
       </c>
       <c r="G162" t="n">
-        <v>16.62</v>
+        <v>18.49</v>
       </c>
       <c r="H162" t="n">
-        <v>2.436</v>
+        <v>2.966</v>
       </c>
       <c r="I162" t="n">
-        <v>2.417</v>
+        <v>3.266</v>
       </c>
       <c r="J162" t="n">
-        <v>0.4001</v>
+        <v>0.4615</v>
       </c>
       <c r="K162" t="n">
-        <v>1.018</v>
+        <v>1.076</v>
       </c>
       <c r="L162" t="n">
-        <v>19.65</v>
+        <v>18.5</v>
       </c>
       <c r="M162" t="n">
-        <v>0.008867999999999999</v>
+        <v>0.02546</v>
       </c>
       <c r="N162" t="n">
-        <v>0.1954</v>
+        <v>0.6829</v>
       </c>
       <c r="O162" t="n">
-        <v>0.0164</v>
+        <v>0.03856</v>
       </c>
       <c r="P162" t="n">
-        <v>0.2005</v>
+        <v>0.5037</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n"/>
-      <c r="B163" s="1" t="n"/>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>SHA</t>
+        </is>
+      </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>PHF-T698-2024</t>
+          <t>SHA-CtK04-2024</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2.64</v>
+        <v>2.329</v>
       </c>
       <c r="E163" t="n">
-        <v>0.5448</v>
+        <v>0.5261</v>
       </c>
       <c r="F163" t="n">
-        <v>0.05425</v>
+        <v>110.5</v>
       </c>
       <c r="G163" t="n">
-        <v>15.6</v>
+        <v>12.29</v>
       </c>
       <c r="H163" t="n">
-        <v>3.493</v>
+        <v>4.281</v>
       </c>
       <c r="I163" t="n">
-        <v>2.429</v>
+        <v>1.279</v>
       </c>
       <c r="J163" t="n">
-        <v>0.5766</v>
+        <v>0.3227</v>
       </c>
       <c r="K163" t="n">
-        <v>1.084</v>
+        <v>0.8927</v>
       </c>
       <c r="L163" t="n">
-        <v>15.2</v>
+        <v>17.61</v>
       </c>
       <c r="M163" t="n">
-        <v>0.006822</v>
+        <v>0.007764</v>
       </c>
       <c r="N163" t="n">
-        <v>0.1216</v>
+        <v>0.1515</v>
       </c>
       <c r="O163" t="n">
-        <v>0.01349</v>
+        <v>0.01517</v>
       </c>
       <c r="P163" t="n">
-        <v>0.1262</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="164">
@@ -8380,47 +8392,47 @@
       <c r="B164" s="1" t="n"/>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>PHF-T7H98-2024</t>
+          <t>SHA-CtK15-2024</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2.76</v>
+        <v>2.19</v>
       </c>
       <c r="E164" t="n">
-        <v>0.55</v>
+        <v>1.206</v>
       </c>
       <c r="F164" t="n">
-        <v>0.05064</v>
+        <v>107.6</v>
       </c>
       <c r="G164" t="n">
-        <v>14.55</v>
+        <v>20.43</v>
       </c>
       <c r="H164" t="n">
-        <v>3.78</v>
+        <v>5.904</v>
       </c>
       <c r="I164" t="n">
-        <v>2.66</v>
+        <v>0.9705</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5457</v>
+        <v>0.1514</v>
       </c>
       <c r="K164" t="n">
-        <v>1.101</v>
+        <v>0.8298</v>
       </c>
       <c r="L164" t="n">
-        <v>14.81</v>
+        <v>39.65</v>
       </c>
       <c r="M164" t="n">
-        <v>0.01158</v>
+        <v>0.00219</v>
       </c>
       <c r="N164" t="n">
-        <v>0.1739</v>
+        <v>0.251</v>
       </c>
       <c r="O164" t="n">
-        <v>0.01575</v>
+        <v>0.01486</v>
       </c>
       <c r="P164" t="n">
-        <v>0.1782</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="165">
@@ -8428,103 +8440,95 @@
       <c r="B165" s="1" t="n"/>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>PHF-TTL98-2024</t>
+          <t>SHA-CtV98-2024</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.695</v>
+        <v>2.197</v>
       </c>
       <c r="E165" t="n">
-        <v>0.6227</v>
+        <v>0.2273</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0563</v>
+        <v>127.9</v>
       </c>
       <c r="G165" t="n">
-        <v>15.48</v>
+        <v>7.86</v>
       </c>
       <c r="H165" t="n">
-        <v>4.023</v>
+        <v>2.892</v>
       </c>
       <c r="I165" t="n">
-        <v>2.364</v>
+        <v>1.101</v>
       </c>
       <c r="J165" t="n">
-        <v>0.3496</v>
+        <v>0.3604</v>
       </c>
       <c r="K165" t="n">
-        <v>1.018</v>
+        <v>0.887</v>
       </c>
       <c r="L165" t="n">
-        <v>22.64</v>
+        <v>16.07</v>
       </c>
       <c r="M165" t="n">
-        <v>0.007385</v>
+        <v>0.01096</v>
       </c>
       <c r="N165" t="n">
-        <v>0.2126</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="O165" t="n">
-        <v>0.01448</v>
+        <v>0.02207</v>
       </c>
       <c r="P165" t="n">
-        <v>0.2255</v>
+        <v>0.3621</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="B166" s="1" t="inlineStr">
-        <is>
-          <t>SFA</t>
-        </is>
-      </c>
+      <c r="A166" s="1" t="n"/>
+      <c r="B166" s="1" t="n"/>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>SFA-PW04-2024</t>
+          <t>SHA-PW04-2024</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.653</v>
+        <v>2.713</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3846</v>
+        <v>0.146</v>
       </c>
       <c r="F166" t="n">
-        <v>0.01954</v>
+        <v>119.8</v>
       </c>
       <c r="G166" t="n">
-        <v>23.13</v>
+        <v>5.504</v>
       </c>
       <c r="H166" t="n">
-        <v>1.663</v>
+        <v>2.652</v>
       </c>
       <c r="I166" t="n">
-        <v>2.694</v>
+        <v>2.166</v>
       </c>
       <c r="J166" t="n">
-        <v>0.3183</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="K166" t="n">
-        <v>0.9565</v>
+        <v>1.045</v>
       </c>
       <c r="L166" t="n">
-        <v>46.24</v>
+        <v>7.659</v>
       </c>
       <c r="M166" t="n">
-        <v>0.0162</v>
+        <v>0.005618</v>
       </c>
       <c r="N166" t="n">
-        <v>0.4161</v>
+        <v>0.03432</v>
       </c>
       <c r="O166" t="n">
-        <v>0.0236</v>
+        <v>0.009009</v>
       </c>
       <c r="P166" t="n">
-        <v>0.4105</v>
+        <v>0.07371</v>
       </c>
     </row>
     <row r="167">
@@ -8532,99 +8536,99 @@
       <c r="B167" s="1" t="n"/>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>SFA-PW16-2024</t>
+          <t>SHA-PW16-2024</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4.404</v>
+        <v>2.94</v>
       </c>
       <c r="E167" t="n">
-        <v>0.5484</v>
+        <v>0.6297</v>
       </c>
       <c r="F167" t="n">
-        <v>0.01638</v>
+        <v>95.78</v>
       </c>
       <c r="G167" t="n">
-        <v>18.49</v>
+        <v>14.88</v>
       </c>
       <c r="H167" t="n">
-        <v>2.966</v>
+        <v>4.232</v>
       </c>
       <c r="I167" t="n">
-        <v>3.266</v>
+        <v>1.176</v>
       </c>
       <c r="J167" t="n">
-        <v>0.4615</v>
+        <v>0.2275</v>
       </c>
       <c r="K167" t="n">
-        <v>1.076</v>
+        <v>0.6784</v>
       </c>
       <c r="L167" t="n">
-        <v>18.5</v>
+        <v>26.42</v>
       </c>
       <c r="M167" t="n">
-        <v>0.02546</v>
+        <v>0.009627</v>
       </c>
       <c r="N167" t="n">
-        <v>0.6829</v>
+        <v>0.2184</v>
       </c>
       <c r="O167" t="n">
-        <v>0.03856</v>
+        <v>0.0224</v>
       </c>
       <c r="P167" t="n">
-        <v>0.5037</v>
+        <v>0.7187</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n"/>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SHF</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>SHA-CtK04-2024</t>
+          <t>SHF-CmK98-2024</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2.329</v>
+        <v>2.178</v>
       </c>
       <c r="E168" t="n">
-        <v>0.5261</v>
+        <v>0.183</v>
       </c>
       <c r="F168" t="n">
-        <v>0.07627</v>
+        <v>153.8</v>
       </c>
       <c r="G168" t="n">
-        <v>12.29</v>
+        <v>3.479</v>
       </c>
       <c r="H168" t="n">
-        <v>4.281</v>
+        <v>5.259</v>
       </c>
       <c r="I168" t="n">
-        <v>1.279</v>
+        <v>1.335</v>
       </c>
       <c r="J168" t="n">
-        <v>0.3227</v>
+        <v>0.2486</v>
       </c>
       <c r="K168" t="n">
-        <v>0.8927</v>
+        <v>0.9616</v>
       </c>
       <c r="L168" t="n">
-        <v>17.61</v>
+        <v>29.92</v>
       </c>
       <c r="M168" t="n">
-        <v>0.007764</v>
+        <v>0.006766</v>
       </c>
       <c r="N168" t="n">
-        <v>0.1515</v>
+        <v>0.1258</v>
       </c>
       <c r="O168" t="n">
-        <v>0.01517</v>
+        <v>0.0112</v>
       </c>
       <c r="P168" t="n">
-        <v>0.3674</v>
+        <v>0.2692</v>
       </c>
     </row>
     <row r="169">
@@ -8632,47 +8636,47 @@
       <c r="B169" s="1" t="n"/>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>SHA-CtK15-2024</t>
+          <t>SHF-CtL00-2024</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2.19</v>
+        <v>2.991</v>
       </c>
       <c r="E169" t="n">
-        <v>1.206</v>
+        <v>0.3581</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1874</v>
+        <v>105.3</v>
       </c>
       <c r="G169" t="n">
-        <v>20.43</v>
+        <v>13.96</v>
       </c>
       <c r="H169" t="n">
-        <v>5.904</v>
+        <v>2.565</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9705</v>
+        <v>1.569</v>
       </c>
       <c r="J169" t="n">
-        <v>0.1514</v>
+        <v>0.3806</v>
       </c>
       <c r="K169" t="n">
-        <v>0.8298</v>
+        <v>0.88</v>
       </c>
       <c r="L169" t="n">
-        <v>39.65</v>
+        <v>18.7</v>
       </c>
       <c r="M169" t="n">
-        <v>0.00219</v>
+        <v>0.008279</v>
       </c>
       <c r="N169" t="n">
-        <v>0.251</v>
+        <v>0.1107</v>
       </c>
       <c r="O169" t="n">
-        <v>0.01486</v>
+        <v>0.01401</v>
       </c>
       <c r="P169" t="n">
-        <v>0.8178</v>
+        <v>0.2328</v>
       </c>
     </row>
     <row r="170">
@@ -8680,47 +8684,47 @@
       <c r="B170" s="1" t="n"/>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>SHA-CtV98-2024</t>
+          <t>SHF-Ctv98-2024</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2.197</v>
+        <v>2.198</v>
       </c>
       <c r="E170" t="n">
-        <v>0.2273</v>
+        <v>0.3225</v>
       </c>
       <c r="F170" t="n">
-        <v>0.03995</v>
+        <v>126.4</v>
       </c>
       <c r="G170" t="n">
-        <v>7.86</v>
+        <v>15.99</v>
       </c>
       <c r="H170" t="n">
-        <v>2.891</v>
+        <v>2.017</v>
       </c>
       <c r="I170" t="n">
-        <v>1.101</v>
+        <v>1.237</v>
       </c>
       <c r="J170" t="n">
-        <v>0.3604</v>
+        <v>0.2039</v>
       </c>
       <c r="K170" t="n">
-        <v>0.887</v>
+        <v>0.902</v>
       </c>
       <c r="L170" t="n">
-        <v>16.07</v>
+        <v>47.25</v>
       </c>
       <c r="M170" t="n">
-        <v>0.01096</v>
+        <v>0.005621</v>
       </c>
       <c r="N170" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1932</v>
       </c>
       <c r="O170" t="n">
-        <v>0.02207</v>
+        <v>0.01346</v>
       </c>
       <c r="P170" t="n">
-        <v>0.3621</v>
+        <v>0.4354</v>
       </c>
     </row>
     <row r="171">
@@ -8728,315 +8732,71 @@
       <c r="B171" s="1" t="n"/>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>SHA-PW04-2024</t>
+          <t>SHF-PW04-2024</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.713</v>
+        <v>3.382</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1459</v>
+        <v>0.2072</v>
       </c>
       <c r="F171" t="n">
-        <v>0.01501</v>
+        <v>115.5</v>
       </c>
       <c r="G171" t="n">
-        <v>5.504</v>
+        <v>4.598</v>
       </c>
       <c r="H171" t="n">
-        <v>2.652</v>
+        <v>4.505</v>
       </c>
       <c r="I171" t="n">
-        <v>2.166</v>
+        <v>3.081</v>
       </c>
       <c r="J171" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.3485</v>
       </c>
       <c r="K171" t="n">
-        <v>1.045</v>
+        <v>1.111</v>
       </c>
       <c r="L171" t="n">
-        <v>7.659</v>
+        <v>25.32</v>
       </c>
       <c r="M171" t="n">
-        <v>0.005618</v>
+        <v>0.007718</v>
       </c>
       <c r="N171" t="n">
-        <v>0.03432</v>
+        <v>0.2849</v>
       </c>
       <c r="O171" t="n">
-        <v>0.009009</v>
+        <v>0.01447</v>
       </c>
       <c r="P171" t="n">
-        <v>0.07371</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="n"/>
-      <c r="B172" s="1" t="n"/>
-      <c r="C172" s="1" t="inlineStr">
-        <is>
-          <t>SHA-PW16-2024</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0.6297</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0.07641000000000001</v>
-      </c>
-      <c r="G172" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="H172" t="n">
-        <v>4.232</v>
-      </c>
-      <c r="I172" t="n">
-        <v>1.176</v>
-      </c>
-      <c r="J172" t="n">
-        <v>0.2275</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0.6784</v>
-      </c>
-      <c r="L172" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="M172" t="n">
-        <v>0.009627</v>
-      </c>
-      <c r="N172" t="n">
-        <v>0.2184</v>
-      </c>
-      <c r="O172" t="n">
-        <v>0.0224</v>
-      </c>
-      <c r="P172" t="n">
-        <v>0.7187</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="n"/>
-      <c r="B173" s="1" t="inlineStr">
-        <is>
-          <t>SHF</t>
-        </is>
-      </c>
-      <c r="C173" s="1" t="inlineStr">
-        <is>
-          <t>SHF-CmK98-2024</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.1829</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.03157</v>
-      </c>
-      <c r="G173" t="n">
-        <v>3.479</v>
-      </c>
-      <c r="H173" t="n">
-        <v>5.258</v>
-      </c>
-      <c r="I173" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="J173" t="n">
-        <v>0.2486</v>
-      </c>
-      <c r="K173" t="n">
-        <v>0.9616</v>
-      </c>
-      <c r="L173" t="n">
-        <v>29.92</v>
-      </c>
-      <c r="M173" t="n">
-        <v>0.006766</v>
-      </c>
-      <c r="N173" t="n">
-        <v>0.1258</v>
-      </c>
-      <c r="O173" t="n">
-        <v>0.0112</v>
-      </c>
-      <c r="P173" t="n">
-        <v>0.2692</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="n"/>
-      <c r="B174" s="1" t="n"/>
-      <c r="C174" s="1" t="inlineStr">
-        <is>
-          <t>SHF-CtL00-2024</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>2.991</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0.3581</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.03917</v>
-      </c>
-      <c r="G174" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="H174" t="n">
-        <v>2.565</v>
-      </c>
-      <c r="I174" t="n">
-        <v>1.569</v>
-      </c>
-      <c r="J174" t="n">
-        <v>0.3806</v>
-      </c>
-      <c r="K174" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L174" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M174" t="n">
-        <v>0.008279</v>
-      </c>
-      <c r="N174" t="n">
-        <v>0.1107</v>
-      </c>
-      <c r="O174" t="n">
-        <v>0.01401</v>
-      </c>
-      <c r="P174" t="n">
-        <v>0.2328</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="n"/>
-      <c r="B175" s="1" t="n"/>
-      <c r="C175" s="1" t="inlineStr">
-        <is>
-          <t>SHF-Ctv98-2024</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>2.198</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.3225</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.05493</v>
-      </c>
-      <c r="G175" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="H175" t="n">
-        <v>2.017</v>
-      </c>
-      <c r="I175" t="n">
-        <v>1.237</v>
-      </c>
-      <c r="J175" t="n">
-        <v>0.2039</v>
-      </c>
-      <c r="K175" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="L175" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="M175" t="n">
-        <v>0.005621</v>
-      </c>
-      <c r="N175" t="n">
-        <v>0.1932</v>
-      </c>
-      <c r="O175" t="n">
-        <v>0.01346</v>
-      </c>
-      <c r="P175" t="n">
-        <v>0.4354</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="1" t="n"/>
-      <c r="B176" s="1" t="n"/>
-      <c r="C176" s="1" t="inlineStr">
-        <is>
-          <t>SHF-PW04-2024</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>3.382</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0.2071</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0.01563</v>
-      </c>
-      <c r="G176" t="n">
-        <v>4.598</v>
-      </c>
-      <c r="H176" t="n">
-        <v>4.505</v>
-      </c>
-      <c r="I176" t="n">
-        <v>3.081</v>
-      </c>
-      <c r="J176" t="n">
-        <v>0.3485</v>
-      </c>
-      <c r="K176" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="L176" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="M176" t="n">
-        <v>0.007718</v>
-      </c>
-      <c r="N176" t="n">
-        <v>0.2849</v>
-      </c>
-      <c r="O176" t="n">
-        <v>0.01447</v>
-      </c>
-      <c r="P176" t="n">
         <v>0.2081</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B153:B156"/>
     <mergeCell ref="B31:B45"/>
-    <mergeCell ref="A82:A151"/>
     <mergeCell ref="B11:B21"/>
     <mergeCell ref="A78:A81"/>
-    <mergeCell ref="B168:B172"/>
-    <mergeCell ref="A152:A165"/>
-    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="B161:B162"/>
     <mergeCell ref="B157:B160"/>
     <mergeCell ref="B46:B64"/>
     <mergeCell ref="B79:B81"/>
+    <mergeCell ref="B163:B167"/>
     <mergeCell ref="B82:B140"/>
     <mergeCell ref="B65:B77"/>
+    <mergeCell ref="B141:B147"/>
+    <mergeCell ref="B168:B171"/>
+    <mergeCell ref="A161:A171"/>
     <mergeCell ref="B22:B30"/>
-    <mergeCell ref="B141:B151"/>
-    <mergeCell ref="B161:B165"/>
-    <mergeCell ref="B152:B156"/>
+    <mergeCell ref="A82:A147"/>
     <mergeCell ref="A2:A77"/>
-    <mergeCell ref="B173:B176"/>
+    <mergeCell ref="A148:A160"/>
     <mergeCell ref="B2:B10"/>
-    <mergeCell ref="A166:A176"/>
+    <mergeCell ref="B148:B152"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
+++ b/Server/Received_data/Statistics/2024/Documents/Исходные данные за 2024 год.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N186"/>
+  <dimension ref="A1:N187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7058,41 +7058,41 @@
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>LST-L-SPB wosalt-2024</t>
+          <t>LG-LST-30-2024</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>10.34</v>
+        <v>14.97</v>
       </c>
       <c r="E156" t="n">
-        <v>0.152</v>
+        <v>0.8712</v>
       </c>
       <c r="F156" t="n">
-        <v>3.744</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="G156" t="n">
-        <v>4.061</v>
+        <v>1.341</v>
       </c>
       <c r="H156" t="n">
-        <v>13.83</v>
+        <v>13.59</v>
       </c>
       <c r="I156" t="n">
-        <v>5.092</v>
+        <v>4.827</v>
       </c>
       <c r="J156" t="n">
-        <v>2.41</v>
+        <v>2.221</v>
       </c>
       <c r="K156" t="n">
-        <v>4.022</v>
+        <v>5.282</v>
       </c>
       <c r="L156" t="n">
-        <v>0.1735</v>
+        <v>0.6131</v>
       </c>
       <c r="M156" t="n">
-        <v>0.01356</v>
+        <v>0.1315</v>
       </c>
       <c r="N156" t="n">
-        <v>0.1535</v>
+        <v>0.3767</v>
       </c>
     </row>
     <row r="157">
@@ -7100,41 +7100,41 @@
       <c r="B157" s="1" t="n"/>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>LST-L-Syas wosalt-2024</t>
+          <t>LST-L-SPB wosalt-2024</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6.935</v>
+        <v>10.34</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2413</v>
+        <v>0.152</v>
       </c>
       <c r="F157" t="n">
-        <v>4.845</v>
+        <v>3.744</v>
       </c>
       <c r="G157" t="n">
-        <v>4.981</v>
+        <v>4.061</v>
       </c>
       <c r="H157" t="n">
-        <v>6.302</v>
+        <v>13.83</v>
       </c>
       <c r="I157" t="n">
-        <v>3.397</v>
+        <v>5.092</v>
       </c>
       <c r="J157" t="n">
-        <v>1.81</v>
+        <v>2.41</v>
       </c>
       <c r="K157" t="n">
-        <v>4.063</v>
+        <v>4.022</v>
       </c>
       <c r="L157" t="n">
-        <v>0.1339</v>
+        <v>0.1735</v>
       </c>
       <c r="M157" t="n">
-        <v>0.1068</v>
+        <v>0.01356</v>
       </c>
       <c r="N157" t="n">
-        <v>0.1315</v>
+        <v>0.1535</v>
       </c>
     </row>
     <row r="158">
@@ -7142,41 +7142,41 @@
       <c r="B158" s="1" t="n"/>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>LST-L-VLK wosalt-2024</t>
+          <t>LST-L-Syas wosalt-2024</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>13.71</v>
+        <v>6.935</v>
       </c>
       <c r="E158" t="n">
-        <v>0.1782</v>
+        <v>0.2413</v>
       </c>
       <c r="F158" t="n">
-        <v>4.678</v>
+        <v>4.845</v>
       </c>
       <c r="G158" t="n">
-        <v>3.809</v>
+        <v>4.981</v>
       </c>
       <c r="H158" t="n">
-        <v>13.44</v>
+        <v>6.302</v>
       </c>
       <c r="I158" t="n">
-        <v>5.113</v>
+        <v>3.397</v>
       </c>
       <c r="J158" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="K158" t="n">
-        <v>4.015</v>
+        <v>4.063</v>
       </c>
       <c r="L158" t="n">
-        <v>0.244</v>
+        <v>0.1339</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>0.1068</v>
       </c>
       <c r="N158" t="n">
-        <v>0.2197</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="159">
@@ -7184,41 +7184,41 @@
       <c r="B159" s="1" t="n"/>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>LST-S-SBP-2024</t>
+          <t>LST-L-VLK wosalt-2024</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>12.34</v>
+        <v>13.71</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1112</v>
+        <v>0.1782</v>
       </c>
       <c r="F159" t="n">
-        <v>27.78</v>
+        <v>4.678</v>
       </c>
       <c r="G159" t="n">
-        <v>0.4002</v>
+        <v>3.809</v>
       </c>
       <c r="H159" t="n">
-        <v>20.04</v>
+        <v>13.44</v>
       </c>
       <c r="I159" t="n">
-        <v>5.513</v>
+        <v>5.113</v>
       </c>
       <c r="J159" t="n">
-        <v>3.185</v>
+        <v>2.35</v>
       </c>
       <c r="K159" t="n">
-        <v>3.282</v>
+        <v>4.015</v>
       </c>
       <c r="L159" t="n">
-        <v>0.7313</v>
+        <v>0.244</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>0.6957</v>
+        <v>0.2197</v>
       </c>
     </row>
     <row r="160">
@@ -7226,41 +7226,41 @@
       <c r="B160" s="1" t="n"/>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>LST-S-SOKOL-2024</t>
+          <t>LST-S-SBP-2024</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>8.74</v>
+        <v>12.34</v>
       </c>
       <c r="E160" t="n">
-        <v>0.07364999999999999</v>
+        <v>0.1112</v>
       </c>
       <c r="F160" t="n">
-        <v>17.87</v>
+        <v>27.78</v>
       </c>
       <c r="G160" t="n">
-        <v>0.4121</v>
+        <v>0.4002</v>
       </c>
       <c r="H160" t="n">
-        <v>17.72</v>
+        <v>20.04</v>
       </c>
       <c r="I160" t="n">
-        <v>5.234</v>
+        <v>5.513</v>
       </c>
       <c r="J160" t="n">
-        <v>2.909</v>
+        <v>3.185</v>
       </c>
       <c r="K160" t="n">
-        <v>3.448</v>
+        <v>3.282</v>
       </c>
       <c r="L160" t="n">
-        <v>0.6249</v>
+        <v>0.7313</v>
       </c>
       <c r="M160" t="n">
-        <v>0.01151</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>0.5878</v>
+        <v>0.6957</v>
       </c>
     </row>
     <row r="161">
@@ -7268,41 +7268,41 @@
       <c r="B161" s="1" t="n"/>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>LST-S-SYAS-2024</t>
+          <t>LST-S-SOKOL-2024</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>6.19</v>
+        <v>8.74</v>
       </c>
       <c r="E161" t="n">
-        <v>0.06693</v>
+        <v>0.07364999999999999</v>
       </c>
       <c r="F161" t="n">
-        <v>21.31</v>
+        <v>17.87</v>
       </c>
       <c r="G161" t="n">
-        <v>0.3141</v>
+        <v>0.4121</v>
       </c>
       <c r="H161" t="n">
-        <v>6.15</v>
+        <v>17.72</v>
       </c>
       <c r="I161" t="n">
-        <v>3.06</v>
+        <v>5.234</v>
       </c>
       <c r="J161" t="n">
-        <v>1.652</v>
+        <v>2.909</v>
       </c>
       <c r="K161" t="n">
-        <v>4.407</v>
+        <v>3.448</v>
       </c>
       <c r="L161" t="n">
-        <v>0.3881</v>
+        <v>0.6249</v>
       </c>
       <c r="M161" t="n">
-        <v>0.4465</v>
+        <v>0.01151</v>
       </c>
       <c r="N161" t="n">
-        <v>0.4303</v>
+        <v>0.5878</v>
       </c>
     </row>
     <row r="162">
@@ -7310,133 +7310,133 @@
       <c r="B162" s="1" t="n"/>
       <c r="C162" s="1" t="inlineStr">
         <is>
+          <t>LST-S-SYAS-2024</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.06693</v>
+      </c>
+      <c r="F162" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="H162" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I162" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="K162" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0.4303</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n"/>
+      <c r="B163" s="1" t="n"/>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
           <t>LST-S-VLK-2024</t>
         </is>
       </c>
-      <c r="D162" t="n">
+      <c r="D163" t="n">
         <v>10.65</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E163" t="n">
         <v>0.1869</v>
       </c>
-      <c r="F162" t="n">
+      <c r="F163" t="n">
         <v>49.88</v>
       </c>
-      <c r="G162" t="n">
+      <c r="G163" t="n">
         <v>0.3747</v>
       </c>
-      <c r="H162" t="n">
+      <c r="H163" t="n">
         <v>16.39</v>
       </c>
-      <c r="I162" t="n">
+      <c r="I163" t="n">
         <v>4.664</v>
       </c>
-      <c r="J162" t="n">
+      <c r="J163" t="n">
         <v>2.772</v>
       </c>
-      <c r="K162" t="n">
+      <c r="K163" t="n">
         <v>4.541</v>
       </c>
-      <c r="L162" t="n">
+      <c r="L163" t="n">
         <v>1</v>
       </c>
-      <c r="M162" t="n">
+      <c r="M163" t="n">
         <v>0.1883</v>
       </c>
-      <c r="N162" t="n">
+      <c r="N163" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
         <is>
           <t>Peat</t>
         </is>
       </c>
-      <c r="B163" s="1" t="inlineStr">
+      <c r="B164" s="1" t="inlineStr">
         <is>
           <t>PFA</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t>PFA-Sk3-00-2024</t>
         </is>
       </c>
-      <c r="D163" t="n">
+      <c r="D164" t="n">
         <v>4.12</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E164" t="n">
         <v>0.4922</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F164" t="n">
         <v>20.37</v>
       </c>
-      <c r="G163" t="n">
+      <c r="G164" t="n">
         <v>2.416</v>
       </c>
-      <c r="H163" t="n">
+      <c r="H164" t="n">
         <v>3.456</v>
       </c>
-      <c r="I163" t="n">
+      <c r="I164" t="n">
         <v>0.3283</v>
       </c>
-      <c r="J163" t="n">
+      <c r="J164" t="n">
         <v>1.163</v>
       </c>
-      <c r="K163" t="n">
+      <c r="K164" t="n">
         <v>39.39</v>
       </c>
-      <c r="L163" t="n">
+      <c r="L164" t="n">
         <v>0.01896</v>
       </c>
-      <c r="M163" t="n">
+      <c r="M164" t="n">
         <v>0.7989000000000001</v>
       </c>
-      <c r="N163" t="n">
+      <c r="N164" t="n">
         <v>0.04981</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="n"/>
-      <c r="B164" s="1" t="n"/>
-      <c r="C164" s="1" t="inlineStr">
-        <is>
-          <t>PFA-T1098-2024</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>3.984</v>
-      </c>
-      <c r="E164" t="n">
-        <v>0.5406</v>
-      </c>
-      <c r="F164" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G164" t="n">
-        <v>2.189</v>
-      </c>
-      <c r="H164" t="n">
-        <v>3.422</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0.3552</v>
-      </c>
-      <c r="J164" t="n">
-        <v>1.104</v>
-      </c>
-      <c r="K164" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="L164" t="n">
-        <v>0.02793</v>
-      </c>
-      <c r="M164" t="n">
-        <v>0.9248</v>
-      </c>
-      <c r="N164" t="n">
-        <v>0.06807000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -7444,41 +7444,41 @@
       <c r="B165" s="1" t="n"/>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>PFA-T598-2024</t>
+          <t>PFA-T1098-2024</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3.861</v>
+        <v>3.984</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4808</v>
+        <v>0.5406</v>
       </c>
       <c r="F165" t="n">
-        <v>21.18</v>
+        <v>24.7</v>
       </c>
       <c r="G165" t="n">
-        <v>2.27</v>
+        <v>2.189</v>
       </c>
       <c r="H165" t="n">
-        <v>3.326</v>
+        <v>3.422</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>0.3552</v>
       </c>
       <c r="J165" t="n">
-        <v>1.103</v>
+        <v>1.104</v>
       </c>
       <c r="K165" t="n">
-        <v>23.19</v>
+        <v>47.43</v>
       </c>
       <c r="L165" t="n">
-        <v>0.01788</v>
+        <v>0.02793</v>
       </c>
       <c r="M165" t="n">
-        <v>0.6343</v>
+        <v>0.9248</v>
       </c>
       <c r="N165" t="n">
-        <v>0.04712</v>
+        <v>0.06807000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -7486,41 +7486,41 @@
       <c r="B166" s="1" t="n"/>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>PFA-T5H98-2024</t>
+          <t>PFA-T598-2024</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3.806</v>
+        <v>3.861</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3614</v>
+        <v>0.4808</v>
       </c>
       <c r="F166" t="n">
-        <v>23.11</v>
+        <v>21.18</v>
       </c>
       <c r="G166" t="n">
-        <v>1.564</v>
+        <v>2.27</v>
       </c>
       <c r="H166" t="n">
-        <v>3.566</v>
+        <v>3.326</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4333</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
-        <v>1.176</v>
+        <v>1.103</v>
       </c>
       <c r="K166" t="n">
-        <v>39.53</v>
+        <v>23.19</v>
       </c>
       <c r="L166" t="n">
-        <v>0.01455</v>
+        <v>0.01788</v>
       </c>
       <c r="M166" t="n">
-        <v>0.6151</v>
+        <v>0.6343</v>
       </c>
       <c r="N166" t="n">
-        <v>0.04911</v>
+        <v>0.04712</v>
       </c>
     </row>
     <row r="167">
@@ -7528,129 +7528,129 @@
       <c r="B167" s="1" t="n"/>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>PFA-T698-2024</t>
+          <t>PFA-T5H98-2024</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3.612</v>
+        <v>3.806</v>
       </c>
       <c r="E167" t="n">
-        <v>0.4165</v>
+        <v>0.3614</v>
       </c>
       <c r="F167" t="n">
-        <v>24.08</v>
+        <v>23.11</v>
       </c>
       <c r="G167" t="n">
-        <v>1.73</v>
+        <v>1.564</v>
       </c>
       <c r="H167" t="n">
-        <v>3.449</v>
+        <v>3.566</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4345</v>
+        <v>0.4333</v>
       </c>
       <c r="J167" t="n">
-        <v>1.148</v>
+        <v>1.176</v>
       </c>
       <c r="K167" t="n">
-        <v>43.54</v>
+        <v>39.53</v>
       </c>
       <c r="L167" t="n">
-        <v>0.01212</v>
+        <v>0.01455</v>
       </c>
       <c r="M167" t="n">
-        <v>0.5208</v>
+        <v>0.6151</v>
       </c>
       <c r="N167" t="n">
-        <v>0.04079</v>
+        <v>0.04911</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n"/>
-      <c r="B168" s="1" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
+      <c r="B168" s="1" t="n"/>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>PHA-Sk3-00-2024</t>
+          <t>PFA-T698-2024</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2.921</v>
+        <v>3.612</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2902</v>
+        <v>0.4165</v>
       </c>
       <c r="F168" t="n">
-        <v>20.37</v>
+        <v>24.08</v>
       </c>
       <c r="G168" t="n">
-        <v>1.425</v>
+        <v>1.73</v>
       </c>
       <c r="H168" t="n">
-        <v>2.398</v>
+        <v>3.449</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4345</v>
       </c>
       <c r="J168" t="n">
-        <v>1.036</v>
+        <v>1.148</v>
       </c>
       <c r="K168" t="n">
-        <v>14.04</v>
+        <v>43.54</v>
       </c>
       <c r="L168" t="n">
-        <v>0.006603</v>
+        <v>0.01212</v>
       </c>
       <c r="M168" t="n">
-        <v>0.2076</v>
+        <v>0.5208</v>
       </c>
       <c r="N168" t="n">
-        <v>0.01327</v>
+        <v>0.04079</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n"/>
-      <c r="B169" s="1" t="n"/>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>PHA</t>
+        </is>
+      </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>PHA-T598-2024</t>
+          <t>PHA-Sk3-00-2024</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2.633</v>
+        <v>2.921</v>
       </c>
       <c r="E169" t="n">
-        <v>0.659</v>
+        <v>0.2902</v>
       </c>
       <c r="F169" t="n">
-        <v>17.8</v>
+        <v>20.37</v>
       </c>
       <c r="G169" t="n">
-        <v>3.702</v>
+        <v>1.425</v>
       </c>
       <c r="H169" t="n">
-        <v>2.017</v>
+        <v>2.398</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8227</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>1.016</v>
+        <v>1.036</v>
       </c>
       <c r="K169" t="n">
-        <v>6.519</v>
+        <v>14.04</v>
       </c>
       <c r="L169" t="n">
-        <v>0.009731</v>
+        <v>0.006603</v>
       </c>
       <c r="M169" t="n">
-        <v>0.1592</v>
+        <v>0.2076</v>
       </c>
       <c r="N169" t="n">
-        <v>0.01163</v>
+        <v>0.01327</v>
       </c>
     </row>
     <row r="170">
@@ -7658,41 +7658,41 @@
       <c r="B170" s="1" t="n"/>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>PHA-T698-2024</t>
+          <t>PHA-T598-2024</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2.437</v>
+        <v>2.633</v>
       </c>
       <c r="E170" t="n">
-        <v>0.6341</v>
+        <v>0.659</v>
       </c>
       <c r="F170" t="n">
-        <v>22.43</v>
+        <v>17.8</v>
       </c>
       <c r="G170" t="n">
-        <v>2.827</v>
+        <v>3.702</v>
       </c>
       <c r="H170" t="n">
-        <v>1.737</v>
+        <v>2.017</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7543</v>
+        <v>0.8227</v>
       </c>
       <c r="J170" t="n">
-        <v>0.9704</v>
+        <v>1.016</v>
       </c>
       <c r="K170" t="n">
-        <v>8.807</v>
+        <v>6.519</v>
       </c>
       <c r="L170" t="n">
-        <v>0.009506000000000001</v>
+        <v>0.009731</v>
       </c>
       <c r="M170" t="n">
-        <v>0.1463</v>
+        <v>0.1592</v>
       </c>
       <c r="N170" t="n">
-        <v>0.01804</v>
+        <v>0.01163</v>
       </c>
     </row>
     <row r="171">
@@ -7700,129 +7700,129 @@
       <c r="B171" s="1" t="n"/>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>PHA-TTL98-2024</t>
+          <t>PHA-T698-2024</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.655</v>
+        <v>2.437</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7224</v>
+        <v>0.6341</v>
       </c>
       <c r="F171" t="n">
-        <v>18.37</v>
+        <v>22.43</v>
       </c>
       <c r="G171" t="n">
-        <v>3.932</v>
+        <v>2.827</v>
       </c>
       <c r="H171" t="n">
-        <v>2.009</v>
+        <v>1.737</v>
       </c>
       <c r="I171" t="n">
-        <v>0.681</v>
+        <v>0.7543</v>
       </c>
       <c r="J171" t="n">
-        <v>0.9859</v>
+        <v>0.9704</v>
       </c>
       <c r="K171" t="n">
-        <v>10.83</v>
+        <v>8.807</v>
       </c>
       <c r="L171" t="n">
-        <v>0.01036</v>
+        <v>0.009506000000000001</v>
       </c>
       <c r="M171" t="n">
-        <v>0.1898</v>
+        <v>0.1463</v>
       </c>
       <c r="N171" t="n">
-        <v>0.02031</v>
+        <v>0.01804</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n"/>
-      <c r="B172" s="1" t="inlineStr">
-        <is>
-          <t>PHF</t>
-        </is>
-      </c>
+      <c r="B172" s="1" t="n"/>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>PHF-Sk300-2024</t>
+          <t>PHA-TTL98-2024</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2.988</v>
+        <v>2.655</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8065</v>
+        <v>0.7224</v>
       </c>
       <c r="F172" t="n">
-        <v>17.29</v>
+        <v>18.37</v>
       </c>
       <c r="G172" t="n">
-        <v>4.665</v>
+        <v>3.932</v>
       </c>
       <c r="H172" t="n">
-        <v>2.161</v>
+        <v>2.009</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3623</v>
+        <v>0.681</v>
       </c>
       <c r="J172" t="n">
-        <v>1.002</v>
+        <v>0.9859</v>
       </c>
       <c r="K172" t="n">
-        <v>14.89</v>
+        <v>10.83</v>
       </c>
       <c r="L172" t="n">
-        <v>0.008003</v>
+        <v>0.01036</v>
       </c>
       <c r="M172" t="n">
-        <v>0.3704</v>
+        <v>0.1898</v>
       </c>
       <c r="N172" t="n">
-        <v>0.01591</v>
+        <v>0.02031</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n"/>
-      <c r="B173" s="1" t="n"/>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>PHF</t>
+        </is>
+      </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>PHF-T10L98-2024</t>
+          <t>PHF-Sk300-2024</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3.044</v>
+        <v>2.988</v>
       </c>
       <c r="E173" t="n">
-        <v>0.4048</v>
+        <v>0.8065</v>
       </c>
       <c r="F173" t="n">
-        <v>16.62</v>
+        <v>17.29</v>
       </c>
       <c r="G173" t="n">
-        <v>2.436</v>
+        <v>4.665</v>
       </c>
       <c r="H173" t="n">
-        <v>2.417</v>
+        <v>2.161</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4001</v>
+        <v>0.3623</v>
       </c>
       <c r="J173" t="n">
-        <v>1.018</v>
+        <v>1.002</v>
       </c>
       <c r="K173" t="n">
-        <v>19.65</v>
+        <v>14.89</v>
       </c>
       <c r="L173" t="n">
-        <v>0.00716</v>
+        <v>0.008003</v>
       </c>
       <c r="M173" t="n">
-        <v>0.2534</v>
+        <v>0.3704</v>
       </c>
       <c r="N173" t="n">
-        <v>0.01694</v>
+        <v>0.01591</v>
       </c>
     </row>
     <row r="174">
@@ -7830,41 +7830,41 @@
       <c r="B174" s="1" t="n"/>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>PHF-T698-2024</t>
+          <t>PHF-T10L98-2024</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2.64</v>
+        <v>3.044</v>
       </c>
       <c r="E174" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.4048</v>
       </c>
       <c r="F174" t="n">
-        <v>15.6</v>
+        <v>16.62</v>
       </c>
       <c r="G174" t="n">
-        <v>3.493</v>
+        <v>2.436</v>
       </c>
       <c r="H174" t="n">
-        <v>2.429</v>
+        <v>2.417</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5766</v>
+        <v>0.4001</v>
       </c>
       <c r="J174" t="n">
-        <v>1.084</v>
+        <v>1.018</v>
       </c>
       <c r="K174" t="n">
-        <v>15.2</v>
+        <v>19.65</v>
       </c>
       <c r="L174" t="n">
-        <v>0.005839</v>
+        <v>0.00716</v>
       </c>
       <c r="M174" t="n">
-        <v>0.158</v>
+        <v>0.2534</v>
       </c>
       <c r="N174" t="n">
-        <v>0.01392</v>
+        <v>0.01694</v>
       </c>
     </row>
     <row r="175">
@@ -7872,221 +7872,221 @@
       <c r="B175" s="1" t="n"/>
       <c r="C175" s="1" t="inlineStr">
         <is>
+          <t>PHF-T698-2024</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.5449000000000001</v>
+      </c>
+      <c r="F175" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G175" t="n">
+        <v>3.493</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K175" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.005839</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.01392</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n"/>
+      <c r="B176" s="1" t="n"/>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
           <t>PHF-T7H98-2024</t>
         </is>
       </c>
-      <c r="D175" t="n">
+      <c r="D176" t="n">
         <v>2.76</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E176" t="n">
         <v>0.55</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F176" t="n">
         <v>14.55</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G176" t="n">
         <v>3.78</v>
       </c>
-      <c r="H175" t="n">
+      <c r="H176" t="n">
         <v>2.66</v>
       </c>
-      <c r="I175" t="n">
+      <c r="I176" t="n">
         <v>0.5457</v>
       </c>
-      <c r="J175" t="n">
+      <c r="J176" t="n">
         <v>1.101</v>
       </c>
-      <c r="K175" t="n">
+      <c r="K176" t="n">
         <v>14.81</v>
       </c>
-      <c r="L175" t="n">
+      <c r="L176" t="n">
         <v>0.009882999999999999</v>
       </c>
-      <c r="M175" t="n">
+      <c r="M176" t="n">
         <v>0.2254</v>
       </c>
-      <c r="N175" t="n">
+      <c r="N176" t="n">
         <v>0.01623</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
         <is>
           <t>Soil</t>
         </is>
       </c>
-      <c r="B176" s="1" t="inlineStr">
+      <c r="B177" s="1" t="inlineStr">
         <is>
           <t>SFA</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C177" s="1" t="inlineStr">
         <is>
           <t>SFA-PW04-2024</t>
         </is>
       </c>
-      <c r="D176" t="n">
+      <c r="D177" t="n">
         <v>3.653</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E177" t="n">
         <v>0.3846</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F177" t="n">
         <v>23.13</v>
       </c>
-      <c r="G176" t="n">
+      <c r="G177" t="n">
         <v>1.663</v>
       </c>
-      <c r="H176" t="n">
+      <c r="H177" t="n">
         <v>2.694</v>
       </c>
-      <c r="I176" t="n">
+      <c r="I177" t="n">
         <v>0.3183</v>
       </c>
-      <c r="J176" t="n">
+      <c r="J177" t="n">
         <v>0.9565</v>
       </c>
-      <c r="K176" t="n">
+      <c r="K177" t="n">
         <v>46.24</v>
       </c>
-      <c r="L176" t="n">
+      <c r="L177" t="n">
         <v>0.01241</v>
       </c>
-      <c r="M176" t="n">
+      <c r="M177" t="n">
         <v>0.5299</v>
       </c>
-      <c r="N176" t="n">
+      <c r="N177" t="n">
         <v>0.02466</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="n"/>
-      <c r="B177" s="1" t="n"/>
-      <c r="C177" s="1" t="inlineStr">
-        <is>
-          <t>SFA-PW16-2024</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>4.403</v>
-      </c>
-      <c r="E177" t="n">
-        <v>0.5484</v>
-      </c>
-      <c r="F177" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="G177" t="n">
-        <v>2.966</v>
-      </c>
-      <c r="H177" t="n">
-        <v>3.266</v>
-      </c>
-      <c r="I177" t="n">
-        <v>0.4615</v>
-      </c>
-      <c r="J177" t="n">
-        <v>1.076</v>
-      </c>
-      <c r="K177" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L177" t="n">
-        <v>0.02223</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0.7398</v>
-      </c>
-      <c r="N177" t="n">
-        <v>0.04592</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n"/>
-      <c r="B178" s="1" t="inlineStr">
-        <is>
-          <t>SHA</t>
-        </is>
-      </c>
+      <c r="B178" s="1" t="n"/>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>SHA-CtK04-2024</t>
+          <t>SFA-PW16-2024</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2.329</v>
+        <v>4.403</v>
       </c>
       <c r="E178" t="n">
-        <v>0.5261</v>
+        <v>0.5484</v>
       </c>
       <c r="F178" t="n">
-        <v>12.29</v>
+        <v>18.49</v>
       </c>
       <c r="G178" t="n">
-        <v>4.281</v>
+        <v>2.966</v>
       </c>
       <c r="H178" t="n">
-        <v>1.279</v>
+        <v>3.266</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3227</v>
+        <v>0.4615</v>
       </c>
       <c r="J178" t="n">
-        <v>0.8927</v>
+        <v>1.076</v>
       </c>
       <c r="K178" t="n">
-        <v>17.61</v>
+        <v>18.5</v>
       </c>
       <c r="L178" t="n">
-        <v>0.003058</v>
+        <v>0.02223</v>
       </c>
       <c r="M178" t="n">
-        <v>0.3585</v>
+        <v>0.7398</v>
       </c>
       <c r="N178" t="n">
-        <v>0.007945000000000001</v>
+        <v>0.04592</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n"/>
-      <c r="B179" s="1" t="n"/>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>SHA</t>
+        </is>
+      </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>SHA-CtK15-2024</t>
+          <t>SHA-CtK04-2024</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2.19</v>
+        <v>2.329</v>
       </c>
       <c r="E179" t="n">
-        <v>1.206</v>
+        <v>0.5261</v>
       </c>
       <c r="F179" t="n">
-        <v>20.43</v>
+        <v>12.29</v>
       </c>
       <c r="G179" t="n">
-        <v>5.904</v>
+        <v>4.281</v>
       </c>
       <c r="H179" t="n">
-        <v>0.9705</v>
+        <v>1.279</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1514</v>
+        <v>0.3227</v>
       </c>
       <c r="J179" t="n">
-        <v>0.8298</v>
+        <v>0.8927</v>
       </c>
       <c r="K179" t="n">
-        <v>39.65</v>
+        <v>17.61</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>0.003058</v>
       </c>
       <c r="M179" t="n">
-        <v>0.7294</v>
+        <v>0.3585</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>0.007945000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -8094,41 +8094,41 @@
       <c r="B180" s="1" t="n"/>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>SHA-CtV98-2024</t>
+          <t>SHA-CtK15-2024</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.197</v>
+        <v>2.19</v>
       </c>
       <c r="E180" t="n">
-        <v>0.2273</v>
+        <v>1.206</v>
       </c>
       <c r="F180" t="n">
-        <v>7.86</v>
+        <v>20.43</v>
       </c>
       <c r="G180" t="n">
-        <v>2.892</v>
+        <v>5.904</v>
       </c>
       <c r="H180" t="n">
-        <v>1.101</v>
+        <v>0.9705</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3604</v>
+        <v>0.1514</v>
       </c>
       <c r="J180" t="n">
-        <v>0.887</v>
+        <v>0.8298</v>
       </c>
       <c r="K180" t="n">
-        <v>16.07</v>
+        <v>39.65</v>
       </c>
       <c r="L180" t="n">
-        <v>0.00623</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>0.323</v>
+        <v>0.7294</v>
       </c>
       <c r="N180" t="n">
-        <v>0.01271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -8136,41 +8136,41 @@
       <c r="B181" s="1" t="n"/>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>SHA-PW04-2024</t>
+          <t>SHA-CtV98-2024</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2.713</v>
+        <v>2.197</v>
       </c>
       <c r="E181" t="n">
-        <v>0.146</v>
+        <v>0.2273</v>
       </c>
       <c r="F181" t="n">
-        <v>5.504</v>
+        <v>7.86</v>
       </c>
       <c r="G181" t="n">
-        <v>2.652</v>
+        <v>2.892</v>
       </c>
       <c r="H181" t="n">
-        <v>2.166</v>
+        <v>1.101</v>
       </c>
       <c r="I181" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.3604</v>
       </c>
       <c r="J181" t="n">
-        <v>1.045</v>
+        <v>0.887</v>
       </c>
       <c r="K181" t="n">
-        <v>7.659</v>
+        <v>16.07</v>
       </c>
       <c r="L181" t="n">
-        <v>0.0047</v>
+        <v>0.00623</v>
       </c>
       <c r="M181" t="n">
-        <v>0.07239</v>
+        <v>0.323</v>
       </c>
       <c r="N181" t="n">
-        <v>0.008218</v>
+        <v>0.01271</v>
       </c>
     </row>
     <row r="182">
@@ -8178,129 +8178,129 @@
       <c r="B182" s="1" t="n"/>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>SHA-PW16-2024</t>
+          <t>SHA-PW04-2024</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2.94</v>
+        <v>2.713</v>
       </c>
       <c r="E182" t="n">
-        <v>0.6297</v>
+        <v>0.146</v>
       </c>
       <c r="F182" t="n">
-        <v>14.88</v>
+        <v>5.504</v>
       </c>
       <c r="G182" t="n">
-        <v>4.232</v>
+        <v>2.652</v>
       </c>
       <c r="H182" t="n">
-        <v>1.176</v>
+        <v>2.166</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2275</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>0.6784</v>
+        <v>1.045</v>
       </c>
       <c r="K182" t="n">
-        <v>26.42</v>
+        <v>7.659</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="M182" t="n">
-        <v>0.6607</v>
+        <v>0.07239</v>
       </c>
       <c r="N182" t="n">
-        <v>0.005181</v>
+        <v>0.008218</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n"/>
-      <c r="B183" s="1" t="inlineStr">
-        <is>
-          <t>SHF</t>
-        </is>
-      </c>
+      <c r="B183" s="1" t="n"/>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>SHF-CmK98-2024</t>
+          <t>SHA-PW16-2024</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2.178</v>
+        <v>2.94</v>
       </c>
       <c r="E183" t="n">
-        <v>0.183</v>
+        <v>0.6297</v>
       </c>
       <c r="F183" t="n">
-        <v>3.479</v>
+        <v>14.88</v>
       </c>
       <c r="G183" t="n">
-        <v>5.259</v>
+        <v>4.232</v>
       </c>
       <c r="H183" t="n">
-        <v>1.335</v>
+        <v>1.176</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2486</v>
+        <v>0.2275</v>
       </c>
       <c r="J183" t="n">
-        <v>0.9616</v>
+        <v>0.6784</v>
       </c>
       <c r="K183" t="n">
-        <v>29.92</v>
+        <v>26.42</v>
       </c>
       <c r="L183" t="n">
-        <v>0.003274</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>0.2702</v>
+        <v>0.6607</v>
       </c>
       <c r="N183" t="n">
-        <v>0.006713</v>
+        <v>0.005181</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n"/>
-      <c r="B184" s="1" t="n"/>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>SHF</t>
+        </is>
+      </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>SHF-CtL00-2024</t>
+          <t>SHF-CmK98-2024</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>2.991</v>
+        <v>2.178</v>
       </c>
       <c r="E184" t="n">
-        <v>0.3581</v>
+        <v>0.183</v>
       </c>
       <c r="F184" t="n">
-        <v>13.96</v>
+        <v>3.479</v>
       </c>
       <c r="G184" t="n">
-        <v>2.565</v>
+        <v>5.259</v>
       </c>
       <c r="H184" t="n">
-        <v>1.569</v>
+        <v>1.335</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3806</v>
+        <v>0.2486</v>
       </c>
       <c r="J184" t="n">
-        <v>0.88</v>
+        <v>0.9616</v>
       </c>
       <c r="K184" t="n">
-        <v>18.7</v>
+        <v>29.92</v>
       </c>
       <c r="L184" t="n">
-        <v>0.0054</v>
+        <v>0.003274</v>
       </c>
       <c r="M184" t="n">
-        <v>0.2337</v>
+        <v>0.2702</v>
       </c>
       <c r="N184" t="n">
-        <v>0.01026</v>
+        <v>0.006713</v>
       </c>
     </row>
     <row r="185">
@@ -8308,41 +8308,41 @@
       <c r="B185" s="1" t="n"/>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>SHF-Ctv98-2024</t>
+          <t>SHF-CtL00-2024</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2.198</v>
+        <v>2.991</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3225</v>
+        <v>0.3581</v>
       </c>
       <c r="F185" t="n">
-        <v>15.99</v>
+        <v>13.96</v>
       </c>
       <c r="G185" t="n">
-        <v>2.017</v>
+        <v>2.565</v>
       </c>
       <c r="H185" t="n">
-        <v>1.237</v>
+        <v>1.569</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2039</v>
+        <v>0.3806</v>
       </c>
       <c r="J185" t="n">
-        <v>0.902</v>
+        <v>0.88</v>
       </c>
       <c r="K185" t="n">
-        <v>47.25</v>
+        <v>18.7</v>
       </c>
       <c r="L185" t="n">
-        <v>6.749000000000001e-05</v>
+        <v>0.0054</v>
       </c>
       <c r="M185" t="n">
-        <v>0.4326</v>
+        <v>0.2337</v>
       </c>
       <c r="N185" t="n">
-        <v>0.005464</v>
+        <v>0.01026</v>
       </c>
     </row>
     <row r="186">
@@ -8350,67 +8350,109 @@
       <c r="B186" s="1" t="n"/>
       <c r="C186" s="1" t="inlineStr">
         <is>
+          <t>SHF-Ctv98-2024</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2.198</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="F186" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="K186" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="L186" t="n">
+        <v>6.749000000000001e-05</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0.005464</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n"/>
+      <c r="B187" s="1" t="n"/>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
           <t>SHF-PW04-2024</t>
         </is>
       </c>
-      <c r="D186" t="n">
+      <c r="D187" t="n">
         <v>3.382</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E187" t="n">
         <v>0.2072</v>
       </c>
-      <c r="F186" t="n">
+      <c r="F187" t="n">
         <v>4.598</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G187" t="n">
         <v>4.505</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H187" t="n">
         <v>3.081</v>
       </c>
-      <c r="I186" t="n">
+      <c r="I187" t="n">
         <v>0.3485</v>
       </c>
-      <c r="J186" t="n">
+      <c r="J187" t="n">
         <v>1.111</v>
       </c>
-      <c r="K186" t="n">
+      <c r="K187" t="n">
         <v>25.32</v>
       </c>
-      <c r="L186" t="n">
+      <c r="L187" t="n">
         <v>0.006364</v>
       </c>
-      <c r="M186" t="n">
+      <c r="M187" t="n">
         <v>0.3063</v>
       </c>
-      <c r="N186" t="n">
+      <c r="N187" t="n">
         <v>0.01822</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B169:B172"/>
     <mergeCell ref="A94:A97"/>
     <mergeCell ref="B31:B45"/>
+    <mergeCell ref="B184:B187"/>
     <mergeCell ref="B78:B93"/>
     <mergeCell ref="B11:B21"/>
-    <mergeCell ref="B178:B182"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="A163:A175"/>
+    <mergeCell ref="A177:A187"/>
+    <mergeCell ref="B156:B163"/>
+    <mergeCell ref="A164:A176"/>
     <mergeCell ref="B95:B97"/>
-    <mergeCell ref="A156:A162"/>
+    <mergeCell ref="B164:B168"/>
     <mergeCell ref="B46:B64"/>
-    <mergeCell ref="B172:B175"/>
+    <mergeCell ref="B177:B178"/>
     <mergeCell ref="A98:A155"/>
-    <mergeCell ref="B163:B167"/>
     <mergeCell ref="B65:B77"/>
-    <mergeCell ref="B168:B171"/>
     <mergeCell ref="A78:A93"/>
     <mergeCell ref="B22:B30"/>
     <mergeCell ref="B98:B155"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="B156:B162"/>
+    <mergeCell ref="B179:B183"/>
     <mergeCell ref="A2:A77"/>
-    <mergeCell ref="A176:A186"/>
+    <mergeCell ref="B173:B176"/>
+    <mergeCell ref="A156:A163"/>
     <mergeCell ref="B2:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
